--- a/reports/excel_base/방문객통계_기준.xlsx
+++ b/reports/excel_base/방문객통계_기준.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kim/Desktop/중앙일보/08.보고서/0421/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kim/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27BA3973-78A1-604B-914A-3293525FF382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38A6CCA0-2EA5-5B4F-9150-CBEC1191E446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3740" yWindow="-21000" windowWidth="38400" windowHeight="21000" tabRatio="426" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" tabRatio="426" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="피플카운트" sheetId="1" r:id="rId1"/>
@@ -33,271 +33,61 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="18">
+  <si>
+    <t>날짜</t>
+  </si>
   <si>
     <t>입장인원</t>
+  </si>
+  <si>
+    <t>09:00-10:00 입장</t>
+  </si>
+  <si>
+    <t>10:00-11:00 입장</t>
+  </si>
+  <si>
+    <t>11:00~12:00 입장</t>
+  </si>
+  <si>
+    <t>12:00-13:00 입장</t>
+  </si>
+  <si>
+    <t>13:00-14:00 입장</t>
+  </si>
+  <si>
+    <t>14:00-15:00 입장</t>
+  </si>
+  <si>
+    <t>15:00-16:00 입장</t>
+  </si>
+  <si>
+    <t>16:00-17:00 입장</t>
+  </si>
+  <si>
+    <t>17:00~18:00 입장</t>
+  </si>
+  <si>
+    <t>18:00~19:00 입장</t>
+  </si>
+  <si>
+    <t>19:00~20:00 입장</t>
   </si>
   <si>
     <t>차량탑승인원</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>주출입구</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>명)</t>
-    </r>
+    <t>주출입구(명)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>부출입구</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>명)</t>
-    </r>
-  </si>
-  <si>
-    <t>날짜</t>
+    <t>부출입구(명)</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">14:00-15:00 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>입장</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">15:00-16:00 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>입장</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">09:00-10:00 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>입장</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">12:00-13:00 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>입장</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">13:00-14:00 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>입장</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">10:00-11:00 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>입장</t>
-    </r>
-  </si>
-  <si>
     <t>-</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">16:00-17:00 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>입장</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">17:00~18:00 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>입장</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">18:00~19:00 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>입장</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">19:00~20:00 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>입장</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">11:00~12:00 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>입장</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -307,7 +97,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -335,20 +125,6 @@
       <charset val="129"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Malgun Gothic"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -367,18 +143,15 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
+      <sz val="8"/>
+      <name val="나눔명조"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Malgun Gothic"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
     </font>
@@ -409,7 +182,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -464,32 +237,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -509,24 +256,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -572,32 +332,26 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -609,20 +363,36 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="표준 3" xfId="2" xr:uid="{878C8C8E-1DFC-40B2-8516-51B14AA0666D}"/>
+    <cellStyle name="표준 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -930,7 +700,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:II113"/>
+  <dimension ref="A1:II128"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20" style="3" customWidth="1"/>
@@ -939,52 +709,52 @@
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="J1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="5" t="s">
+      <c r="M1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="20" customHeight="1">
@@ -1029,7 +799,7 @@
         <v>11</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="O2" s="6">
         <v>318</v>
@@ -1075,13 +845,13 @@
         <v>11</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="O3" s="6">
         <v>370</v>
@@ -1744,10 +1514,10 @@
         <v>18</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N16" s="6">
         <v>11</v>
@@ -1795,10 +1565,10 @@
         <v>18</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N17" s="6">
         <v>3</v>
@@ -1846,10 +1616,10 @@
         <v>0</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N18" s="6">
         <v>17</v>
@@ -2050,10 +1820,10 @@
         <v>19</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N22" s="6">
         <v>3</v>
@@ -2101,10 +1871,10 @@
         <v>0</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N23" s="6">
         <v>4</v>
@@ -2152,10 +1922,10 @@
         <v>19</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N24" s="6">
         <v>5</v>
@@ -2356,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N28" s="6">
         <v>5</v>
@@ -2407,10 +2177,10 @@
         <v>10</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N29" s="6">
         <v>0</v>
@@ -2458,10 +2228,10 @@
         <v>0</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N30" s="6">
         <v>0</v>
@@ -2662,10 +2432,10 @@
         <v>0</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N34" s="6">
         <v>4</v>
@@ -2713,10 +2483,10 @@
         <v>0</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N35" s="6">
         <v>3</v>
@@ -2764,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N36" s="13">
         <v>4</v>
@@ -2815,10 +2585,10 @@
         <v>0</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N37" s="13">
         <v>11</v>
@@ -2917,10 +2687,10 @@
         <v>0</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N39" s="13">
         <v>30</v>
@@ -2968,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N40" s="13">
         <v>9</v>
@@ -3070,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="L42" s="16" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M42" s="16" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N42" s="16">
         <v>12</v>
@@ -3121,10 +2891,10 @@
         <v>0</v>
       </c>
       <c r="L43" s="16" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M43" s="16" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N43" s="16">
         <v>5</v>
@@ -3223,10 +2993,10 @@
         <v>0</v>
       </c>
       <c r="L45" s="16" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M45" s="16" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N45" s="16">
         <v>124</v>
@@ -3274,10 +3044,10 @@
         <v>0</v>
       </c>
       <c r="L46" s="16" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M46" s="16" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N46" s="16">
         <v>54</v>
@@ -3376,10 +3146,10 @@
         <v>0</v>
       </c>
       <c r="L48" s="16" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M48" s="16" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N48" s="16">
         <v>26</v>
@@ -3529,10 +3299,10 @@
         <v>0</v>
       </c>
       <c r="L51" s="20" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M51" s="20" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N51" s="16">
         <v>3</v>
@@ -3580,10 +3350,10 @@
         <v>0</v>
       </c>
       <c r="L52" s="20" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M52" s="20" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N52" s="16">
         <v>65</v>
@@ -3631,10 +3401,10 @@
         <v>0</v>
       </c>
       <c r="L53" s="17" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M53" s="17" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N53" s="16">
         <v>51</v>
@@ -3682,10 +3452,10 @@
         <v>14</v>
       </c>
       <c r="L54" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M54" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N54" s="6">
         <v>88</v>
@@ -3784,10 +3554,10 @@
         <v>0</v>
       </c>
       <c r="L56" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M56" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N56" s="6">
         <v>327</v>
@@ -3835,10 +3605,10 @@
         <v>10</v>
       </c>
       <c r="L57" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M57" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N57" s="6">
         <v>25</v>
@@ -3886,10 +3656,10 @@
         <v>14</v>
       </c>
       <c r="L58" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M58" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N58" s="6">
         <v>13</v>
@@ -4141,10 +3911,10 @@
         <v>0</v>
       </c>
       <c r="L63" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M63" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N63" s="6">
         <v>3</v>
@@ -4192,10 +3962,10 @@
         <v>0</v>
       </c>
       <c r="L64" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M64" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N64" s="6">
         <v>7</v>
@@ -4243,10 +4013,10 @@
         <v>0</v>
       </c>
       <c r="L65" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M65" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N65" s="6">
         <v>18</v>
@@ -4294,10 +4064,10 @@
         <v>0</v>
       </c>
       <c r="L66" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M66" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N66" s="16">
         <v>21</v>
@@ -4394,10 +4164,10 @@
         <v>0</v>
       </c>
       <c r="L68" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M68" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N68" s="6">
         <v>189</v>
@@ -4444,10 +4214,10 @@
         <v>12</v>
       </c>
       <c r="L69" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M69" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N69" s="6">
         <v>8</v>
@@ -4494,10 +4264,10 @@
         <v>17</v>
       </c>
       <c r="L70" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M70" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N70" s="6">
         <v>6</v>
@@ -4544,10 +4314,10 @@
         <v>24</v>
       </c>
       <c r="L71" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M71" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N71" s="6">
         <v>18</v>
@@ -4594,10 +4364,10 @@
         <v>10</v>
       </c>
       <c r="L72" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M72" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N72" s="6">
         <v>33</v>
@@ -4694,10 +4464,10 @@
         <v>28</v>
       </c>
       <c r="L74" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M74" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N74" s="6">
         <v>368</v>
@@ -4741,13 +4511,13 @@
         <v>160</v>
       </c>
       <c r="K75" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L75" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M75" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N75" s="6">
         <v>22</v>
@@ -4791,13 +4561,13 @@
         <v>79</v>
       </c>
       <c r="K76" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L76" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M76" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N76" s="6">
         <v>13</v>
@@ -4841,10 +4611,10 @@
         <v>117</v>
       </c>
       <c r="K77" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L77" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M77" s="14"/>
       <c r="N77" s="6">
@@ -4942,10 +4712,10 @@
         <v>51</v>
       </c>
       <c r="L79" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M79" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N79" s="6">
         <v>377</v>
@@ -4989,13 +4759,13 @@
         <v>119</v>
       </c>
       <c r="K80" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L80" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M80" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N80" s="6">
         <v>51</v>
@@ -5011,57 +4781,57 @@
       <c r="A81" s="21">
         <v>46113</v>
       </c>
-      <c r="B81" s="28">
+      <c r="B81" s="26">
         <v>1973</v>
       </c>
-      <c r="C81" s="29">
+      <c r="C81" s="27">
         <v>95</v>
       </c>
-      <c r="D81" s="29">
+      <c r="D81" s="27">
         <v>76</v>
       </c>
-      <c r="E81" s="29">
+      <c r="E81" s="27">
         <v>235</v>
       </c>
-      <c r="F81" s="29">
+      <c r="F81" s="27">
         <v>792</v>
       </c>
-      <c r="G81" s="29">
+      <c r="G81" s="27">
         <v>198</v>
       </c>
-      <c r="H81" s="29">
+      <c r="H81" s="27">
         <v>186</v>
       </c>
-      <c r="I81" s="29">
+      <c r="I81" s="27">
         <v>180</v>
       </c>
-      <c r="J81" s="29">
+      <c r="J81" s="27">
         <v>174</v>
       </c>
-      <c r="K81" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="L81" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="M81" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="N81" s="29">
+      <c r="K81" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="L81" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="M81" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="N81" s="27">
         <v>37</v>
       </c>
-      <c r="O81" s="28">
+      <c r="O81" s="26">
         <v>1662</v>
       </c>
-      <c r="P81" s="28">
+      <c r="P81" s="26">
         <v>274</v>
       </c>
     </row>
     <row r="82" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
-      <c r="A82" s="31">
+      <c r="A82" s="29">
         <v>46114</v>
       </c>
-      <c r="B82" s="32">
+      <c r="B82" s="30">
         <v>1956</v>
       </c>
       <c r="C82" s="12">
@@ -5088,22 +4858,22 @@
       <c r="J82" s="12">
         <v>154</v>
       </c>
-      <c r="K82" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="L82" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="M82" s="30" t="s">
-        <v>12</v>
+      <c r="K82" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="L82" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="M82" s="28" t="s">
+        <v>16</v>
       </c>
       <c r="N82" s="12">
         <v>30</v>
       </c>
-      <c r="O82" s="32">
+      <c r="O82" s="30">
         <v>1705</v>
       </c>
-      <c r="P82" s="32">
+      <c r="P82" s="30">
         <v>221</v>
       </c>
     </row>
@@ -5139,13 +4909,13 @@
         <v>195</v>
       </c>
       <c r="K83" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L83" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M83" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N83" s="6">
         <v>42</v>
@@ -5239,13 +5009,13 @@
         <v>472</v>
       </c>
       <c r="K85" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L85" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M85" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N85" s="6">
         <v>334</v>
@@ -5261,49 +5031,49 @@
       <c r="A86" s="21">
         <v>46119</v>
       </c>
-      <c r="B86" s="28">
+      <c r="B86" s="26">
         <v>1632</v>
       </c>
-      <c r="C86" s="29">
+      <c r="C86" s="27">
         <v>82</v>
       </c>
-      <c r="D86" s="29">
+      <c r="D86" s="27">
         <v>58</v>
       </c>
-      <c r="E86" s="29">
+      <c r="E86" s="27">
         <v>174</v>
       </c>
-      <c r="F86" s="29">
+      <c r="F86" s="27">
         <v>702</v>
       </c>
-      <c r="G86" s="29">
+      <c r="G86" s="27">
         <v>184</v>
       </c>
-      <c r="H86" s="29">
+      <c r="H86" s="27">
         <v>161</v>
       </c>
-      <c r="I86" s="29">
+      <c r="I86" s="27">
         <v>132</v>
       </c>
-      <c r="J86" s="29">
+      <c r="J86" s="27">
         <v>128</v>
       </c>
-      <c r="K86" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="L86" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="M86" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="N86" s="29">
+      <c r="K86" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="L86" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="M86" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="N86" s="27">
         <v>11</v>
       </c>
-      <c r="O86" s="28">
+      <c r="O86" s="26">
         <v>1392</v>
       </c>
-      <c r="P86" s="28">
+      <c r="P86" s="26">
         <v>229</v>
       </c>
     </row>
@@ -5339,13 +5109,13 @@
         <v>170</v>
       </c>
       <c r="K87" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L87" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M87" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N87" s="6">
         <v>119</v>
@@ -5389,13 +5159,13 @@
         <v>12</v>
       </c>
       <c r="K88" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L88" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M88" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N88" s="6">
         <v>0</v>
@@ -5439,13 +5209,13 @@
         <v>62</v>
       </c>
       <c r="K89" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L89" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M89" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N89" s="6">
         <v>14</v>
@@ -5539,13 +5309,13 @@
         <v>465</v>
       </c>
       <c r="K91" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L91" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M91" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N91" s="6">
         <v>424</v>
@@ -5558,10 +5328,10 @@
       </c>
     </row>
     <row r="92" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
-      <c r="A92" s="34">
+      <c r="A92" s="32">
         <v>46126</v>
       </c>
-      <c r="B92" s="32">
+      <c r="B92" s="30">
         <v>1925</v>
       </c>
       <c r="C92" s="6">
@@ -5588,22 +5358,22 @@
       <c r="J92" s="6">
         <v>110</v>
       </c>
-      <c r="K92" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="L92" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="M92" s="30" t="s">
-        <v>12</v>
+      <c r="K92" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="L92" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="M92" s="28" t="s">
+        <v>16</v>
       </c>
       <c r="N92" s="12">
         <v>94</v>
       </c>
-      <c r="O92" s="32">
+      <c r="O92" s="30">
         <v>1616</v>
       </c>
-      <c r="P92" s="32">
+      <c r="P92" s="30">
         <v>215</v>
       </c>
     </row>
@@ -5639,13 +5409,13 @@
         <v>144</v>
       </c>
       <c r="K93" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L93" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M93" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N93" s="6">
         <v>62</v>
@@ -5689,13 +5459,13 @@
         <v>134</v>
       </c>
       <c r="K94" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L94" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M94" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N94" s="6">
         <v>172</v>
@@ -5739,13 +5509,13 @@
         <v>171</v>
       </c>
       <c r="K95" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L95" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M95" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N95" s="6">
         <v>81</v>
@@ -5807,57 +5577,57 @@
         <v>920</v>
       </c>
     </row>
-    <row r="97" spans="1:243" s="18" customFormat="1" ht="20" customHeight="1">
-      <c r="A97" s="31">
+    <row r="97" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="A97" s="29">
         <v>46131</v>
       </c>
-      <c r="B97" s="28">
+      <c r="B97" s="26">
         <v>2979</v>
       </c>
-      <c r="C97" s="29">
+      <c r="C97" s="27">
         <v>165</v>
       </c>
-      <c r="D97" s="29">
+      <c r="D97" s="27">
         <v>198</v>
       </c>
-      <c r="E97" s="29">
+      <c r="E97" s="27">
         <v>286</v>
       </c>
-      <c r="F97" s="29">
+      <c r="F97" s="27">
         <v>305</v>
       </c>
-      <c r="G97" s="29">
+      <c r="G97" s="27">
         <v>438</v>
       </c>
-      <c r="H97" s="29">
+      <c r="H97" s="27">
         <v>508</v>
       </c>
-      <c r="I97" s="29">
+      <c r="I97" s="27">
         <v>500</v>
       </c>
-      <c r="J97" s="29">
+      <c r="J97" s="27">
         <v>458</v>
       </c>
-      <c r="K97" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="L97" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="M97" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="N97" s="29">
+      <c r="K97" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="L97" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="M97" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="N97" s="27">
         <v>121</v>
       </c>
-      <c r="O97" s="28">
+      <c r="O97" s="26">
         <v>2217</v>
       </c>
-      <c r="P97" s="35">
+      <c r="P97" s="33">
         <v>641</v>
       </c>
     </row>
-    <row r="98" spans="1:243" s="18" customFormat="1" ht="20" customHeight="1">
+    <row r="98" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
       <c r="A98" s="21">
         <v>46133</v>
       </c>
@@ -5889,13 +5659,13 @@
         <v>102</v>
       </c>
       <c r="K98" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L98" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M98" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N98" s="6">
         <v>80</v>
@@ -5907,815 +5677,1492 @@
         <v>269</v>
       </c>
     </row>
-    <row r="99" spans="1:243" s="4" customFormat="1" ht="16.25" customHeight="1" thickBot="1">
-      <c r="A99" s="26"/>
-      <c r="B99" s="27">
-        <f>SUM(B2:B98)</f>
-        <v>122680</v>
-      </c>
-      <c r="C99" s="27">
-        <f t="shared" ref="C99:P99" si="1">SUM(C2:C98)</f>
-        <v>6648</v>
-      </c>
-      <c r="D99" s="27">
+    <row r="99" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="A99" s="8">
+        <v>46134</v>
+      </c>
+      <c r="B99" s="6">
+        <v>1314</v>
+      </c>
+      <c r="C99" s="6">
+        <v>38</v>
+      </c>
+      <c r="D99" s="6">
+        <v>78</v>
+      </c>
+      <c r="E99" s="6">
+        <v>127</v>
+      </c>
+      <c r="F99" s="6">
+        <v>502</v>
+      </c>
+      <c r="G99" s="6">
+        <v>127</v>
+      </c>
+      <c r="H99" s="6">
+        <v>181</v>
+      </c>
+      <c r="I99" s="6">
+        <v>156</v>
+      </c>
+      <c r="J99" s="6">
+        <v>105</v>
+      </c>
+      <c r="K99" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="L99" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="M99" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N99" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O99" s="6">
+        <v>1060</v>
+      </c>
+      <c r="P99" s="6">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="A100" s="8">
+        <v>46135</v>
+      </c>
+      <c r="B100" s="6">
+        <v>1836</v>
+      </c>
+      <c r="C100" s="6">
+        <v>58</v>
+      </c>
+      <c r="D100" s="6">
+        <v>129</v>
+      </c>
+      <c r="E100" s="6">
+        <v>255</v>
+      </c>
+      <c r="F100" s="6">
+        <v>628</v>
+      </c>
+      <c r="G100" s="6">
+        <v>158</v>
+      </c>
+      <c r="H100" s="6">
+        <v>117</v>
+      </c>
+      <c r="I100" s="6">
+        <v>134</v>
+      </c>
+      <c r="J100" s="6">
+        <v>156</v>
+      </c>
+      <c r="K100" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="L100" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="M100" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N100" s="6">
+        <v>201</v>
+      </c>
+      <c r="O100" s="6">
+        <v>1389</v>
+      </c>
+      <c r="P100" s="6">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="A101" s="8">
+        <v>46136</v>
+      </c>
+      <c r="B101" s="6">
+        <v>2414</v>
+      </c>
+      <c r="C101" s="6">
+        <v>93</v>
+      </c>
+      <c r="D101" s="6">
+        <v>171</v>
+      </c>
+      <c r="E101" s="6">
+        <v>279</v>
+      </c>
+      <c r="F101" s="6">
+        <v>727</v>
+      </c>
+      <c r="G101" s="6">
+        <v>364</v>
+      </c>
+      <c r="H101" s="6">
+        <v>165</v>
+      </c>
+      <c r="I101" s="6">
+        <v>188</v>
+      </c>
+      <c r="J101" s="6">
+        <v>169</v>
+      </c>
+      <c r="K101" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="L101" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="M101" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N101" s="6">
+        <v>258</v>
+      </c>
+      <c r="O101" s="6">
+        <v>1914</v>
+      </c>
+      <c r="P101" s="6">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="A102" s="8">
+        <v>46137</v>
+      </c>
+      <c r="B102" s="6">
+        <v>4570</v>
+      </c>
+      <c r="C102" s="6">
+        <v>244</v>
+      </c>
+      <c r="D102" s="6">
+        <v>249</v>
+      </c>
+      <c r="E102" s="6">
+        <v>223</v>
+      </c>
+      <c r="F102" s="6">
+        <v>315</v>
+      </c>
+      <c r="G102" s="6">
+        <v>478</v>
+      </c>
+      <c r="H102" s="6">
+        <v>479</v>
+      </c>
+      <c r="I102" s="6">
+        <v>574</v>
+      </c>
+      <c r="J102" s="6">
+        <v>634</v>
+      </c>
+      <c r="K102" s="6">
+        <v>428</v>
+      </c>
+      <c r="L102" s="6">
+        <v>278</v>
+      </c>
+      <c r="M102" s="6">
+        <v>198</v>
+      </c>
+      <c r="N102" s="6">
+        <v>497</v>
+      </c>
+      <c r="O102" s="6">
+        <v>3247</v>
+      </c>
+      <c r="P102" s="6">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="A103" s="34">
+        <v>46138</v>
+      </c>
+      <c r="B103" s="12">
+        <v>3847</v>
+      </c>
+      <c r="C103" s="12">
+        <v>216</v>
+      </c>
+      <c r="D103" s="12">
+        <v>229</v>
+      </c>
+      <c r="E103" s="12">
+        <v>272</v>
+      </c>
+      <c r="F103" s="12">
+        <v>368</v>
+      </c>
+      <c r="G103" s="12">
+        <v>563</v>
+      </c>
+      <c r="H103" s="12">
+        <v>583</v>
+      </c>
+      <c r="I103" s="12">
+        <v>648</v>
+      </c>
+      <c r="J103" s="12">
+        <v>500</v>
+      </c>
+      <c r="K103" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="L103" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="M103" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="N103" s="12">
+        <v>468</v>
+      </c>
+      <c r="O103" s="12">
+        <v>2641</v>
+      </c>
+      <c r="P103" s="12">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="A104" s="8">
+        <v>46140</v>
+      </c>
+      <c r="B104" s="6">
+        <v>1145</v>
+      </c>
+      <c r="C104" s="6">
+        <v>69</v>
+      </c>
+      <c r="D104" s="6">
+        <v>47</v>
+      </c>
+      <c r="E104" s="6">
+        <v>97</v>
+      </c>
+      <c r="F104" s="6">
+        <v>434</v>
+      </c>
+      <c r="G104" s="6">
+        <v>132</v>
+      </c>
+      <c r="H104" s="6">
+        <v>140</v>
+      </c>
+      <c r="I104" s="6">
+        <v>114</v>
+      </c>
+      <c r="J104" s="6">
+        <v>98</v>
+      </c>
+      <c r="K104" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="L104" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="M104" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N104" s="6">
+        <v>14</v>
+      </c>
+      <c r="O104" s="6">
+        <v>961</v>
+      </c>
+      <c r="P104" s="6">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="A105" s="8">
+        <v>46141</v>
+      </c>
+      <c r="B105" s="6">
+        <v>1952</v>
+      </c>
+      <c r="C105" s="6">
+        <f>C100+C102</f>
+        <v>302</v>
+      </c>
+      <c r="D105" s="6">
+        <f t="shared" ref="D105:J105" si="1">D100+D102</f>
+        <v>378</v>
+      </c>
+      <c r="E105" s="6">
         <f t="shared" si="1"/>
-        <v>7497</v>
-      </c>
-      <c r="E99" s="27">
+        <v>478</v>
+      </c>
+      <c r="F105" s="6">
         <f t="shared" si="1"/>
-        <v>10326</v>
-      </c>
-      <c r="F99" s="27">
+        <v>943</v>
+      </c>
+      <c r="G105" s="6">
         <f t="shared" si="1"/>
-        <v>23288</v>
-      </c>
-      <c r="G99" s="27">
+        <v>636</v>
+      </c>
+      <c r="H105" s="6">
         <f t="shared" si="1"/>
-        <v>16433</v>
-      </c>
-      <c r="H99" s="27">
+        <v>596</v>
+      </c>
+      <c r="I105" s="6">
         <f t="shared" si="1"/>
-        <v>16490</v>
-      </c>
-      <c r="I99" s="27">
+        <v>708</v>
+      </c>
+      <c r="J105" s="6">
         <f t="shared" si="1"/>
-        <v>16152</v>
-      </c>
-      <c r="J99" s="27">
-        <f t="shared" si="1"/>
-        <v>12401</v>
-      </c>
-      <c r="K99" s="27">
-        <f t="shared" si="1"/>
-        <v>3172</v>
-      </c>
-      <c r="L99" s="27">
-        <f t="shared" si="1"/>
-        <v>1497</v>
-      </c>
-      <c r="M99" s="27">
-        <f t="shared" si="1"/>
-        <v>831</v>
-      </c>
-      <c r="N99" s="27">
-        <f t="shared" si="1"/>
-        <v>7584</v>
-      </c>
-      <c r="O99" s="27">
-        <f t="shared" si="1"/>
-        <v>84410</v>
-      </c>
-      <c r="P99" s="27">
-        <f t="shared" si="1"/>
-        <v>30686</v>
-      </c>
-      <c r="Q99"/>
-      <c r="R99"/>
-      <c r="S99"/>
-      <c r="T99"/>
-      <c r="U99"/>
-      <c r="V99"/>
-      <c r="W99"/>
-      <c r="X99"/>
-      <c r="Y99"/>
-      <c r="Z99"/>
-      <c r="AA99"/>
-      <c r="AB99"/>
-      <c r="AC99"/>
-      <c r="AD99"/>
-      <c r="AE99"/>
-      <c r="AF99"/>
-      <c r="AG99"/>
-      <c r="AH99"/>
-      <c r="AI99"/>
-      <c r="AJ99"/>
-      <c r="AK99"/>
-      <c r="AL99"/>
-      <c r="AM99"/>
-      <c r="AN99"/>
-      <c r="AO99"/>
-      <c r="AP99"/>
-      <c r="AQ99"/>
-      <c r="AR99"/>
-      <c r="AS99"/>
-      <c r="AT99"/>
-      <c r="AU99"/>
-      <c r="AV99"/>
-      <c r="AW99"/>
-      <c r="AX99"/>
-      <c r="AY99"/>
-      <c r="AZ99"/>
-      <c r="BA99"/>
-      <c r="BB99"/>
-      <c r="BC99"/>
-      <c r="BD99"/>
-      <c r="BE99"/>
-      <c r="BF99"/>
-      <c r="BG99"/>
-      <c r="BH99"/>
-      <c r="BI99"/>
-      <c r="BJ99"/>
-      <c r="BK99"/>
-      <c r="BL99"/>
-      <c r="BM99"/>
-      <c r="BN99"/>
-      <c r="BO99"/>
-      <c r="BP99"/>
-      <c r="BQ99"/>
-      <c r="BR99"/>
-      <c r="BS99"/>
-      <c r="BT99"/>
-      <c r="BU99"/>
-      <c r="BV99"/>
-      <c r="BW99"/>
-      <c r="BX99"/>
-      <c r="BY99"/>
-      <c r="BZ99"/>
-      <c r="CA99"/>
-      <c r="CB99"/>
-      <c r="CC99"/>
-      <c r="CD99"/>
-      <c r="CE99"/>
-      <c r="CF99"/>
-      <c r="CG99"/>
-      <c r="CH99"/>
-      <c r="CI99"/>
-      <c r="CJ99"/>
-      <c r="CK99"/>
-      <c r="CL99"/>
-      <c r="CM99"/>
-      <c r="CN99"/>
-      <c r="CO99"/>
-      <c r="CP99"/>
-      <c r="CQ99"/>
-      <c r="CR99"/>
-      <c r="CS99"/>
-      <c r="CT99"/>
-      <c r="CU99"/>
-      <c r="CV99"/>
-      <c r="CW99"/>
-      <c r="CX99"/>
-      <c r="CY99"/>
-      <c r="CZ99"/>
-      <c r="DA99"/>
-      <c r="DB99"/>
-      <c r="DC99"/>
-      <c r="DD99"/>
-      <c r="DE99"/>
-      <c r="DF99"/>
-      <c r="DG99"/>
-      <c r="DH99"/>
-      <c r="DI99"/>
-      <c r="DJ99"/>
-      <c r="DK99"/>
-      <c r="DL99"/>
-      <c r="DM99"/>
-      <c r="DN99"/>
-      <c r="DO99"/>
-      <c r="DP99"/>
-      <c r="DQ99"/>
-      <c r="DR99"/>
-      <c r="DS99"/>
-      <c r="DT99"/>
-      <c r="DU99"/>
-      <c r="DV99"/>
-      <c r="DW99"/>
-      <c r="DX99"/>
-      <c r="DY99"/>
-      <c r="DZ99"/>
-      <c r="EA99"/>
-      <c r="EB99"/>
-      <c r="EC99"/>
-      <c r="ED99"/>
-      <c r="EE99"/>
-      <c r="EF99"/>
-      <c r="EG99"/>
-      <c r="EH99"/>
-      <c r="EI99"/>
-      <c r="EJ99"/>
-      <c r="EK99"/>
-      <c r="EL99"/>
-      <c r="EM99"/>
-      <c r="EN99"/>
-      <c r="EO99"/>
-      <c r="EP99"/>
-      <c r="EQ99"/>
-      <c r="ER99"/>
-      <c r="ES99"/>
-      <c r="ET99"/>
-      <c r="EU99"/>
-      <c r="EV99"/>
-      <c r="EW99"/>
-      <c r="EX99"/>
-      <c r="EY99"/>
-      <c r="EZ99"/>
-      <c r="FA99"/>
-      <c r="FB99"/>
-      <c r="FC99"/>
-      <c r="FD99"/>
-      <c r="FE99"/>
-      <c r="FF99"/>
-      <c r="FG99"/>
-      <c r="FH99"/>
-      <c r="FI99"/>
-      <c r="FJ99"/>
-      <c r="FK99"/>
-      <c r="FL99"/>
-      <c r="FM99"/>
-      <c r="FN99"/>
-      <c r="FO99"/>
-      <c r="FP99"/>
-      <c r="FQ99"/>
-      <c r="FR99"/>
-      <c r="FS99"/>
-      <c r="FT99"/>
-      <c r="FU99"/>
-      <c r="FV99"/>
-      <c r="FW99"/>
-      <c r="FX99"/>
-      <c r="FY99"/>
-      <c r="FZ99"/>
-      <c r="GA99"/>
-      <c r="GB99"/>
-      <c r="GC99"/>
-      <c r="GD99"/>
-      <c r="GE99"/>
-      <c r="GF99"/>
-      <c r="GG99"/>
-      <c r="GH99"/>
-      <c r="GI99"/>
-      <c r="GJ99"/>
-      <c r="GK99"/>
-      <c r="GL99"/>
-      <c r="GM99"/>
-      <c r="GN99"/>
-      <c r="GO99"/>
-      <c r="GP99"/>
-      <c r="GQ99"/>
-      <c r="GR99"/>
-      <c r="GS99"/>
-      <c r="GT99"/>
-      <c r="GU99"/>
-      <c r="GV99"/>
-      <c r="GW99"/>
-      <c r="GX99"/>
-      <c r="GY99"/>
-      <c r="GZ99"/>
-      <c r="HA99"/>
-      <c r="HB99"/>
-      <c r="HC99"/>
-      <c r="HD99"/>
-      <c r="HE99"/>
-      <c r="HF99"/>
-      <c r="HG99"/>
-      <c r="HH99"/>
-      <c r="HI99"/>
-      <c r="HJ99"/>
-      <c r="HK99"/>
-      <c r="HL99"/>
-      <c r="HM99"/>
-      <c r="HN99"/>
-      <c r="HO99"/>
-      <c r="HP99"/>
-      <c r="HQ99"/>
-      <c r="HR99"/>
-      <c r="HS99"/>
-      <c r="HT99"/>
-      <c r="HU99"/>
-      <c r="HV99"/>
-      <c r="HW99"/>
-      <c r="HX99"/>
-      <c r="HY99"/>
-      <c r="HZ99"/>
-      <c r="IA99"/>
-      <c r="IB99"/>
-      <c r="IC99"/>
-      <c r="ID99"/>
-      <c r="IE99"/>
-      <c r="IF99"/>
-      <c r="IG99"/>
-      <c r="IH99"/>
-      <c r="II99"/>
-    </row>
-    <row r="100" spans="1:243">
-      <c r="A100" s="25"/>
-    </row>
-    <row r="101" spans="1:243">
-      <c r="A101" s="25"/>
-      <c r="B101" s="4"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="4"/>
-      <c r="E101" s="4"/>
-      <c r="F101" s="4"/>
-      <c r="G101" s="4"/>
-      <c r="H101" s="4"/>
-      <c r="I101" s="4"/>
-      <c r="J101" s="4"/>
-      <c r="N101" s="4"/>
-      <c r="Q101" s="4"/>
-      <c r="R101" s="4"/>
-      <c r="S101" s="4"/>
-      <c r="T101" s="4"/>
-      <c r="U101" s="4"/>
-      <c r="V101" s="4"/>
-      <c r="W101" s="4"/>
-      <c r="X101" s="4"/>
-      <c r="Y101" s="4"/>
-      <c r="Z101" s="4"/>
-      <c r="AA101" s="4"/>
-      <c r="AB101" s="4"/>
-      <c r="AC101" s="4"/>
-      <c r="AD101" s="4"/>
-      <c r="AE101" s="4"/>
-      <c r="AF101" s="4"/>
-      <c r="AG101" s="4"/>
-      <c r="AH101" s="4"/>
-      <c r="AI101" s="4"/>
-      <c r="AJ101" s="4"/>
-      <c r="AK101" s="4"/>
-      <c r="AL101" s="4"/>
-      <c r="AM101" s="4"/>
-      <c r="AN101" s="4"/>
-      <c r="AO101" s="4"/>
-      <c r="AP101" s="4"/>
-      <c r="AQ101" s="4"/>
-      <c r="AR101" s="4"/>
-      <c r="AS101" s="4"/>
-      <c r="AT101" s="4"/>
-      <c r="AU101" s="4"/>
-      <c r="AV101" s="4"/>
-      <c r="AW101" s="4"/>
-      <c r="AX101" s="4"/>
-      <c r="AY101" s="4"/>
-      <c r="AZ101" s="4"/>
-      <c r="BA101" s="4"/>
-      <c r="BB101" s="4"/>
-      <c r="BC101" s="4"/>
-      <c r="BD101" s="4"/>
-      <c r="BE101" s="4"/>
-      <c r="BF101" s="4"/>
-      <c r="BG101" s="4"/>
-      <c r="BH101" s="4"/>
-      <c r="BI101" s="4"/>
-      <c r="BJ101" s="4"/>
-      <c r="BK101" s="4"/>
-      <c r="BL101" s="4"/>
-      <c r="BM101" s="4"/>
-      <c r="BN101" s="4"/>
-      <c r="BO101" s="4"/>
-      <c r="BP101" s="4"/>
-      <c r="BQ101" s="4"/>
-      <c r="BR101" s="4"/>
-      <c r="BS101" s="4"/>
-      <c r="BT101" s="4"/>
-      <c r="BU101" s="4"/>
-      <c r="BV101" s="4"/>
-      <c r="BW101" s="4"/>
-      <c r="BX101" s="4"/>
-      <c r="BY101" s="4"/>
-      <c r="BZ101" s="4"/>
-      <c r="CA101" s="4"/>
-      <c r="CB101" s="4"/>
-      <c r="CC101" s="4"/>
-      <c r="CD101" s="4"/>
-      <c r="CE101" s="4"/>
-      <c r="CF101" s="4"/>
-      <c r="CG101" s="4"/>
-      <c r="CH101" s="4"/>
-      <c r="CI101" s="4"/>
-      <c r="CJ101" s="4"/>
-      <c r="CK101" s="4"/>
-      <c r="CL101" s="4"/>
-      <c r="CM101" s="4"/>
-      <c r="CN101" s="4"/>
-      <c r="CO101" s="4"/>
-      <c r="CP101" s="4"/>
-      <c r="CQ101" s="4"/>
-      <c r="CR101" s="4"/>
-      <c r="CS101" s="4"/>
-      <c r="CT101" s="4"/>
-      <c r="CU101" s="4"/>
-      <c r="CV101" s="4"/>
-      <c r="CW101" s="4"/>
-      <c r="CX101" s="4"/>
-      <c r="CY101" s="4"/>
-      <c r="CZ101" s="4"/>
-      <c r="DA101" s="4"/>
-      <c r="DB101" s="4"/>
-      <c r="DC101" s="4"/>
-      <c r="DD101" s="4"/>
-      <c r="DE101" s="4"/>
-      <c r="DF101" s="4"/>
-      <c r="DG101" s="4"/>
-      <c r="DH101" s="4"/>
-      <c r="DI101" s="4"/>
-      <c r="DJ101" s="4"/>
-      <c r="DK101" s="4"/>
-      <c r="DL101" s="4"/>
-      <c r="DM101" s="4"/>
-      <c r="DN101" s="4"/>
-      <c r="DO101" s="4"/>
-      <c r="DP101" s="4"/>
-      <c r="DQ101" s="4"/>
-      <c r="DR101" s="4"/>
-      <c r="DS101" s="4"/>
-      <c r="DT101" s="4"/>
-      <c r="DU101" s="4"/>
-      <c r="DV101" s="4"/>
-      <c r="DW101" s="4"/>
-      <c r="DX101" s="4"/>
-      <c r="DY101" s="4"/>
-      <c r="DZ101" s="4"/>
-      <c r="EA101" s="4"/>
-      <c r="EB101" s="4"/>
-      <c r="EC101" s="4"/>
-      <c r="ED101" s="4"/>
-      <c r="EE101" s="4"/>
-      <c r="EF101" s="4"/>
-      <c r="EG101" s="4"/>
-      <c r="EH101" s="4"/>
-      <c r="EI101" s="4"/>
-      <c r="EJ101" s="4"/>
-      <c r="EK101" s="4"/>
-      <c r="EL101" s="4"/>
-      <c r="EM101" s="4"/>
-      <c r="EN101" s="4"/>
-      <c r="EO101" s="4"/>
-      <c r="EP101" s="4"/>
-      <c r="EQ101" s="4"/>
-      <c r="ER101" s="4"/>
-      <c r="ES101" s="4"/>
-      <c r="ET101" s="4"/>
-      <c r="EU101" s="4"/>
-      <c r="EV101" s="4"/>
-      <c r="EW101" s="4"/>
-      <c r="EX101" s="4"/>
-      <c r="EY101" s="4"/>
-      <c r="EZ101" s="4"/>
-      <c r="FA101" s="4"/>
-      <c r="FB101" s="4"/>
-      <c r="FC101" s="4"/>
-      <c r="FD101" s="4"/>
-      <c r="FE101" s="4"/>
-      <c r="FF101" s="4"/>
-      <c r="FG101" s="4"/>
-      <c r="FH101" s="4"/>
-      <c r="FI101" s="4"/>
-      <c r="FJ101" s="4"/>
-      <c r="FK101" s="4"/>
-      <c r="FL101" s="4"/>
-      <c r="FM101" s="4"/>
-      <c r="FN101" s="4"/>
-      <c r="FO101" s="4"/>
-      <c r="FP101" s="4"/>
-      <c r="FQ101" s="4"/>
-      <c r="FR101" s="4"/>
-      <c r="FS101" s="4"/>
-      <c r="FT101" s="4"/>
-      <c r="FU101" s="4"/>
-      <c r="FV101" s="4"/>
-      <c r="FW101" s="4"/>
-      <c r="FX101" s="4"/>
-      <c r="FY101" s="4"/>
-      <c r="FZ101" s="4"/>
-      <c r="GA101" s="4"/>
-      <c r="GB101" s="4"/>
-      <c r="GC101" s="4"/>
-      <c r="GD101" s="4"/>
-      <c r="GE101" s="4"/>
-      <c r="GF101" s="4"/>
-      <c r="GG101" s="4"/>
-      <c r="GH101" s="4"/>
-      <c r="GI101" s="4"/>
-      <c r="GJ101" s="4"/>
-      <c r="GK101" s="4"/>
-      <c r="GL101" s="4"/>
-      <c r="GM101" s="4"/>
-      <c r="GN101" s="4"/>
-      <c r="GO101" s="4"/>
-      <c r="GP101" s="4"/>
-      <c r="GQ101" s="4"/>
-      <c r="GR101" s="4"/>
-      <c r="GS101" s="4"/>
-      <c r="GT101" s="4"/>
-      <c r="GU101" s="4"/>
-      <c r="GV101" s="4"/>
-      <c r="GW101" s="4"/>
-      <c r="GX101" s="4"/>
-      <c r="GY101" s="4"/>
-      <c r="GZ101" s="4"/>
-      <c r="HA101" s="4"/>
-      <c r="HB101" s="4"/>
-      <c r="HC101" s="4"/>
-      <c r="HD101" s="4"/>
-      <c r="HE101" s="4"/>
-      <c r="HF101" s="4"/>
-      <c r="HG101" s="4"/>
-      <c r="HH101" s="4"/>
-      <c r="HI101" s="4"/>
-      <c r="HJ101" s="4"/>
-      <c r="HK101" s="4"/>
-      <c r="HL101" s="4"/>
-      <c r="HM101" s="4"/>
-      <c r="HN101" s="4"/>
-      <c r="HO101" s="4"/>
-      <c r="HP101" s="4"/>
-      <c r="HQ101" s="4"/>
-      <c r="HR101" s="4"/>
-      <c r="HS101" s="4"/>
-      <c r="HT101" s="4"/>
-      <c r="HU101" s="4"/>
-      <c r="HV101" s="4"/>
-      <c r="HW101" s="4"/>
-      <c r="HX101" s="4"/>
-      <c r="HY101" s="4"/>
-      <c r="HZ101" s="4"/>
-      <c r="IA101" s="4"/>
-      <c r="IB101" s="4"/>
-      <c r="IC101" s="4"/>
-      <c r="ID101" s="4"/>
-      <c r="IE101" s="4"/>
-      <c r="IF101" s="4"/>
-      <c r="IG101" s="4"/>
-      <c r="IH101" s="4"/>
-      <c r="II101" s="4"/>
-    </row>
-    <row r="102" spans="1:243">
-      <c r="B102" s="23"/>
-      <c r="C102" s="23"/>
-      <c r="D102" s="23"/>
-      <c r="Q102" s="4"/>
-      <c r="R102" s="4"/>
-      <c r="S102" s="4"/>
-      <c r="T102" s="4"/>
-      <c r="U102" s="4"/>
-      <c r="V102" s="4"/>
-      <c r="W102" s="4"/>
-      <c r="X102" s="4"/>
-      <c r="Y102" s="4"/>
-      <c r="Z102" s="4"/>
-      <c r="AA102" s="4"/>
-      <c r="AB102" s="4"/>
-      <c r="AC102" s="4"/>
-      <c r="AD102" s="4"/>
-      <c r="AE102" s="4"/>
-      <c r="AF102" s="4"/>
-      <c r="AG102" s="4"/>
-      <c r="AH102" s="4"/>
-      <c r="AI102" s="4"/>
-      <c r="AJ102" s="4"/>
-      <c r="AK102" s="4"/>
-      <c r="AL102" s="4"/>
-      <c r="AM102" s="4"/>
-      <c r="AN102" s="4"/>
-      <c r="AO102" s="4"/>
-      <c r="AP102" s="4"/>
-      <c r="AQ102" s="4"/>
-      <c r="AR102" s="4"/>
-      <c r="AS102" s="4"/>
-      <c r="AT102" s="4"/>
-      <c r="AU102" s="4"/>
-      <c r="AV102" s="4"/>
-      <c r="AW102" s="4"/>
-      <c r="AX102" s="4"/>
-      <c r="AY102" s="4"/>
-      <c r="AZ102" s="4"/>
-      <c r="BA102" s="4"/>
-      <c r="BB102" s="4"/>
-      <c r="BC102" s="4"/>
-      <c r="BD102" s="4"/>
-      <c r="BE102" s="4"/>
-      <c r="BF102" s="4"/>
-      <c r="BG102" s="4"/>
-      <c r="BH102" s="4"/>
-      <c r="BI102" s="4"/>
-      <c r="BJ102" s="4"/>
-      <c r="BK102" s="4"/>
-      <c r="BL102" s="4"/>
-      <c r="BM102" s="4"/>
-      <c r="BN102" s="4"/>
-      <c r="BO102" s="4"/>
-      <c r="BP102" s="4"/>
-      <c r="BQ102" s="4"/>
-      <c r="BR102" s="4"/>
-      <c r="BS102" s="4"/>
-      <c r="BT102" s="4"/>
-      <c r="BU102" s="4"/>
-      <c r="BV102" s="4"/>
-      <c r="BW102" s="4"/>
-      <c r="BX102" s="4"/>
-      <c r="BY102" s="4"/>
-      <c r="BZ102" s="4"/>
-      <c r="CA102" s="4"/>
-      <c r="CB102" s="4"/>
-      <c r="CC102" s="4"/>
-      <c r="CD102" s="4"/>
-      <c r="CE102" s="4"/>
-      <c r="CF102" s="4"/>
-      <c r="CG102" s="4"/>
-      <c r="CH102" s="4"/>
-      <c r="CI102" s="4"/>
-      <c r="CJ102" s="4"/>
-      <c r="CK102" s="4"/>
-      <c r="CL102" s="4"/>
-      <c r="CM102" s="4"/>
-      <c r="CN102" s="4"/>
-      <c r="CO102" s="4"/>
-      <c r="CP102" s="4"/>
-      <c r="CQ102" s="4"/>
-      <c r="CR102" s="4"/>
-      <c r="CS102" s="4"/>
-      <c r="CT102" s="4"/>
-      <c r="CU102" s="4"/>
-      <c r="CV102" s="4"/>
-      <c r="CW102" s="4"/>
-      <c r="CX102" s="4"/>
-      <c r="CY102" s="4"/>
-      <c r="CZ102" s="4"/>
-      <c r="DA102" s="4"/>
-      <c r="DB102" s="4"/>
-      <c r="DC102" s="4"/>
-      <c r="DD102" s="4"/>
-      <c r="DE102" s="4"/>
-      <c r="DF102" s="4"/>
-      <c r="DG102" s="4"/>
-      <c r="DH102" s="4"/>
-      <c r="DI102" s="4"/>
-      <c r="DJ102" s="4"/>
-      <c r="DK102" s="4"/>
-      <c r="DL102" s="4"/>
-      <c r="DM102" s="4"/>
-      <c r="DN102" s="4"/>
-      <c r="DO102" s="4"/>
-      <c r="DP102" s="4"/>
-      <c r="DQ102" s="4"/>
-      <c r="DR102" s="4"/>
-      <c r="DS102" s="4"/>
-      <c r="DT102" s="4"/>
-      <c r="DU102" s="4"/>
-      <c r="DV102" s="4"/>
-      <c r="DW102" s="4"/>
-      <c r="DX102" s="4"/>
-      <c r="DY102" s="4"/>
-      <c r="DZ102" s="4"/>
-      <c r="EA102" s="4"/>
-      <c r="EB102" s="4"/>
-      <c r="EC102" s="4"/>
-      <c r="ED102" s="4"/>
-      <c r="EE102" s="4"/>
-      <c r="EF102" s="4"/>
-      <c r="EG102" s="4"/>
-      <c r="EH102" s="4"/>
-      <c r="EI102" s="4"/>
-      <c r="EJ102" s="4"/>
-      <c r="EK102" s="4"/>
-      <c r="EL102" s="4"/>
-      <c r="EM102" s="4"/>
-      <c r="EN102" s="4"/>
-      <c r="EO102" s="4"/>
-      <c r="EP102" s="4"/>
-      <c r="EQ102" s="4"/>
-      <c r="ER102" s="4"/>
-      <c r="ES102" s="4"/>
-      <c r="ET102" s="4"/>
-      <c r="EU102" s="4"/>
-      <c r="EV102" s="4"/>
-      <c r="EW102" s="4"/>
-      <c r="EX102" s="4"/>
-      <c r="EY102" s="4"/>
-      <c r="EZ102" s="4"/>
-      <c r="FA102" s="4"/>
-      <c r="FB102" s="4"/>
-      <c r="FC102" s="4"/>
-      <c r="FD102" s="4"/>
-      <c r="FE102" s="4"/>
-      <c r="FF102" s="4"/>
-      <c r="FG102" s="4"/>
-      <c r="FH102" s="4"/>
-      <c r="FI102" s="4"/>
-      <c r="FJ102" s="4"/>
-      <c r="FK102" s="4"/>
-      <c r="FL102" s="4"/>
-      <c r="FM102" s="4"/>
-      <c r="FN102" s="4"/>
-      <c r="FO102" s="4"/>
-      <c r="FP102" s="4"/>
-      <c r="FQ102" s="4"/>
-      <c r="FR102" s="4"/>
-      <c r="FS102" s="4"/>
-      <c r="FT102" s="4"/>
-      <c r="FU102" s="4"/>
-      <c r="FV102" s="4"/>
-      <c r="FW102" s="4"/>
-      <c r="FX102" s="4"/>
-      <c r="FY102" s="4"/>
-      <c r="FZ102" s="4"/>
-      <c r="GA102" s="4"/>
-      <c r="GB102" s="4"/>
-      <c r="GC102" s="4"/>
-      <c r="GD102" s="4"/>
-      <c r="GE102" s="4"/>
-      <c r="GF102" s="4"/>
-      <c r="GG102" s="4"/>
-      <c r="GH102" s="4"/>
-      <c r="GI102" s="4"/>
-      <c r="GJ102" s="4"/>
-      <c r="GK102" s="4"/>
-      <c r="GL102" s="4"/>
-      <c r="GM102" s="4"/>
-      <c r="GN102" s="4"/>
-      <c r="GO102" s="4"/>
-      <c r="GP102" s="4"/>
-      <c r="GQ102" s="4"/>
-      <c r="GR102" s="4"/>
-      <c r="GS102" s="4"/>
-      <c r="GT102" s="4"/>
-      <c r="GU102" s="4"/>
-      <c r="GV102" s="4"/>
-      <c r="GW102" s="4"/>
-      <c r="GX102" s="4"/>
-      <c r="GY102" s="4"/>
-      <c r="GZ102" s="4"/>
-      <c r="HA102" s="4"/>
-      <c r="HB102" s="4"/>
-      <c r="HC102" s="4"/>
-      <c r="HD102" s="4"/>
-      <c r="HE102" s="4"/>
-      <c r="HF102" s="4"/>
-      <c r="HG102" s="4"/>
-      <c r="HH102" s="4"/>
-      <c r="HI102" s="4"/>
-      <c r="HJ102" s="4"/>
-      <c r="HK102" s="4"/>
-      <c r="HL102" s="4"/>
-      <c r="HM102" s="4"/>
-      <c r="HN102" s="4"/>
-      <c r="HO102" s="4"/>
-      <c r="HP102" s="4"/>
-      <c r="HQ102" s="4"/>
-      <c r="HR102" s="4"/>
-      <c r="HS102" s="4"/>
-      <c r="HT102" s="4"/>
-      <c r="HU102" s="4"/>
-      <c r="HV102" s="4"/>
-      <c r="HW102" s="4"/>
-      <c r="HX102" s="4"/>
-      <c r="HY102" s="4"/>
-      <c r="HZ102" s="4"/>
-      <c r="IA102" s="4"/>
-      <c r="IB102" s="4"/>
-      <c r="IC102" s="4"/>
-      <c r="ID102" s="4"/>
-      <c r="IE102" s="4"/>
-      <c r="IF102" s="4"/>
-      <c r="IG102" s="4"/>
-      <c r="IH102" s="4"/>
-      <c r="II102" s="4"/>
-    </row>
-    <row r="103" spans="1:243">
-      <c r="B103" s="23"/>
-      <c r="C103" s="23"/>
-      <c r="D103" s="23"/>
-    </row>
-    <row r="104" spans="1:243">
-      <c r="A104"/>
-      <c r="B104" s="23"/>
-      <c r="C104" s="23"/>
-      <c r="D104" s="23"/>
-      <c r="H104" s="22"/>
-    </row>
-    <row r="105" spans="1:243">
-      <c r="A105"/>
-      <c r="B105" s="23"/>
-      <c r="C105" s="23"/>
-      <c r="D105" s="23"/>
-    </row>
-    <row r="106" spans="1:243">
-      <c r="B106" s="23"/>
-      <c r="C106" s="23"/>
-      <c r="D106" s="23"/>
-    </row>
-    <row r="107" spans="1:243">
-      <c r="B107" s="23"/>
-      <c r="C107" s="23"/>
-      <c r="D107" s="23"/>
-    </row>
-    <row r="108" spans="1:243">
-      <c r="B108" s="23"/>
-      <c r="C108" s="23"/>
-      <c r="D108" s="23"/>
-    </row>
-    <row r="109" spans="1:243">
-      <c r="B109" s="23"/>
-      <c r="C109" s="23"/>
-      <c r="D109" s="23"/>
-    </row>
-    <row r="113" ht="16.75" customHeight="1"/>
+        <v>790</v>
+      </c>
+      <c r="K105" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="L105" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="M105" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N105" s="6">
+        <v>203</v>
+      </c>
+      <c r="O105" s="6">
+        <v>1494</v>
+      </c>
+      <c r="P105" s="6">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="A106" s="11">
+        <v>46142</v>
+      </c>
+      <c r="B106" s="12">
+        <v>1830</v>
+      </c>
+      <c r="C106" s="12">
+        <v>83</v>
+      </c>
+      <c r="D106" s="12">
+        <v>93</v>
+      </c>
+      <c r="E106" s="12">
+        <v>235</v>
+      </c>
+      <c r="F106" s="12">
+        <v>669</v>
+      </c>
+      <c r="G106" s="12">
+        <v>203</v>
+      </c>
+      <c r="H106" s="12">
+        <v>184</v>
+      </c>
+      <c r="I106" s="12">
+        <v>141</v>
+      </c>
+      <c r="J106" s="12">
+        <v>132</v>
+      </c>
+      <c r="K106" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="L106" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="M106" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="N106" s="12">
+        <v>90</v>
+      </c>
+      <c r="O106" s="12">
+        <v>1486</v>
+      </c>
+      <c r="P106" s="12">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="A107" s="8">
+        <v>46143</v>
+      </c>
+      <c r="B107" s="6">
+        <v>3770</v>
+      </c>
+      <c r="C107" s="6">
+        <v>152</v>
+      </c>
+      <c r="D107" s="6">
+        <v>262</v>
+      </c>
+      <c r="E107" s="6">
+        <v>301</v>
+      </c>
+      <c r="F107" s="6">
+        <v>355</v>
+      </c>
+      <c r="G107" s="6">
+        <v>505</v>
+      </c>
+      <c r="H107" s="6">
+        <v>570</v>
+      </c>
+      <c r="I107" s="6">
+        <v>636</v>
+      </c>
+      <c r="J107" s="6">
+        <v>534</v>
+      </c>
+      <c r="K107" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="L107" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="M107" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N107" s="6">
+        <v>455</v>
+      </c>
+      <c r="O107" s="6">
+        <v>2785</v>
+      </c>
+      <c r="P107" s="6">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="A108" s="8">
+        <v>46144</v>
+      </c>
+      <c r="B108" s="36">
+        <v>4521</v>
+      </c>
+      <c r="C108" s="36">
+        <v>219</v>
+      </c>
+      <c r="D108" s="36">
+        <v>308</v>
+      </c>
+      <c r="E108" s="36">
+        <v>367</v>
+      </c>
+      <c r="F108" s="36">
+        <v>425</v>
+      </c>
+      <c r="G108" s="36">
+        <v>597</v>
+      </c>
+      <c r="H108" s="36">
+        <v>658</v>
+      </c>
+      <c r="I108" s="36">
+        <v>547</v>
+      </c>
+      <c r="J108" s="36">
+        <v>420</v>
+      </c>
+      <c r="K108" s="37">
+        <v>268</v>
+      </c>
+      <c r="L108" s="37">
+        <v>139</v>
+      </c>
+      <c r="M108" s="37">
+        <v>73</v>
+      </c>
+      <c r="N108" s="36">
+        <v>500</v>
+      </c>
+      <c r="O108" s="36">
+        <v>3204</v>
+      </c>
+      <c r="P108" s="36">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="A109" s="8">
+        <v>46145</v>
+      </c>
+      <c r="B109" s="6">
+        <v>1208</v>
+      </c>
+      <c r="C109" s="6">
+        <v>54</v>
+      </c>
+      <c r="D109" s="6">
+        <v>66</v>
+      </c>
+      <c r="E109" s="6">
+        <v>80</v>
+      </c>
+      <c r="F109" s="6">
+        <v>85</v>
+      </c>
+      <c r="G109" s="6">
+        <v>122</v>
+      </c>
+      <c r="H109" s="6">
+        <v>211</v>
+      </c>
+      <c r="I109" s="6">
+        <v>231</v>
+      </c>
+      <c r="J109" s="6">
+        <v>202</v>
+      </c>
+      <c r="K109" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="L109" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="M109" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N109" s="6">
+        <v>157</v>
+      </c>
+      <c r="O109" s="6">
+        <v>818</v>
+      </c>
+      <c r="P109" s="6">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="A110" s="8">
+        <v>46147</v>
+      </c>
+      <c r="B110" s="36">
+        <v>11381</v>
+      </c>
+      <c r="C110" s="36">
+        <v>1083</v>
+      </c>
+      <c r="D110" s="36">
+        <v>1633</v>
+      </c>
+      <c r="E110" s="36">
+        <v>1630</v>
+      </c>
+      <c r="F110" s="36">
+        <v>1521</v>
+      </c>
+      <c r="G110" s="36">
+        <v>1537</v>
+      </c>
+      <c r="H110" s="36">
+        <v>1425</v>
+      </c>
+      <c r="I110" s="36">
+        <v>1151</v>
+      </c>
+      <c r="J110" s="36">
+        <v>826</v>
+      </c>
+      <c r="K110" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="L110" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="M110" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N110" s="36">
+        <v>575</v>
+      </c>
+      <c r="O110" s="36">
+        <v>9160</v>
+      </c>
+      <c r="P110" s="36">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="A111" s="8">
+        <v>46148</v>
+      </c>
+      <c r="B111" s="6">
+        <v>1704</v>
+      </c>
+      <c r="C111" s="6">
+        <v>45</v>
+      </c>
+      <c r="D111" s="6">
+        <v>103</v>
+      </c>
+      <c r="E111" s="6">
+        <v>181</v>
+      </c>
+      <c r="F111" s="6">
+        <v>768</v>
+      </c>
+      <c r="G111" s="6">
+        <v>134</v>
+      </c>
+      <c r="H111" s="6">
+        <v>110</v>
+      </c>
+      <c r="I111" s="6">
+        <v>143</v>
+      </c>
+      <c r="J111" s="6">
+        <v>156</v>
+      </c>
+      <c r="K111" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="L111" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="M111" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N111" s="6">
+        <v>64</v>
+      </c>
+      <c r="O111" s="6">
+        <v>1406</v>
+      </c>
+      <c r="P111" s="6">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="A112" s="8">
+        <v>46149</v>
+      </c>
+      <c r="B112" s="6">
+        <v>1516</v>
+      </c>
+      <c r="C112" s="6">
+        <v>131</v>
+      </c>
+      <c r="D112" s="6">
+        <v>94</v>
+      </c>
+      <c r="E112" s="6">
+        <v>144</v>
+      </c>
+      <c r="F112" s="6">
+        <v>655</v>
+      </c>
+      <c r="G112" s="6">
+        <v>243</v>
+      </c>
+      <c r="H112" s="6">
+        <v>61</v>
+      </c>
+      <c r="I112" s="6">
+        <v>30</v>
+      </c>
+      <c r="J112" s="6">
+        <v>22</v>
+      </c>
+      <c r="K112" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="L112" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="M112" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N112" s="6">
+        <v>136</v>
+      </c>
+      <c r="O112" s="6">
+        <v>1200</v>
+      </c>
+      <c r="P112" s="6">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="113" spans="1:243" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="A113" s="8">
+        <v>46150</v>
+      </c>
+      <c r="B113" s="6">
+        <v>1913</v>
+      </c>
+      <c r="C113" s="6">
+        <v>72</v>
+      </c>
+      <c r="D113" s="6">
+        <v>137</v>
+      </c>
+      <c r="E113" s="6">
+        <v>208</v>
+      </c>
+      <c r="F113" s="6">
+        <v>729</v>
+      </c>
+      <c r="G113" s="6">
+        <v>196</v>
+      </c>
+      <c r="H113" s="6">
+        <v>172</v>
+      </c>
+      <c r="I113" s="6">
+        <v>150</v>
+      </c>
+      <c r="J113" s="6">
+        <v>164</v>
+      </c>
+      <c r="K113" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="L113" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="M113" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N113" s="6">
+        <v>85</v>
+      </c>
+      <c r="O113" s="6">
+        <v>1556</v>
+      </c>
+      <c r="P113" s="6">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="114" spans="1:243" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="A114" s="39">
+        <v>46151</v>
+      </c>
+      <c r="B114" s="6">
+        <v>4829</v>
+      </c>
+      <c r="C114" s="6">
+        <v>227</v>
+      </c>
+      <c r="D114" s="6">
+        <v>183</v>
+      </c>
+      <c r="E114" s="6">
+        <v>252</v>
+      </c>
+      <c r="F114" s="6">
+        <v>310</v>
+      </c>
+      <c r="G114" s="6">
+        <v>521</v>
+      </c>
+      <c r="H114" s="6">
+        <v>623</v>
+      </c>
+      <c r="I114" s="6">
+        <v>774</v>
+      </c>
+      <c r="J114" s="6">
+        <v>581</v>
+      </c>
+      <c r="K114" s="6">
+        <v>397</v>
+      </c>
+      <c r="L114" s="6">
+        <v>245</v>
+      </c>
+      <c r="M114" s="6">
+        <v>208</v>
+      </c>
+      <c r="N114" s="6">
+        <v>508</v>
+      </c>
+      <c r="O114" s="6">
+        <v>3417</v>
+      </c>
+      <c r="P114" s="6">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="115" spans="1:243" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="A115" s="39">
+        <v>46152</v>
+      </c>
+      <c r="B115" s="6">
+        <v>3400</v>
+      </c>
+      <c r="C115" s="6">
+        <v>242</v>
+      </c>
+      <c r="D115" s="6">
+        <v>225</v>
+      </c>
+      <c r="E115" s="6">
+        <v>297</v>
+      </c>
+      <c r="F115" s="6">
+        <v>384</v>
+      </c>
+      <c r="G115" s="6">
+        <v>527</v>
+      </c>
+      <c r="H115" s="6">
+        <v>590</v>
+      </c>
+      <c r="I115" s="6">
+        <v>518</v>
+      </c>
+      <c r="J115" s="6">
+        <v>483</v>
+      </c>
+      <c r="K115" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="L115" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="M115" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="N115" s="6">
+        <v>134</v>
+      </c>
+      <c r="O115" s="6">
+        <v>2546</v>
+      </c>
+      <c r="P115" s="6">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="116" spans="1:243" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="A116" s="39">
+        <v>46154</v>
+      </c>
+      <c r="B116" s="36">
+        <v>1660</v>
+      </c>
+      <c r="C116" s="36">
+        <v>78</v>
+      </c>
+      <c r="D116" s="36">
+        <v>81</v>
+      </c>
+      <c r="E116" s="36">
+        <v>131</v>
+      </c>
+      <c r="F116" s="36">
+        <v>736</v>
+      </c>
+      <c r="G116" s="36">
+        <v>152</v>
+      </c>
+      <c r="H116" s="36">
+        <v>148</v>
+      </c>
+      <c r="I116" s="36">
+        <v>113</v>
+      </c>
+      <c r="J116" s="36">
+        <v>133</v>
+      </c>
+      <c r="K116" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="L116" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="M116" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N116" s="37">
+        <v>88</v>
+      </c>
+      <c r="O116" s="36">
+        <v>1363</v>
+      </c>
+      <c r="P116" s="36">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="117" spans="1:243" s="4" customFormat="1" ht="15" customHeight="1">
+      <c r="A117" s="35"/>
+      <c r="B117" s="35">
+        <f>SUM(B2:B116)</f>
+        <v>177490</v>
+      </c>
+      <c r="C117" s="35">
+        <f>SUM(C2:C116)</f>
+        <v>10054</v>
+      </c>
+      <c r="D117" s="35">
+        <f t="shared" ref="D117:P117" si="2">SUM(D2:D116)</f>
+        <v>11963</v>
+      </c>
+      <c r="E117" s="35">
+        <f t="shared" si="2"/>
+        <v>15883</v>
+      </c>
+      <c r="F117" s="35">
+        <f t="shared" si="2"/>
+        <v>33842</v>
+      </c>
+      <c r="G117" s="35">
+        <f t="shared" si="2"/>
+        <v>23628</v>
+      </c>
+      <c r="H117" s="35">
+        <f t="shared" si="2"/>
+        <v>23503</v>
+      </c>
+      <c r="I117" s="35">
+        <f t="shared" si="2"/>
+        <v>23108</v>
+      </c>
+      <c r="J117" s="35">
+        <f t="shared" si="2"/>
+        <v>18506</v>
+      </c>
+      <c r="K117" s="35">
+        <f t="shared" si="2"/>
+        <v>4265</v>
+      </c>
+      <c r="L117" s="35">
+        <f t="shared" si="2"/>
+        <v>2159</v>
+      </c>
+      <c r="M117" s="35">
+        <f t="shared" si="2"/>
+        <v>1310</v>
+      </c>
+      <c r="N117" s="35">
+        <f t="shared" si="2"/>
+        <v>12017</v>
+      </c>
+      <c r="O117" s="35">
+        <f>SUM(O2:O116)</f>
+        <v>126057</v>
+      </c>
+      <c r="P117" s="35">
+        <f t="shared" si="2"/>
+        <v>39416</v>
+      </c>
+    </row>
+    <row r="118" spans="1:243">
+      <c r="A118" s="25"/>
+    </row>
+    <row r="119" spans="1:243">
+      <c r="A119" s="4"/>
+      <c r="C119" s="4"/>
+      <c r="D119" s="4"/>
+      <c r="E119" s="4"/>
+      <c r="F119" s="4"/>
+      <c r="G119" s="4"/>
+      <c r="H119" s="4"/>
+      <c r="I119" s="4"/>
+      <c r="J119" s="4"/>
+      <c r="N119" s="4"/>
+      <c r="Q119" s="4"/>
+      <c r="R119" s="4"/>
+      <c r="S119" s="4"/>
+      <c r="T119" s="4"/>
+      <c r="U119" s="4"/>
+      <c r="V119" s="4"/>
+      <c r="W119" s="4"/>
+      <c r="X119" s="4"/>
+      <c r="Y119" s="4"/>
+      <c r="Z119" s="4"/>
+      <c r="AA119" s="4"/>
+      <c r="AB119" s="4"/>
+      <c r="AC119" s="4"/>
+      <c r="AD119" s="4"/>
+      <c r="AE119" s="4"/>
+      <c r="AF119" s="4"/>
+      <c r="AG119" s="4"/>
+      <c r="AH119" s="4"/>
+      <c r="AI119" s="4"/>
+      <c r="AJ119" s="4"/>
+      <c r="AK119" s="4"/>
+      <c r="AL119" s="4"/>
+      <c r="AM119" s="4"/>
+      <c r="AN119" s="4"/>
+      <c r="AO119" s="4"/>
+      <c r="AP119" s="4"/>
+      <c r="AQ119" s="4"/>
+      <c r="AR119" s="4"/>
+      <c r="AS119" s="4"/>
+      <c r="AT119" s="4"/>
+      <c r="AU119" s="4"/>
+      <c r="AV119" s="4"/>
+      <c r="AW119" s="4"/>
+      <c r="AX119" s="4"/>
+      <c r="AY119" s="4"/>
+      <c r="AZ119" s="4"/>
+      <c r="BA119" s="4"/>
+      <c r="BB119" s="4"/>
+      <c r="BC119" s="4"/>
+      <c r="BD119" s="4"/>
+      <c r="BE119" s="4"/>
+      <c r="BF119" s="4"/>
+      <c r="BG119" s="4"/>
+      <c r="BH119" s="4"/>
+      <c r="BI119" s="4"/>
+      <c r="BJ119" s="4"/>
+      <c r="BK119" s="4"/>
+      <c r="BL119" s="4"/>
+      <c r="BM119" s="4"/>
+      <c r="BN119" s="4"/>
+      <c r="BO119" s="4"/>
+      <c r="BP119" s="4"/>
+      <c r="BQ119" s="4"/>
+      <c r="BR119" s="4"/>
+      <c r="BS119" s="4"/>
+      <c r="BT119" s="4"/>
+      <c r="BU119" s="4"/>
+      <c r="BV119" s="4"/>
+      <c r="BW119" s="4"/>
+      <c r="BX119" s="4"/>
+      <c r="BY119" s="4"/>
+      <c r="BZ119" s="4"/>
+      <c r="CA119" s="4"/>
+      <c r="CB119" s="4"/>
+      <c r="CC119" s="4"/>
+      <c r="CD119" s="4"/>
+      <c r="CE119" s="4"/>
+      <c r="CF119" s="4"/>
+      <c r="CG119" s="4"/>
+      <c r="CH119" s="4"/>
+      <c r="CI119" s="4"/>
+      <c r="CJ119" s="4"/>
+      <c r="CK119" s="4"/>
+      <c r="CL119" s="4"/>
+      <c r="CM119" s="4"/>
+      <c r="CN119" s="4"/>
+      <c r="CO119" s="4"/>
+      <c r="CP119" s="4"/>
+      <c r="CQ119" s="4"/>
+      <c r="CR119" s="4"/>
+      <c r="CS119" s="4"/>
+      <c r="CT119" s="4"/>
+      <c r="CU119" s="4"/>
+      <c r="CV119" s="4"/>
+      <c r="CW119" s="4"/>
+      <c r="CX119" s="4"/>
+      <c r="CY119" s="4"/>
+      <c r="CZ119" s="4"/>
+      <c r="DA119" s="4"/>
+      <c r="DB119" s="4"/>
+      <c r="DC119" s="4"/>
+      <c r="DD119" s="4"/>
+      <c r="DE119" s="4"/>
+      <c r="DF119" s="4"/>
+      <c r="DG119" s="4"/>
+      <c r="DH119" s="4"/>
+      <c r="DI119" s="4"/>
+      <c r="DJ119" s="4"/>
+      <c r="DK119" s="4"/>
+      <c r="DL119" s="4"/>
+      <c r="DM119" s="4"/>
+      <c r="DN119" s="4"/>
+      <c r="DO119" s="4"/>
+      <c r="DP119" s="4"/>
+      <c r="DQ119" s="4"/>
+      <c r="DR119" s="4"/>
+      <c r="DS119" s="4"/>
+      <c r="DT119" s="4"/>
+      <c r="DU119" s="4"/>
+      <c r="DV119" s="4"/>
+      <c r="DW119" s="4"/>
+      <c r="DX119" s="4"/>
+      <c r="DY119" s="4"/>
+      <c r="DZ119" s="4"/>
+      <c r="EA119" s="4"/>
+      <c r="EB119" s="4"/>
+      <c r="EC119" s="4"/>
+      <c r="ED119" s="4"/>
+      <c r="EE119" s="4"/>
+      <c r="EF119" s="4"/>
+      <c r="EG119" s="4"/>
+      <c r="EH119" s="4"/>
+      <c r="EI119" s="4"/>
+      <c r="EJ119" s="4"/>
+      <c r="EK119" s="4"/>
+      <c r="EL119" s="4"/>
+      <c r="EM119" s="4"/>
+      <c r="EN119" s="4"/>
+      <c r="EO119" s="4"/>
+      <c r="EP119" s="4"/>
+      <c r="EQ119" s="4"/>
+      <c r="ER119" s="4"/>
+      <c r="ES119" s="4"/>
+      <c r="ET119" s="4"/>
+      <c r="EU119" s="4"/>
+      <c r="EV119" s="4"/>
+      <c r="EW119" s="4"/>
+      <c r="EX119" s="4"/>
+      <c r="EY119" s="4"/>
+      <c r="EZ119" s="4"/>
+      <c r="FA119" s="4"/>
+      <c r="FB119" s="4"/>
+      <c r="FC119" s="4"/>
+      <c r="FD119" s="4"/>
+      <c r="FE119" s="4"/>
+      <c r="FF119" s="4"/>
+      <c r="FG119" s="4"/>
+      <c r="FH119" s="4"/>
+      <c r="FI119" s="4"/>
+      <c r="FJ119" s="4"/>
+      <c r="FK119" s="4"/>
+      <c r="FL119" s="4"/>
+      <c r="FM119" s="4"/>
+      <c r="FN119" s="4"/>
+      <c r="FO119" s="4"/>
+      <c r="FP119" s="4"/>
+      <c r="FQ119" s="4"/>
+      <c r="FR119" s="4"/>
+      <c r="FS119" s="4"/>
+      <c r="FT119" s="4"/>
+      <c r="FU119" s="4"/>
+      <c r="FV119" s="4"/>
+      <c r="FW119" s="4"/>
+      <c r="FX119" s="4"/>
+      <c r="FY119" s="4"/>
+      <c r="FZ119" s="4"/>
+      <c r="GA119" s="4"/>
+      <c r="GB119" s="4"/>
+      <c r="GC119" s="4"/>
+      <c r="GD119" s="4"/>
+      <c r="GE119" s="4"/>
+      <c r="GF119" s="4"/>
+      <c r="GG119" s="4"/>
+      <c r="GH119" s="4"/>
+      <c r="GI119" s="4"/>
+      <c r="GJ119" s="4"/>
+      <c r="GK119" s="4"/>
+      <c r="GL119" s="4"/>
+      <c r="GM119" s="4"/>
+      <c r="GN119" s="4"/>
+      <c r="GO119" s="4"/>
+      <c r="GP119" s="4"/>
+      <c r="GQ119" s="4"/>
+      <c r="GR119" s="4"/>
+      <c r="GS119" s="4"/>
+      <c r="GT119" s="4"/>
+      <c r="GU119" s="4"/>
+      <c r="GV119" s="4"/>
+      <c r="GW119" s="4"/>
+      <c r="GX119" s="4"/>
+      <c r="GY119" s="4"/>
+      <c r="GZ119" s="4"/>
+      <c r="HA119" s="4"/>
+      <c r="HB119" s="4"/>
+      <c r="HC119" s="4"/>
+      <c r="HD119" s="4"/>
+      <c r="HE119" s="4"/>
+      <c r="HF119" s="4"/>
+      <c r="HG119" s="4"/>
+      <c r="HH119" s="4"/>
+      <c r="HI119" s="4"/>
+      <c r="HJ119" s="4"/>
+      <c r="HK119" s="4"/>
+      <c r="HL119" s="4"/>
+      <c r="HM119" s="4"/>
+      <c r="HN119" s="4"/>
+      <c r="HO119" s="4"/>
+      <c r="HP119" s="4"/>
+      <c r="HQ119" s="4"/>
+      <c r="HR119" s="4"/>
+      <c r="HS119" s="4"/>
+      <c r="HT119" s="4"/>
+      <c r="HU119" s="4"/>
+      <c r="HV119" s="4"/>
+      <c r="HW119" s="4"/>
+      <c r="HX119" s="4"/>
+      <c r="HY119" s="4"/>
+      <c r="HZ119" s="4"/>
+      <c r="IA119" s="4"/>
+      <c r="IB119" s="4"/>
+      <c r="IC119" s="4"/>
+      <c r="ID119" s="4"/>
+      <c r="IE119" s="4"/>
+      <c r="IF119" s="4"/>
+      <c r="IG119" s="4"/>
+      <c r="IH119" s="4"/>
+      <c r="II119" s="4"/>
+    </row>
+    <row r="120" spans="1:243">
+      <c r="B120" s="23"/>
+      <c r="C120" s="23"/>
+      <c r="D120" s="23"/>
+      <c r="Q120" s="4"/>
+      <c r="R120" s="4"/>
+      <c r="S120" s="4"/>
+      <c r="T120" s="4"/>
+      <c r="U120" s="4"/>
+      <c r="V120" s="4"/>
+      <c r="W120" s="4"/>
+      <c r="X120" s="4"/>
+      <c r="Y120" s="4"/>
+      <c r="Z120" s="4"/>
+      <c r="AA120" s="4"/>
+      <c r="AB120" s="4"/>
+      <c r="AC120" s="4"/>
+      <c r="AD120" s="4"/>
+      <c r="AE120" s="4"/>
+      <c r="AF120" s="4"/>
+      <c r="AG120" s="4"/>
+      <c r="AH120" s="4"/>
+      <c r="AI120" s="4"/>
+      <c r="AJ120" s="4"/>
+      <c r="AK120" s="4"/>
+      <c r="AL120" s="4"/>
+      <c r="AM120" s="4"/>
+      <c r="AN120" s="4"/>
+      <c r="AO120" s="4"/>
+      <c r="AP120" s="4"/>
+      <c r="AQ120" s="4"/>
+      <c r="AR120" s="4"/>
+      <c r="AS120" s="4"/>
+      <c r="AT120" s="4"/>
+      <c r="AU120" s="4"/>
+      <c r="AV120" s="4"/>
+      <c r="AW120" s="4"/>
+      <c r="AX120" s="4"/>
+      <c r="AY120" s="4"/>
+      <c r="AZ120" s="4"/>
+      <c r="BA120" s="4"/>
+      <c r="BB120" s="4"/>
+      <c r="BC120" s="4"/>
+      <c r="BD120" s="4"/>
+      <c r="BE120" s="4"/>
+      <c r="BF120" s="4"/>
+      <c r="BG120" s="4"/>
+      <c r="BH120" s="4"/>
+      <c r="BI120" s="4"/>
+      <c r="BJ120" s="4"/>
+      <c r="BK120" s="4"/>
+      <c r="BL120" s="4"/>
+      <c r="BM120" s="4"/>
+      <c r="BN120" s="4"/>
+      <c r="BO120" s="4"/>
+      <c r="BP120" s="4"/>
+      <c r="BQ120" s="4"/>
+      <c r="BR120" s="4"/>
+      <c r="BS120" s="4"/>
+      <c r="BT120" s="4"/>
+      <c r="BU120" s="4"/>
+      <c r="BV120" s="4"/>
+      <c r="BW120" s="4"/>
+      <c r="BX120" s="4"/>
+      <c r="BY120" s="4"/>
+      <c r="BZ120" s="4"/>
+      <c r="CA120" s="4"/>
+      <c r="CB120" s="4"/>
+      <c r="CC120" s="4"/>
+      <c r="CD120" s="4"/>
+      <c r="CE120" s="4"/>
+      <c r="CF120" s="4"/>
+      <c r="CG120" s="4"/>
+      <c r="CH120" s="4"/>
+      <c r="CI120" s="4"/>
+      <c r="CJ120" s="4"/>
+      <c r="CK120" s="4"/>
+      <c r="CL120" s="4"/>
+      <c r="CM120" s="4"/>
+      <c r="CN120" s="4"/>
+      <c r="CO120" s="4"/>
+      <c r="CP120" s="4"/>
+      <c r="CQ120" s="4"/>
+      <c r="CR120" s="4"/>
+      <c r="CS120" s="4"/>
+      <c r="CT120" s="4"/>
+      <c r="CU120" s="4"/>
+      <c r="CV120" s="4"/>
+      <c r="CW120" s="4"/>
+      <c r="CX120" s="4"/>
+      <c r="CY120" s="4"/>
+      <c r="CZ120" s="4"/>
+      <c r="DA120" s="4"/>
+      <c r="DB120" s="4"/>
+      <c r="DC120" s="4"/>
+      <c r="DD120" s="4"/>
+      <c r="DE120" s="4"/>
+      <c r="DF120" s="4"/>
+      <c r="DG120" s="4"/>
+      <c r="DH120" s="4"/>
+      <c r="DI120" s="4"/>
+      <c r="DJ120" s="4"/>
+      <c r="DK120" s="4"/>
+      <c r="DL120" s="4"/>
+      <c r="DM120" s="4"/>
+      <c r="DN120" s="4"/>
+      <c r="DO120" s="4"/>
+      <c r="DP120" s="4"/>
+      <c r="DQ120" s="4"/>
+      <c r="DR120" s="4"/>
+      <c r="DS120" s="4"/>
+      <c r="DT120" s="4"/>
+      <c r="DU120" s="4"/>
+      <c r="DV120" s="4"/>
+      <c r="DW120" s="4"/>
+      <c r="DX120" s="4"/>
+      <c r="DY120" s="4"/>
+      <c r="DZ120" s="4"/>
+      <c r="EA120" s="4"/>
+      <c r="EB120" s="4"/>
+      <c r="EC120" s="4"/>
+      <c r="ED120" s="4"/>
+      <c r="EE120" s="4"/>
+      <c r="EF120" s="4"/>
+      <c r="EG120" s="4"/>
+      <c r="EH120" s="4"/>
+      <c r="EI120" s="4"/>
+      <c r="EJ120" s="4"/>
+      <c r="EK120" s="4"/>
+      <c r="EL120" s="4"/>
+      <c r="EM120" s="4"/>
+      <c r="EN120" s="4"/>
+      <c r="EO120" s="4"/>
+      <c r="EP120" s="4"/>
+      <c r="EQ120" s="4"/>
+      <c r="ER120" s="4"/>
+      <c r="ES120" s="4"/>
+      <c r="ET120" s="4"/>
+      <c r="EU120" s="4"/>
+      <c r="EV120" s="4"/>
+      <c r="EW120" s="4"/>
+      <c r="EX120" s="4"/>
+      <c r="EY120" s="4"/>
+      <c r="EZ120" s="4"/>
+      <c r="FA120" s="4"/>
+      <c r="FB120" s="4"/>
+      <c r="FC120" s="4"/>
+      <c r="FD120" s="4"/>
+      <c r="FE120" s="4"/>
+      <c r="FF120" s="4"/>
+      <c r="FG120" s="4"/>
+      <c r="FH120" s="4"/>
+      <c r="FI120" s="4"/>
+      <c r="FJ120" s="4"/>
+      <c r="FK120" s="4"/>
+      <c r="FL120" s="4"/>
+      <c r="FM120" s="4"/>
+      <c r="FN120" s="4"/>
+      <c r="FO120" s="4"/>
+      <c r="FP120" s="4"/>
+      <c r="FQ120" s="4"/>
+      <c r="FR120" s="4"/>
+      <c r="FS120" s="4"/>
+      <c r="FT120" s="4"/>
+      <c r="FU120" s="4"/>
+      <c r="FV120" s="4"/>
+      <c r="FW120" s="4"/>
+      <c r="FX120" s="4"/>
+      <c r="FY120" s="4"/>
+      <c r="FZ120" s="4"/>
+      <c r="GA120" s="4"/>
+      <c r="GB120" s="4"/>
+      <c r="GC120" s="4"/>
+      <c r="GD120" s="4"/>
+      <c r="GE120" s="4"/>
+      <c r="GF120" s="4"/>
+      <c r="GG120" s="4"/>
+      <c r="GH120" s="4"/>
+      <c r="GI120" s="4"/>
+      <c r="GJ120" s="4"/>
+      <c r="GK120" s="4"/>
+      <c r="GL120" s="4"/>
+      <c r="GM120" s="4"/>
+      <c r="GN120" s="4"/>
+      <c r="GO120" s="4"/>
+      <c r="GP120" s="4"/>
+      <c r="GQ120" s="4"/>
+      <c r="GR120" s="4"/>
+      <c r="GS120" s="4"/>
+      <c r="GT120" s="4"/>
+      <c r="GU120" s="4"/>
+      <c r="GV120" s="4"/>
+      <c r="GW120" s="4"/>
+      <c r="GX120" s="4"/>
+      <c r="GY120" s="4"/>
+      <c r="GZ120" s="4"/>
+      <c r="HA120" s="4"/>
+      <c r="HB120" s="4"/>
+      <c r="HC120" s="4"/>
+      <c r="HD120" s="4"/>
+      <c r="HE120" s="4"/>
+      <c r="HF120" s="4"/>
+      <c r="HG120" s="4"/>
+      <c r="HH120" s="4"/>
+      <c r="HI120" s="4"/>
+      <c r="HJ120" s="4"/>
+      <c r="HK120" s="4"/>
+      <c r="HL120" s="4"/>
+      <c r="HM120" s="4"/>
+      <c r="HN120" s="4"/>
+      <c r="HO120" s="4"/>
+      <c r="HP120" s="4"/>
+      <c r="HQ120" s="4"/>
+      <c r="HR120" s="4"/>
+      <c r="HS120" s="4"/>
+      <c r="HT120" s="4"/>
+      <c r="HU120" s="4"/>
+      <c r="HV120" s="4"/>
+      <c r="HW120" s="4"/>
+      <c r="HX120" s="4"/>
+      <c r="HY120" s="4"/>
+      <c r="HZ120" s="4"/>
+      <c r="IA120" s="4"/>
+      <c r="IB120" s="4"/>
+      <c r="IC120" s="4"/>
+      <c r="ID120" s="4"/>
+      <c r="IE120" s="4"/>
+      <c r="IF120" s="4"/>
+      <c r="IG120" s="4"/>
+      <c r="IH120" s="4"/>
+      <c r="II120" s="4"/>
+    </row>
+    <row r="121" spans="1:243" ht="17">
+      <c r="B121" s="23"/>
+      <c r="C121" s="23"/>
+      <c r="D121" s="23"/>
+      <c r="L121" s="38"/>
+    </row>
+    <row r="122" spans="1:243">
+      <c r="B122" s="23"/>
+      <c r="C122" s="23"/>
+      <c r="D122" s="23"/>
+      <c r="H122" s="22"/>
+    </row>
+    <row r="123" spans="1:243">
+      <c r="B123" s="23"/>
+      <c r="C123" s="23"/>
+      <c r="D123" s="23"/>
+    </row>
+    <row r="124" spans="1:243">
+      <c r="B124" s="23"/>
+      <c r="C124" s="23"/>
+      <c r="D124" s="23"/>
+    </row>
+    <row r="125" spans="1:243">
+      <c r="B125" s="23"/>
+      <c r="C125" s="23"/>
+      <c r="D125" s="23"/>
+    </row>
+    <row r="126" spans="1:243">
+      <c r="B126" s="23"/>
+      <c r="C126" s="23"/>
+      <c r="D126" s="23"/>
+    </row>
+    <row r="127" spans="1:243">
+      <c r="B127" s="23"/>
+      <c r="C127" s="23"/>
+      <c r="D127" s="23"/>
+    </row>
+    <row r="128" spans="1:243" ht="16.75" customHeight="1"/>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
--- a/reports/excel_base/방문객통계_기준.xlsx
+++ b/reports/excel_base/방문객통계_기준.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kim/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\N210722002\Desktop\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38A6CCA0-2EA5-5B4F-9150-CBEC1191E446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3560528-ED0D-4405-AB0C-91B5E745047A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" tabRatio="426" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="426" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="피플카운트" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="18">
   <si>
     <t>날짜</t>
   </si>
@@ -86,8 +86,49 @@
     <t>-</t>
   </si>
   <si>
-    <t>-</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">후문주차장 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>명</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -97,7 +138,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -143,15 +184,31 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Malgun Gothic"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
       <sz val="8"/>
-      <name val="나눔명조"/>
+      <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Malgun Gothic"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
     </font>
@@ -182,7 +239,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -269,6 +326,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -279,7 +349,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -384,9 +454,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -700,14 +784,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:II128"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15"/>
+  <dimension ref="A1:II198"/>
+  <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20" style="3" customWidth="1"/>
-    <col min="2" max="16" width="15.83203125" customWidth="1"/>
+    <col min="2" max="16" width="15.77734375" customWidth="1"/>
+    <col min="17" max="17" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -756,8 +841,11 @@
       <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" ht="20" customHeight="1">
+      <c r="Q1" s="44" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="19.95" customHeight="1">
       <c r="A2" s="8">
         <v>46018</v>
       </c>
@@ -807,9 +895,9 @@
       <c r="P2" s="6">
         <v>71</v>
       </c>
-      <c r="Q2" s="18"/>
-    </row>
-    <row r="3" spans="1:17" ht="20" customHeight="1">
+      <c r="Q2" s="16"/>
+    </row>
+    <row r="3" spans="1:17" ht="19.95" customHeight="1">
       <c r="A3" s="8">
         <v>46019</v>
       </c>
@@ -859,9 +947,9 @@
       <c r="P3" s="6">
         <v>248</v>
       </c>
-      <c r="Q3" s="18"/>
-    </row>
-    <row r="4" spans="1:17" ht="20" customHeight="1">
+      <c r="Q3" s="16"/>
+    </row>
+    <row r="4" spans="1:17" ht="19.95" customHeight="1">
       <c r="A4" s="8">
         <v>46021</v>
       </c>
@@ -911,9 +999,9 @@
       <c r="P4" s="6">
         <v>102</v>
       </c>
-      <c r="Q4" s="18"/>
-    </row>
-    <row r="5" spans="1:17" ht="20" customHeight="1">
+      <c r="Q4" s="16"/>
+    </row>
+    <row r="5" spans="1:17" ht="19.95" customHeight="1">
       <c r="A5" s="8">
         <v>46022</v>
       </c>
@@ -963,9 +1051,9 @@
       <c r="P5" s="6">
         <v>95</v>
       </c>
-      <c r="Q5" s="18"/>
-    </row>
-    <row r="6" spans="1:17" ht="20" customHeight="1">
+      <c r="Q5" s="16"/>
+    </row>
+    <row r="6" spans="1:17" ht="19.95" customHeight="1">
       <c r="A6" s="8">
         <v>46023</v>
       </c>
@@ -1015,9 +1103,9 @@
       <c r="P6" s="6">
         <v>23</v>
       </c>
-      <c r="Q6" s="18"/>
-    </row>
-    <row r="7" spans="1:17" ht="20" customHeight="1">
+      <c r="Q6" s="16"/>
+    </row>
+    <row r="7" spans="1:17" ht="19.95" customHeight="1">
       <c r="A7" s="8">
         <v>46024</v>
       </c>
@@ -1067,9 +1155,9 @@
       <c r="P7" s="6">
         <v>82</v>
       </c>
-      <c r="Q7" s="18"/>
-    </row>
-    <row r="8" spans="1:17" ht="20" customHeight="1">
+      <c r="Q7" s="16"/>
+    </row>
+    <row r="8" spans="1:17" ht="19.95" customHeight="1">
       <c r="A8" s="8">
         <v>46025</v>
       </c>
@@ -1119,9 +1207,9 @@
       <c r="P8" s="6">
         <v>196</v>
       </c>
-      <c r="Q8" s="18"/>
-    </row>
-    <row r="9" spans="1:17" ht="20" customHeight="1">
+      <c r="Q8" s="16"/>
+    </row>
+    <row r="9" spans="1:17" ht="19.95" customHeight="1">
       <c r="A9" s="8">
         <v>46026</v>
       </c>
@@ -1171,9 +1259,9 @@
       <c r="P9" s="6">
         <v>219</v>
       </c>
-      <c r="Q9" s="18"/>
-    </row>
-    <row r="10" spans="1:17" ht="20" customHeight="1">
+      <c r="Q9" s="16"/>
+    </row>
+    <row r="10" spans="1:17" ht="19.95" customHeight="1">
       <c r="A10" s="8">
         <v>46028</v>
       </c>
@@ -1222,9 +1310,9 @@
       <c r="P10" s="6">
         <v>84</v>
       </c>
-      <c r="Q10" s="18"/>
-    </row>
-    <row r="11" spans="1:17" ht="20" customHeight="1">
+      <c r="Q10" s="16"/>
+    </row>
+    <row r="11" spans="1:17" ht="19.95" customHeight="1">
       <c r="A11" s="8">
         <v>46029</v>
       </c>
@@ -1273,9 +1361,9 @@
       <c r="P11" s="6">
         <v>108</v>
       </c>
-      <c r="Q11" s="18"/>
-    </row>
-    <row r="12" spans="1:17" ht="20" customHeight="1">
+      <c r="Q11" s="16"/>
+    </row>
+    <row r="12" spans="1:17" ht="19.95" customHeight="1">
       <c r="A12" s="8">
         <v>46030</v>
       </c>
@@ -1324,9 +1412,9 @@
       <c r="P12" s="6">
         <v>80</v>
       </c>
-      <c r="Q12" s="18"/>
-    </row>
-    <row r="13" spans="1:17" ht="20" customHeight="1">
+      <c r="Q12" s="16"/>
+    </row>
+    <row r="13" spans="1:17" ht="19.95" customHeight="1">
       <c r="A13" s="8">
         <v>46031</v>
       </c>
@@ -1375,9 +1463,9 @@
       <c r="P13" s="6">
         <v>84</v>
       </c>
-      <c r="Q13" s="18"/>
-    </row>
-    <row r="14" spans="1:17" ht="20" customHeight="1">
+      <c r="Q13" s="16"/>
+    </row>
+    <row r="14" spans="1:17" ht="19.95" customHeight="1">
       <c r="A14" s="8">
         <v>46032</v>
       </c>
@@ -1426,9 +1514,9 @@
       <c r="P14" s="6">
         <v>90</v>
       </c>
-      <c r="Q14" s="18"/>
-    </row>
-    <row r="15" spans="1:17" ht="20" customHeight="1">
+      <c r="Q14" s="16"/>
+    </row>
+    <row r="15" spans="1:17" ht="19.95" customHeight="1">
       <c r="A15" s="8">
         <v>46033</v>
       </c>
@@ -1477,9 +1565,9 @@
       <c r="P15" s="6">
         <v>121</v>
       </c>
-      <c r="Q15" s="18"/>
-    </row>
-    <row r="16" spans="1:17" ht="20" customHeight="1">
+      <c r="Q15" s="16"/>
+    </row>
+    <row r="16" spans="1:17" ht="19.95" customHeight="1">
       <c r="A16" s="8">
         <v>46035</v>
       </c>
@@ -1528,9 +1616,9 @@
       <c r="P16" s="6">
         <v>203</v>
       </c>
-      <c r="Q16" s="18"/>
-    </row>
-    <row r="17" spans="1:17" ht="20" customHeight="1">
+      <c r="Q16" s="16"/>
+    </row>
+    <row r="17" spans="1:17" ht="19.95" customHeight="1">
       <c r="A17" s="8">
         <v>46036</v>
       </c>
@@ -1579,9 +1667,9 @@
       <c r="P17" s="6">
         <v>85</v>
       </c>
-      <c r="Q17" s="18"/>
-    </row>
-    <row r="18" spans="1:17" ht="20" customHeight="1">
+      <c r="Q17" s="16"/>
+    </row>
+    <row r="18" spans="1:17" ht="19.95" customHeight="1">
       <c r="A18" s="8">
         <v>46037</v>
       </c>
@@ -1630,9 +1718,9 @@
       <c r="P18" s="6">
         <v>82</v>
       </c>
-      <c r="Q18" s="18"/>
-    </row>
-    <row r="19" spans="1:17" ht="20" customHeight="1">
+      <c r="Q18" s="16"/>
+    </row>
+    <row r="19" spans="1:17" ht="19.95" customHeight="1">
       <c r="A19" s="8">
         <v>46038</v>
       </c>
@@ -1681,9 +1769,9 @@
       <c r="P19" s="6">
         <v>110</v>
       </c>
-      <c r="Q19" s="18"/>
-    </row>
-    <row r="20" spans="1:17" ht="20" customHeight="1">
+      <c r="Q19" s="16"/>
+    </row>
+    <row r="20" spans="1:17" ht="19.95" customHeight="1">
       <c r="A20" s="8">
         <v>46039</v>
       </c>
@@ -1732,9 +1820,9 @@
       <c r="P20" s="6">
         <v>354</v>
       </c>
-      <c r="Q20" s="18"/>
-    </row>
-    <row r="21" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q20" s="16"/>
+    </row>
+    <row r="21" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A21" s="8">
         <v>46040</v>
       </c>
@@ -1783,9 +1871,9 @@
       <c r="P21" s="6">
         <v>249</v>
       </c>
-      <c r="Q21" s="18"/>
-    </row>
-    <row r="22" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q21" s="16"/>
+    </row>
+    <row r="22" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A22" s="8">
         <v>46042</v>
       </c>
@@ -1834,9 +1922,9 @@
       <c r="P22" s="6">
         <v>71</v>
       </c>
-      <c r="Q22" s="18"/>
-    </row>
-    <row r="23" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q22" s="16"/>
+    </row>
+    <row r="23" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A23" s="8">
         <v>46043</v>
       </c>
@@ -1885,9 +1973,9 @@
       <c r="P23" s="6">
         <v>48</v>
       </c>
-      <c r="Q23" s="18"/>
-    </row>
-    <row r="24" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q23" s="16"/>
+    </row>
+    <row r="24" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A24" s="8">
         <v>46044</v>
       </c>
@@ -1936,9 +2024,9 @@
       <c r="P24" s="6">
         <v>49</v>
       </c>
-      <c r="Q24" s="18"/>
-    </row>
-    <row r="25" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q24" s="16"/>
+    </row>
+    <row r="25" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A25" s="11">
         <v>46045</v>
       </c>
@@ -1987,9 +2075,9 @@
       <c r="P25" s="12">
         <v>97</v>
       </c>
-      <c r="Q25" s="18"/>
-    </row>
-    <row r="26" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q25" s="16"/>
+    </row>
+    <row r="26" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A26" s="8">
         <v>46046</v>
       </c>
@@ -2038,9 +2126,9 @@
       <c r="P26" s="6">
         <v>131</v>
       </c>
-      <c r="Q26" s="18"/>
-    </row>
-    <row r="27" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q26" s="16"/>
+    </row>
+    <row r="27" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A27" s="8">
         <v>46047</v>
       </c>
@@ -2089,9 +2177,9 @@
       <c r="P27" s="6">
         <v>125</v>
       </c>
-      <c r="Q27" s="18"/>
-    </row>
-    <row r="28" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q27" s="16"/>
+    </row>
+    <row r="28" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A28" s="8">
         <v>46049</v>
       </c>
@@ -2140,9 +2228,9 @@
       <c r="P28" s="6">
         <v>124</v>
       </c>
-      <c r="Q28" s="18"/>
-    </row>
-    <row r="29" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q28" s="16"/>
+    </row>
+    <row r="29" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A29" s="8">
         <v>46050</v>
       </c>
@@ -2191,9 +2279,9 @@
       <c r="P29" s="6">
         <v>114</v>
       </c>
-      <c r="Q29" s="18"/>
-    </row>
-    <row r="30" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q29" s="16"/>
+    </row>
+    <row r="30" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A30" s="8">
         <v>46051</v>
       </c>
@@ -2242,9 +2330,9 @@
       <c r="P30" s="6">
         <v>71</v>
       </c>
-      <c r="Q30" s="18"/>
-    </row>
-    <row r="31" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q30" s="16"/>
+    </row>
+    <row r="31" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A31" s="8">
         <v>46052</v>
       </c>
@@ -2293,9 +2381,9 @@
       <c r="P31" s="6">
         <v>52</v>
       </c>
-      <c r="Q31" s="18"/>
-    </row>
-    <row r="32" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q31" s="16"/>
+    </row>
+    <row r="32" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A32" s="8">
         <v>46053</v>
       </c>
@@ -2344,9 +2432,9 @@
       <c r="P32" s="6">
         <v>189</v>
       </c>
-      <c r="Q32" s="18"/>
-    </row>
-    <row r="33" spans="1:17" s="19" customFormat="1" ht="20" customHeight="1">
+      <c r="Q32" s="16"/>
+    </row>
+    <row r="33" spans="1:17" s="19" customFormat="1" ht="19.95" customHeight="1">
       <c r="A33" s="15">
         <v>46054</v>
       </c>
@@ -2395,9 +2483,9 @@
       <c r="P33" s="16">
         <v>300</v>
       </c>
-      <c r="Q33" s="18"/>
-    </row>
-    <row r="34" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q33" s="16"/>
+    </row>
+    <row r="34" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A34" s="8">
         <v>46056</v>
       </c>
@@ -2446,9 +2534,9 @@
       <c r="P34" s="6">
         <v>237</v>
       </c>
-      <c r="Q34" s="18"/>
-    </row>
-    <row r="35" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q34" s="16"/>
+    </row>
+    <row r="35" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A35" s="8">
         <v>46057</v>
       </c>
@@ -2497,9 +2585,9 @@
       <c r="P35" s="6">
         <v>132</v>
       </c>
-      <c r="Q35" s="18"/>
-    </row>
-    <row r="36" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q35" s="16"/>
+    </row>
+    <row r="36" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A36" s="8">
         <v>46058</v>
       </c>
@@ -2548,9 +2636,9 @@
       <c r="P36" s="6">
         <v>199</v>
       </c>
-      <c r="Q36" s="18"/>
-    </row>
-    <row r="37" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q36" s="16"/>
+    </row>
+    <row r="37" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A37" s="8">
         <v>46059</v>
       </c>
@@ -2599,9 +2687,9 @@
       <c r="P37" s="6">
         <v>94</v>
       </c>
-      <c r="Q37" s="18"/>
-    </row>
-    <row r="38" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q37" s="16"/>
+    </row>
+    <row r="38" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A38" s="8">
         <v>46060</v>
       </c>
@@ -2650,9 +2738,9 @@
       <c r="P38" s="6">
         <v>205</v>
       </c>
-      <c r="Q38" s="18"/>
-    </row>
-    <row r="39" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q38" s="16"/>
+    </row>
+    <row r="39" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A39" s="8">
         <v>46061</v>
       </c>
@@ -2701,9 +2789,9 @@
       <c r="P39" s="6">
         <v>237</v>
       </c>
-      <c r="Q39" s="18"/>
-    </row>
-    <row r="40" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q39" s="16"/>
+    </row>
+    <row r="40" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A40" s="8">
         <v>46063</v>
       </c>
@@ -2752,9 +2840,9 @@
       <c r="P40" s="6">
         <v>218</v>
       </c>
-      <c r="Q40" s="18"/>
-    </row>
-    <row r="41" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q40" s="16"/>
+    </row>
+    <row r="41" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A41" s="8">
         <v>46064</v>
       </c>
@@ -2803,9 +2891,9 @@
       <c r="P41" s="6">
         <v>152</v>
       </c>
-      <c r="Q41" s="18"/>
-    </row>
-    <row r="42" spans="1:17" s="19" customFormat="1" ht="20" customHeight="1">
+      <c r="Q41" s="16"/>
+    </row>
+    <row r="42" spans="1:17" s="19" customFormat="1" ht="19.95" customHeight="1">
       <c r="A42" s="15">
         <v>46065</v>
       </c>
@@ -2854,9 +2942,9 @@
       <c r="P42" s="16">
         <v>99</v>
       </c>
-      <c r="Q42" s="18"/>
-    </row>
-    <row r="43" spans="1:17" s="19" customFormat="1" ht="20" customHeight="1">
+      <c r="Q42" s="16"/>
+    </row>
+    <row r="43" spans="1:17" s="19" customFormat="1" ht="19.95" customHeight="1">
       <c r="A43" s="15">
         <v>46066</v>
       </c>
@@ -2905,9 +2993,9 @@
       <c r="P43" s="16">
         <v>127</v>
       </c>
-      <c r="Q43" s="18"/>
-    </row>
-    <row r="44" spans="1:17" s="19" customFormat="1" ht="20" customHeight="1">
+      <c r="Q43" s="16"/>
+    </row>
+    <row r="44" spans="1:17" s="19" customFormat="1" ht="19.95" customHeight="1">
       <c r="A44" s="15">
         <v>46067</v>
       </c>
@@ -2956,9 +3044,9 @@
       <c r="P44" s="16">
         <v>362</v>
       </c>
-      <c r="Q44" s="18"/>
-    </row>
-    <row r="45" spans="1:17" s="19" customFormat="1" ht="20" customHeight="1">
+      <c r="Q44" s="16"/>
+    </row>
+    <row r="45" spans="1:17" s="19" customFormat="1" ht="19.95" customHeight="1">
       <c r="A45" s="15">
         <v>46068</v>
       </c>
@@ -3007,9 +3095,9 @@
       <c r="P45" s="16">
         <v>226</v>
       </c>
-      <c r="Q45" s="18"/>
-    </row>
-    <row r="46" spans="1:17" s="19" customFormat="1" ht="20" customHeight="1">
+      <c r="Q45" s="16"/>
+    </row>
+    <row r="46" spans="1:17" s="19" customFormat="1" ht="19.95" customHeight="1">
       <c r="A46" s="15">
         <v>46069</v>
       </c>
@@ -3058,9 +3146,9 @@
       <c r="P46" s="16">
         <v>228</v>
       </c>
-      <c r="Q46" s="18"/>
-    </row>
-    <row r="47" spans="1:17" s="19" customFormat="1" ht="20" customHeight="1">
+      <c r="Q46" s="16"/>
+    </row>
+    <row r="47" spans="1:17" s="19" customFormat="1" ht="19.95" customHeight="1">
       <c r="A47" s="15">
         <v>46071</v>
       </c>
@@ -3109,9 +3197,9 @@
       <c r="P47" s="16">
         <v>300</v>
       </c>
-      <c r="Q47" s="18"/>
-    </row>
-    <row r="48" spans="1:17" s="19" customFormat="1" ht="20" customHeight="1">
+      <c r="Q47" s="16"/>
+    </row>
+    <row r="48" spans="1:17" s="19" customFormat="1" ht="19.95" customHeight="1">
       <c r="A48" s="15">
         <v>46073</v>
       </c>
@@ -3160,9 +3248,9 @@
       <c r="P48" s="16">
         <v>191</v>
       </c>
-      <c r="Q48" s="18"/>
-    </row>
-    <row r="49" spans="1:17" s="19" customFormat="1" ht="20" customHeight="1">
+      <c r="Q48" s="16"/>
+    </row>
+    <row r="49" spans="1:17" s="19" customFormat="1" ht="19.95" customHeight="1">
       <c r="A49" s="15">
         <v>46074</v>
       </c>
@@ -3211,9 +3299,9 @@
       <c r="P49" s="16">
         <v>745</v>
       </c>
-      <c r="Q49" s="18"/>
-    </row>
-    <row r="50" spans="1:17" s="19" customFormat="1" ht="20" customHeight="1">
+      <c r="Q49" s="16"/>
+    </row>
+    <row r="50" spans="1:17" s="19" customFormat="1" ht="19.95" customHeight="1">
       <c r="A50" s="15">
         <v>46075</v>
       </c>
@@ -3262,9 +3350,9 @@
       <c r="P50" s="16">
         <v>172</v>
       </c>
-      <c r="Q50" s="18"/>
-    </row>
-    <row r="51" spans="1:17" s="19" customFormat="1" ht="20" customHeight="1">
+      <c r="Q50" s="16"/>
+    </row>
+    <row r="51" spans="1:17" s="19" customFormat="1" ht="19.95" customHeight="1">
       <c r="A51" s="15">
         <v>46077</v>
       </c>
@@ -3313,9 +3401,9 @@
       <c r="P51" s="16">
         <v>216</v>
       </c>
-      <c r="Q51" s="18"/>
-    </row>
-    <row r="52" spans="1:17" s="19" customFormat="1" ht="20" customHeight="1">
+      <c r="Q51" s="16"/>
+    </row>
+    <row r="52" spans="1:17" s="19" customFormat="1" ht="19.95" customHeight="1">
       <c r="A52" s="15">
         <v>46078</v>
       </c>
@@ -3364,9 +3452,9 @@
       <c r="P52" s="16">
         <v>397</v>
       </c>
-      <c r="Q52" s="18"/>
-    </row>
-    <row r="53" spans="1:17" s="19" customFormat="1" ht="20" customHeight="1">
+      <c r="Q52" s="16"/>
+    </row>
+    <row r="53" spans="1:17" s="19" customFormat="1" ht="19.95" customHeight="1">
       <c r="A53" s="15">
         <v>46079</v>
       </c>
@@ -3415,9 +3503,9 @@
       <c r="P53" s="16">
         <v>395</v>
       </c>
-      <c r="Q53" s="18"/>
-    </row>
-    <row r="54" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q53" s="16"/>
+    </row>
+    <row r="54" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A54" s="8">
         <v>46080</v>
       </c>
@@ -3466,9 +3554,9 @@
       <c r="P54" s="6">
         <v>382</v>
       </c>
-      <c r="Q54" s="18"/>
-    </row>
-    <row r="55" spans="1:17" s="19" customFormat="1" ht="20" customHeight="1">
+      <c r="Q54" s="16"/>
+    </row>
+    <row r="55" spans="1:17" s="19" customFormat="1" ht="19.95" customHeight="1">
       <c r="A55" s="15">
         <v>46081</v>
       </c>
@@ -3517,9 +3605,9 @@
       <c r="P55" s="16">
         <v>955</v>
       </c>
-      <c r="Q55" s="18"/>
-    </row>
-    <row r="56" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q55" s="16"/>
+    </row>
+    <row r="56" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A56" s="8">
         <v>46082</v>
       </c>
@@ -3568,9 +3656,9 @@
       <c r="P56" s="6">
         <v>801</v>
       </c>
-      <c r="Q56" s="18"/>
-    </row>
-    <row r="57" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q56" s="16"/>
+    </row>
+    <row r="57" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A57" s="8">
         <v>46083</v>
       </c>
@@ -3619,9 +3707,9 @@
       <c r="P57" s="6">
         <v>27</v>
       </c>
-      <c r="Q57" s="18"/>
-    </row>
-    <row r="58" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q57" s="16"/>
+    </row>
+    <row r="58" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A58" s="8">
         <v>46085</v>
       </c>
@@ -3670,9 +3758,9 @@
       <c r="P58" s="6">
         <v>139</v>
       </c>
-      <c r="Q58" s="18"/>
-    </row>
-    <row r="59" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q58" s="16"/>
+    </row>
+    <row r="59" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A59" s="8">
         <v>46086</v>
       </c>
@@ -3721,9 +3809,9 @@
       <c r="P59" s="6">
         <v>252</v>
       </c>
-      <c r="Q59" s="18"/>
-    </row>
-    <row r="60" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q59" s="16"/>
+    </row>
+    <row r="60" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A60" s="8">
         <v>46087</v>
       </c>
@@ -3772,9 +3860,9 @@
       <c r="P60" s="6">
         <v>100</v>
       </c>
-      <c r="Q60" s="18"/>
-    </row>
-    <row r="61" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q60" s="16"/>
+    </row>
+    <row r="61" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A61" s="8">
         <v>46088</v>
       </c>
@@ -3823,9 +3911,9 @@
       <c r="P61" s="6">
         <v>678</v>
       </c>
-      <c r="Q61" s="18"/>
-    </row>
-    <row r="62" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q61" s="16"/>
+    </row>
+    <row r="62" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A62" s="8">
         <v>46089</v>
       </c>
@@ -3874,9 +3962,9 @@
       <c r="P62" s="6">
         <v>527</v>
       </c>
-      <c r="Q62" s="18"/>
-    </row>
-    <row r="63" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q62" s="16"/>
+    </row>
+    <row r="63" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A63" s="21">
         <v>46091</v>
       </c>
@@ -3925,9 +4013,9 @@
       <c r="P63" s="6">
         <v>209</v>
       </c>
-      <c r="Q63" s="18"/>
-    </row>
-    <row r="64" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q63" s="16"/>
+    </row>
+    <row r="64" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A64" s="21">
         <v>46092</v>
       </c>
@@ -3976,9 +4064,9 @@
       <c r="P64" s="6">
         <v>122</v>
       </c>
-      <c r="Q64" s="18"/>
-    </row>
-    <row r="65" spans="1:17" s="10" customFormat="1" ht="20" customHeight="1">
+      <c r="Q64" s="16"/>
+    </row>
+    <row r="65" spans="1:17" s="10" customFormat="1" ht="19.95" customHeight="1">
       <c r="A65" s="21">
         <v>46093</v>
       </c>
@@ -4027,9 +4115,9 @@
       <c r="P65" s="6">
         <v>109</v>
       </c>
-      <c r="Q65" s="18"/>
-    </row>
-    <row r="66" spans="1:17" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q65" s="16"/>
+    </row>
+    <row r="66" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A66" s="21">
         <v>46094</v>
       </c>
@@ -4078,8 +4166,9 @@
       <c r="P66" s="16">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:17" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q66" s="16"/>
+    </row>
+    <row r="67" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A67" s="21">
         <v>46095</v>
       </c>
@@ -4128,8 +4217,9 @@
       <c r="P67" s="16">
         <v>1497</v>
       </c>
-    </row>
-    <row r="68" spans="1:17" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q67" s="16"/>
+    </row>
+    <row r="68" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A68" s="21">
         <v>46096</v>
       </c>
@@ -4178,8 +4268,9 @@
       <c r="P68" s="16">
         <v>1138</v>
       </c>
-    </row>
-    <row r="69" spans="1:17" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q68" s="16"/>
+    </row>
+    <row r="69" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A69" s="21">
         <v>46098</v>
       </c>
@@ -4228,8 +4319,9 @@
       <c r="P69" s="16">
         <v>560</v>
       </c>
-    </row>
-    <row r="70" spans="1:17" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q69" s="16"/>
+    </row>
+    <row r="70" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A70" s="21">
         <v>46099</v>
       </c>
@@ -4278,8 +4370,9 @@
       <c r="P70" s="16">
         <v>54</v>
       </c>
-    </row>
-    <row r="71" spans="1:17" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q70" s="16"/>
+    </row>
+    <row r="71" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A71" s="21">
         <v>46100</v>
       </c>
@@ -4328,8 +4421,9 @@
       <c r="P71" s="16">
         <v>403</v>
       </c>
-    </row>
-    <row r="72" spans="1:17" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q71" s="16"/>
+    </row>
+    <row r="72" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A72" s="21">
         <v>46101</v>
       </c>
@@ -4378,8 +4472,9 @@
       <c r="P72" s="16">
         <v>395</v>
       </c>
-    </row>
-    <row r="73" spans="1:17" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q72" s="16"/>
+    </row>
+    <row r="73" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A73" s="21">
         <v>46102</v>
       </c>
@@ -4428,8 +4523,9 @@
       <c r="P73" s="16">
         <v>793</v>
       </c>
-    </row>
-    <row r="74" spans="1:17" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q73" s="16"/>
+    </row>
+    <row r="74" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A74" s="21">
         <v>46103</v>
       </c>
@@ -4478,8 +4574,9 @@
       <c r="P74" s="16">
         <v>568</v>
       </c>
-    </row>
-    <row r="75" spans="1:17" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q74" s="16"/>
+    </row>
+    <row r="75" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A75" s="21">
         <v>46106</v>
       </c>
@@ -4528,8 +4625,9 @@
       <c r="P75" s="16">
         <v>580</v>
       </c>
-    </row>
-    <row r="76" spans="1:17" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q75" s="16"/>
+    </row>
+    <row r="76" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A76" s="21">
         <v>46107</v>
       </c>
@@ -4578,8 +4676,9 @@
       <c r="P76" s="16">
         <v>572</v>
       </c>
-    </row>
-    <row r="77" spans="1:17" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q76" s="16"/>
+    </row>
+    <row r="77" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A77" s="21">
         <v>46108</v>
       </c>
@@ -4626,8 +4725,9 @@
       <c r="P77" s="16">
         <v>473</v>
       </c>
-    </row>
-    <row r="78" spans="1:17" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q77" s="16"/>
+    </row>
+    <row r="78" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A78" s="21">
         <v>46109</v>
       </c>
@@ -4676,8 +4776,9 @@
       <c r="P78" s="16">
         <v>1182</v>
       </c>
-    </row>
-    <row r="79" spans="1:17" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q78" s="16"/>
+    </row>
+    <row r="79" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A79" s="21">
         <v>46110</v>
       </c>
@@ -4726,8 +4827,9 @@
       <c r="P79" s="16">
         <v>1299</v>
       </c>
-    </row>
-    <row r="80" spans="1:17" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q79" s="16"/>
+    </row>
+    <row r="80" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A80" s="21">
         <v>46112</v>
       </c>
@@ -4776,8 +4878,9 @@
       <c r="P80" s="16">
         <v>630</v>
       </c>
-    </row>
-    <row r="81" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q80" s="16"/>
+    </row>
+    <row r="81" spans="1:18" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A81" s="21">
         <v>46113</v>
       </c>
@@ -4826,8 +4929,9 @@
       <c r="P81" s="26">
         <v>274</v>
       </c>
-    </row>
-    <row r="82" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q81" s="16"/>
+    </row>
+    <row r="82" spans="1:18" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A82" s="29">
         <v>46114</v>
       </c>
@@ -4876,8 +4980,9 @@
       <c r="P82" s="30">
         <v>221</v>
       </c>
-    </row>
-    <row r="83" spans="1:16" s="16" customFormat="1" ht="20" customHeight="1">
+      <c r="Q82" s="16"/>
+    </row>
+    <row r="83" spans="1:18" s="16" customFormat="1" ht="19.95" customHeight="1">
       <c r="A83" s="21">
         <v>46115</v>
       </c>
@@ -4926,8 +5031,9 @@
       <c r="P83" s="16">
         <v>224</v>
       </c>
-    </row>
-    <row r="84" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="R83" s="40"/>
+    </row>
+    <row r="84" spans="1:18" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A84" s="21">
         <v>46116</v>
       </c>
@@ -4976,8 +5082,9 @@
       <c r="P84" s="16">
         <v>872</v>
       </c>
-    </row>
-    <row r="85" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q84" s="16"/>
+    </row>
+    <row r="85" spans="1:18" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A85" s="21">
         <v>46117</v>
       </c>
@@ -5026,8 +5133,9 @@
       <c r="P85" s="16">
         <v>708</v>
       </c>
-    </row>
-    <row r="86" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q85" s="16"/>
+    </row>
+    <row r="86" spans="1:18" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A86" s="21">
         <v>46119</v>
       </c>
@@ -5076,8 +5184,9 @@
       <c r="P86" s="26">
         <v>229</v>
       </c>
-    </row>
-    <row r="87" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q86" s="16"/>
+    </row>
+    <row r="87" spans="1:18" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A87" s="21">
         <v>46120</v>
       </c>
@@ -5126,8 +5235,9 @@
       <c r="P87" s="16">
         <v>250</v>
       </c>
-    </row>
-    <row r="88" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q87" s="16"/>
+    </row>
+    <row r="88" spans="1:18" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A88" s="21">
         <v>46121</v>
       </c>
@@ -5176,8 +5286,9 @@
       <c r="P88" s="16">
         <v>30</v>
       </c>
-    </row>
-    <row r="89" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q88" s="16"/>
+    </row>
+    <row r="89" spans="1:18" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A89" s="21">
         <v>46122</v>
       </c>
@@ -5226,8 +5337,9 @@
       <c r="P89" s="16">
         <v>95</v>
       </c>
-    </row>
-    <row r="90" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q89" s="16"/>
+    </row>
+    <row r="90" spans="1:18" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A90" s="21">
         <v>46123</v>
       </c>
@@ -5276,8 +5388,9 @@
       <c r="P90" s="16">
         <v>724</v>
       </c>
-    </row>
-    <row r="91" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q90" s="16"/>
+    </row>
+    <row r="91" spans="1:18" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A91" s="21">
         <v>46124</v>
       </c>
@@ -5326,8 +5439,9 @@
       <c r="P91" s="16">
         <v>942</v>
       </c>
-    </row>
-    <row r="92" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q91" s="16"/>
+    </row>
+    <row r="92" spans="1:18" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A92" s="32">
         <v>46126</v>
       </c>
@@ -5376,8 +5490,9 @@
       <c r="P92" s="30">
         <v>215</v>
       </c>
-    </row>
-    <row r="93" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q92" s="16"/>
+    </row>
+    <row r="93" spans="1:18" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A93" s="21">
         <v>46127</v>
       </c>
@@ -5426,8 +5541,9 @@
       <c r="P93" s="16">
         <v>205</v>
       </c>
-    </row>
-    <row r="94" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q93" s="16"/>
+    </row>
+    <row r="94" spans="1:18" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A94" s="21">
         <v>46128</v>
       </c>
@@ -5476,8 +5592,9 @@
       <c r="P94" s="16">
         <v>204</v>
       </c>
-    </row>
-    <row r="95" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q94" s="16"/>
+    </row>
+    <row r="95" spans="1:18" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A95" s="21">
         <v>46129</v>
       </c>
@@ -5526,8 +5643,9 @@
       <c r="P95" s="16">
         <v>229</v>
       </c>
-    </row>
-    <row r="96" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q95" s="16"/>
+    </row>
+    <row r="96" spans="1:18" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A96" s="21">
         <v>46130</v>
       </c>
@@ -5576,8 +5694,9 @@
       <c r="P96" s="17">
         <v>920</v>
       </c>
-    </row>
-    <row r="97" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q96" s="16"/>
+    </row>
+    <row r="97" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A97" s="29">
         <v>46131</v>
       </c>
@@ -5626,8 +5745,9 @@
       <c r="P97" s="33">
         <v>641</v>
       </c>
-    </row>
-    <row r="98" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q97" s="16"/>
+    </row>
+    <row r="98" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A98" s="21">
         <v>46133</v>
       </c>
@@ -5676,8 +5796,9 @@
       <c r="P98" s="17">
         <v>269</v>
       </c>
-    </row>
-    <row r="99" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q98" s="16"/>
+    </row>
+    <row r="99" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A99" s="8">
         <v>46134</v>
       </c>
@@ -5709,13 +5830,13 @@
         <v>105</v>
       </c>
       <c r="K99" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L99" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M99" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N99" s="6" t="s">
         <v>16</v>
@@ -5726,8 +5847,9 @@
       <c r="P99" s="6">
         <v>254</v>
       </c>
-    </row>
-    <row r="100" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q99" s="16"/>
+    </row>
+    <row r="100" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A100" s="8">
         <v>46135</v>
       </c>
@@ -5759,13 +5881,13 @@
         <v>156</v>
       </c>
       <c r="K100" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L100" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M100" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N100" s="6">
         <v>201</v>
@@ -5776,8 +5898,9 @@
       <c r="P100" s="6">
         <v>246</v>
       </c>
-    </row>
-    <row r="101" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q100" s="16"/>
+    </row>
+    <row r="101" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A101" s="8">
         <v>46136</v>
       </c>
@@ -5809,13 +5932,13 @@
         <v>169</v>
       </c>
       <c r="K101" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L101" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M101" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N101" s="6">
         <v>258</v>
@@ -5826,8 +5949,9 @@
       <c r="P101" s="6">
         <v>242</v>
       </c>
-    </row>
-    <row r="102" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q101" s="16"/>
+    </row>
+    <row r="102" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A102" s="8">
         <v>46137</v>
       </c>
@@ -5876,8 +6000,9 @@
       <c r="P102" s="6">
         <v>826</v>
       </c>
-    </row>
-    <row r="103" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q102" s="16"/>
+    </row>
+    <row r="103" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A103" s="34">
         <v>46138</v>
       </c>
@@ -5909,13 +6034,13 @@
         <v>500</v>
       </c>
       <c r="K103" s="28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L103" s="28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M103" s="28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N103" s="12">
         <v>468</v>
@@ -5926,8 +6051,9 @@
       <c r="P103" s="12">
         <v>738</v>
       </c>
-    </row>
-    <row r="104" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q103" s="16"/>
+    </row>
+    <row r="104" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A104" s="8">
         <v>46140</v>
       </c>
@@ -5959,13 +6085,13 @@
         <v>98</v>
       </c>
       <c r="K104" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L104" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M104" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N104" s="6">
         <v>14</v>
@@ -5976,8 +6102,9 @@
       <c r="P104" s="6">
         <v>170</v>
       </c>
-    </row>
-    <row r="105" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q104" s="16"/>
+    </row>
+    <row r="105" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A105" s="8">
         <v>46141</v>
       </c>
@@ -5985,11 +6112,11 @@
         <v>1952</v>
       </c>
       <c r="C105" s="6">
-        <f>C100+C102</f>
+        <f t="shared" ref="C105:J105" si="1">C100+C102</f>
         <v>302</v>
       </c>
       <c r="D105" s="6">
-        <f t="shared" ref="D105:J105" si="1">D100+D102</f>
+        <f t="shared" si="1"/>
         <v>378</v>
       </c>
       <c r="E105" s="6">
@@ -6017,13 +6144,13 @@
         <v>790</v>
       </c>
       <c r="K105" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L105" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M105" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N105" s="6">
         <v>203</v>
@@ -6034,8 +6161,9 @@
       <c r="P105" s="6">
         <v>255</v>
       </c>
-    </row>
-    <row r="106" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q105" s="16"/>
+    </row>
+    <row r="106" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A106" s="11">
         <v>46142</v>
       </c>
@@ -6067,13 +6195,13 @@
         <v>132</v>
       </c>
       <c r="K106" s="28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L106" s="28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M106" s="28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N106" s="12">
         <v>90</v>
@@ -6084,8 +6212,9 @@
       <c r="P106" s="12">
         <v>254</v>
       </c>
-    </row>
-    <row r="107" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q106" s="16"/>
+    </row>
+    <row r="107" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A107" s="8">
         <v>46143</v>
       </c>
@@ -6117,13 +6246,13 @@
         <v>534</v>
       </c>
       <c r="K107" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L107" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M107" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N107" s="6">
         <v>455</v>
@@ -6134,8 +6263,9 @@
       <c r="P107" s="6">
         <v>530</v>
       </c>
-    </row>
-    <row r="108" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q107" s="16"/>
+    </row>
+    <row r="108" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A108" s="8">
         <v>46144</v>
       </c>
@@ -6184,8 +6314,9 @@
       <c r="P108" s="36">
         <v>817</v>
       </c>
-    </row>
-    <row r="109" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q108" s="16"/>
+    </row>
+    <row r="109" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A109" s="8">
         <v>46145</v>
       </c>
@@ -6217,13 +6348,13 @@
         <v>202</v>
       </c>
       <c r="K109" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L109" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M109" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N109" s="6">
         <v>157</v>
@@ -6234,8 +6365,9 @@
       <c r="P109" s="6">
         <v>233</v>
       </c>
-    </row>
-    <row r="110" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q109" s="16"/>
+    </row>
+    <row r="110" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A110" s="8">
         <v>46147</v>
       </c>
@@ -6267,13 +6399,13 @@
         <v>826</v>
       </c>
       <c r="K110" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L110" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M110" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N110" s="36">
         <v>575</v>
@@ -6284,8 +6416,9 @@
       <c r="P110" s="36">
         <v>1646</v>
       </c>
-    </row>
-    <row r="111" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q110" s="16"/>
+    </row>
+    <row r="111" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A111" s="8">
         <v>46148</v>
       </c>
@@ -6317,13 +6450,13 @@
         <v>156</v>
       </c>
       <c r="K111" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L111" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M111" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N111" s="6">
         <v>64</v>
@@ -6334,8 +6467,9 @@
       <c r="P111" s="6">
         <v>234</v>
       </c>
-    </row>
-    <row r="112" spans="1:16" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q111" s="16"/>
+    </row>
+    <row r="112" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A112" s="8">
         <v>46149</v>
       </c>
@@ -6367,13 +6501,13 @@
         <v>22</v>
       </c>
       <c r="K112" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L112" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M112" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N112" s="6">
         <v>136</v>
@@ -6384,8 +6518,9 @@
       <c r="P112" s="6">
         <v>180</v>
       </c>
-    </row>
-    <row r="113" spans="1:243" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q112" s="16"/>
+    </row>
+    <row r="113" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A113" s="8">
         <v>46150</v>
       </c>
@@ -6417,13 +6552,13 @@
         <v>164</v>
       </c>
       <c r="K113" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L113" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M113" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N113" s="6">
         <v>85</v>
@@ -6434,8 +6569,9 @@
       <c r="P113" s="6">
         <v>272</v>
       </c>
-    </row>
-    <row r="114" spans="1:243" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q113" s="16"/>
+    </row>
+    <row r="114" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A114" s="39">
         <v>46151</v>
       </c>
@@ -6484,8 +6620,9 @@
       <c r="P114" s="6">
         <v>904</v>
       </c>
-    </row>
-    <row r="115" spans="1:243" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q114" s="16"/>
+    </row>
+    <row r="115" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A115" s="39">
         <v>46152</v>
       </c>
@@ -6517,13 +6654,13 @@
         <v>483</v>
       </c>
       <c r="K115" s="17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L115" s="17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M115" s="17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N115" s="6">
         <v>134</v>
@@ -6534,8 +6671,9 @@
       <c r="P115" s="6">
         <v>720</v>
       </c>
-    </row>
-    <row r="116" spans="1:243" s="18" customFormat="1" ht="20" customHeight="1">
+      <c r="Q115" s="16"/>
+    </row>
+    <row r="116" spans="1:17" s="18" customFormat="1" ht="19.95" customHeight="1">
       <c r="A116" s="39">
         <v>46154</v>
       </c>
@@ -6567,13 +6705,13 @@
         <v>133</v>
       </c>
       <c r="K116" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L116" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M116" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N116" s="37">
         <v>88</v>
@@ -6584,584 +6722,3973 @@
       <c r="P116" s="36">
         <v>209</v>
       </c>
-    </row>
-    <row r="117" spans="1:243" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A117" s="35"/>
-      <c r="B117" s="35">
-        <f>SUM(B2:B116)</f>
-        <v>177490</v>
-      </c>
-      <c r="C117" s="35">
-        <f>SUM(C2:C116)</f>
-        <v>10054</v>
-      </c>
-      <c r="D117" s="35">
-        <f t="shared" ref="D117:P117" si="2">SUM(D2:D116)</f>
-        <v>11963</v>
-      </c>
-      <c r="E117" s="35">
+      <c r="Q116" s="16"/>
+    </row>
+    <row r="117" spans="1:17" s="4" customFormat="1" ht="15" customHeight="1">
+      <c r="A117" s="8">
+        <v>46155</v>
+      </c>
+      <c r="B117" s="6">
+        <v>1559</v>
+      </c>
+      <c r="C117" s="6">
+        <v>42</v>
+      </c>
+      <c r="D117" s="6">
+        <v>117</v>
+      </c>
+      <c r="E117" s="6">
+        <v>187</v>
+      </c>
+      <c r="F117" s="6">
+        <v>583</v>
+      </c>
+      <c r="G117" s="6">
+        <v>180</v>
+      </c>
+      <c r="H117" s="6">
+        <v>123</v>
+      </c>
+      <c r="I117" s="6">
+        <v>164</v>
+      </c>
+      <c r="J117" s="6">
+        <v>139</v>
+      </c>
+      <c r="K117" s="6"/>
+      <c r="L117" s="6"/>
+      <c r="M117" s="6"/>
+      <c r="N117" s="6">
+        <v>24</v>
+      </c>
+      <c r="O117" s="6">
+        <v>1349</v>
+      </c>
+      <c r="P117" s="6">
+        <v>186</v>
+      </c>
+      <c r="Q117" s="41"/>
+    </row>
+    <row r="118" spans="1:17">
+      <c r="A118" s="8">
+        <v>46156</v>
+      </c>
+      <c r="B118" s="6">
+        <v>1391</v>
+      </c>
+      <c r="C118" s="6">
+        <v>90</v>
+      </c>
+      <c r="D118" s="6">
+        <v>90</v>
+      </c>
+      <c r="E118" s="6">
+        <v>148</v>
+      </c>
+      <c r="F118" s="6">
+        <v>450</v>
+      </c>
+      <c r="G118" s="6">
+        <v>134</v>
+      </c>
+      <c r="H118" s="6">
+        <v>129</v>
+      </c>
+      <c r="I118" s="6">
+        <v>85</v>
+      </c>
+      <c r="J118" s="6">
+        <v>110</v>
+      </c>
+      <c r="K118" s="6"/>
+      <c r="L118" s="6"/>
+      <c r="M118" s="6"/>
+      <c r="N118" s="6">
+        <v>155</v>
+      </c>
+      <c r="O118" s="6">
+        <v>1099</v>
+      </c>
+      <c r="P118" s="6">
+        <v>137</v>
+      </c>
+      <c r="Q118" s="42"/>
+    </row>
+    <row r="119" spans="1:17">
+      <c r="A119" s="8">
+        <v>46157</v>
+      </c>
+      <c r="B119" s="6">
+        <v>1897</v>
+      </c>
+      <c r="C119" s="6">
+        <v>203</v>
+      </c>
+      <c r="D119" s="6">
+        <v>310</v>
+      </c>
+      <c r="E119" s="6">
+        <v>179</v>
+      </c>
+      <c r="F119" s="6">
+        <v>369</v>
+      </c>
+      <c r="G119" s="6">
+        <v>227</v>
+      </c>
+      <c r="H119" s="6">
+        <v>168</v>
+      </c>
+      <c r="I119" s="6">
+        <v>110</v>
+      </c>
+      <c r="J119" s="6">
+        <v>126</v>
+      </c>
+      <c r="K119" s="6">
+        <v>12</v>
+      </c>
+      <c r="L119" s="6"/>
+      <c r="M119" s="6"/>
+      <c r="N119" s="6">
+        <v>205</v>
+      </c>
+      <c r="O119" s="6">
+        <v>1222</v>
+      </c>
+      <c r="P119" s="6">
+        <v>470</v>
+      </c>
+      <c r="Q119" s="42"/>
+    </row>
+    <row r="120" spans="1:17">
+      <c r="A120" s="8">
+        <v>46158</v>
+      </c>
+      <c r="B120" s="6">
+        <v>3550</v>
+      </c>
+      <c r="C120" s="6">
+        <v>128</v>
+      </c>
+      <c r="D120" s="6">
+        <v>142</v>
+      </c>
+      <c r="E120" s="6">
+        <v>171</v>
+      </c>
+      <c r="F120" s="6">
+        <v>183</v>
+      </c>
+      <c r="G120" s="6">
+        <v>494</v>
+      </c>
+      <c r="H120" s="6">
+        <v>415</v>
+      </c>
+      <c r="I120" s="6">
+        <v>397</v>
+      </c>
+      <c r="J120" s="6">
+        <v>334</v>
+      </c>
+      <c r="K120" s="6">
+        <v>316</v>
+      </c>
+      <c r="L120" s="6">
+        <v>319</v>
+      </c>
+      <c r="M120" s="6">
+        <v>264</v>
+      </c>
+      <c r="N120" s="6">
+        <v>387</v>
+      </c>
+      <c r="O120" s="6">
+        <v>2437</v>
+      </c>
+      <c r="P120" s="6">
+        <v>726</v>
+      </c>
+      <c r="Q120" s="42"/>
+    </row>
+    <row r="121" spans="1:17" ht="16.95" customHeight="1">
+      <c r="A121" s="8">
+        <v>46159</v>
+      </c>
+      <c r="B121" s="6">
+        <v>2654</v>
+      </c>
+      <c r="C121" s="6">
+        <v>230</v>
+      </c>
+      <c r="D121" s="6">
+        <v>191</v>
+      </c>
+      <c r="E121" s="6">
+        <v>239</v>
+      </c>
+      <c r="F121" s="6">
+        <v>274</v>
+      </c>
+      <c r="G121" s="6">
+        <v>353</v>
+      </c>
+      <c r="H121" s="6">
+        <v>394</v>
+      </c>
+      <c r="I121" s="6">
+        <v>302</v>
+      </c>
+      <c r="J121" s="6">
+        <v>290</v>
+      </c>
+      <c r="K121" s="6">
+        <v>30</v>
+      </c>
+      <c r="L121" s="6"/>
+      <c r="M121" s="6"/>
+      <c r="N121" s="6">
+        <v>381</v>
+      </c>
+      <c r="O121" s="6">
+        <v>1648</v>
+      </c>
+      <c r="P121" s="6">
+        <v>625</v>
+      </c>
+      <c r="Q121" s="42"/>
+    </row>
+    <row r="122" spans="1:17">
+      <c r="A122" s="8">
+        <v>46161</v>
+      </c>
+      <c r="B122" s="6">
+        <v>1534</v>
+      </c>
+      <c r="C122" s="6">
+        <v>85</v>
+      </c>
+      <c r="D122" s="6">
+        <v>76</v>
+      </c>
+      <c r="E122" s="6">
+        <v>187</v>
+      </c>
+      <c r="F122" s="6">
+        <v>556</v>
+      </c>
+      <c r="G122" s="6">
+        <v>146</v>
+      </c>
+      <c r="H122" s="6">
+        <v>107</v>
+      </c>
+      <c r="I122" s="6">
+        <v>146</v>
+      </c>
+      <c r="J122" s="6">
+        <v>123</v>
+      </c>
+      <c r="K122" s="6">
+        <v>28</v>
+      </c>
+      <c r="L122" s="6"/>
+      <c r="M122" s="6"/>
+      <c r="N122" s="6">
+        <v>80</v>
+      </c>
+      <c r="O122" s="6">
+        <v>1267</v>
+      </c>
+      <c r="P122" s="6">
+        <v>187</v>
+      </c>
+      <c r="Q122" s="42"/>
+    </row>
+    <row r="123" spans="1:17">
+      <c r="A123" s="8">
+        <v>46162</v>
+      </c>
+      <c r="B123" s="6">
+        <v>225</v>
+      </c>
+      <c r="C123" s="6">
+        <v>25</v>
+      </c>
+      <c r="D123" s="6">
+        <v>14</v>
+      </c>
+      <c r="E123" s="6">
+        <v>17</v>
+      </c>
+      <c r="F123" s="6">
+        <v>50</v>
+      </c>
+      <c r="G123" s="6">
+        <v>21</v>
+      </c>
+      <c r="H123" s="6">
+        <v>12</v>
+      </c>
+      <c r="I123" s="6">
+        <v>13</v>
+      </c>
+      <c r="J123" s="6">
+        <v>10</v>
+      </c>
+      <c r="K123" s="6">
+        <v>0</v>
+      </c>
+      <c r="L123" s="6"/>
+      <c r="M123" s="6"/>
+      <c r="N123" s="6">
+        <v>63</v>
+      </c>
+      <c r="O123" s="6">
+        <v>156</v>
+      </c>
+      <c r="P123" s="6">
+        <v>6</v>
+      </c>
+      <c r="Q123" s="42"/>
+    </row>
+    <row r="124" spans="1:17">
+      <c r="A124" s="8">
+        <v>46163</v>
+      </c>
+      <c r="B124" s="6">
+        <v>941</v>
+      </c>
+      <c r="C124" s="6">
+        <v>27</v>
+      </c>
+      <c r="D124" s="6">
+        <v>19</v>
+      </c>
+      <c r="E124" s="6">
+        <v>96</v>
+      </c>
+      <c r="F124" s="6">
+        <v>330</v>
+      </c>
+      <c r="G124" s="6">
+        <v>106</v>
+      </c>
+      <c r="H124" s="6">
+        <v>80</v>
+      </c>
+      <c r="I124" s="6">
+        <v>94</v>
+      </c>
+      <c r="J124" s="6">
+        <v>89</v>
+      </c>
+      <c r="K124" s="6">
+        <v>27</v>
+      </c>
+      <c r="L124" s="6"/>
+      <c r="M124" s="6"/>
+      <c r="N124" s="6">
+        <v>73</v>
+      </c>
+      <c r="O124" s="6">
+        <v>729</v>
+      </c>
+      <c r="P124" s="6">
+        <v>139</v>
+      </c>
+      <c r="Q124" s="42"/>
+    </row>
+    <row r="125" spans="1:17">
+      <c r="A125" s="8">
+        <v>46164</v>
+      </c>
+      <c r="B125" s="6">
+        <v>1875</v>
+      </c>
+      <c r="C125" s="6">
+        <v>168</v>
+      </c>
+      <c r="D125" s="6">
+        <v>104</v>
+      </c>
+      <c r="E125" s="6">
+        <v>180</v>
+      </c>
+      <c r="F125" s="6">
+        <v>445</v>
+      </c>
+      <c r="G125" s="6">
+        <v>182</v>
+      </c>
+      <c r="H125" s="6">
+        <v>167</v>
+      </c>
+      <c r="I125" s="6">
+        <v>180</v>
+      </c>
+      <c r="J125" s="6">
+        <v>191</v>
+      </c>
+      <c r="K125" s="6">
+        <v>42</v>
+      </c>
+      <c r="L125" s="6"/>
+      <c r="M125" s="6"/>
+      <c r="N125" s="6">
+        <v>216</v>
+      </c>
+      <c r="O125" s="6">
+        <v>1456</v>
+      </c>
+      <c r="P125" s="6">
+        <v>203</v>
+      </c>
+      <c r="Q125" s="42"/>
+    </row>
+    <row r="126" spans="1:17">
+      <c r="A126" s="8">
+        <v>46165</v>
+      </c>
+      <c r="B126" s="6">
+        <v>4346</v>
+      </c>
+      <c r="C126" s="6">
+        <v>174</v>
+      </c>
+      <c r="D126" s="6">
+        <v>220</v>
+      </c>
+      <c r="E126" s="6">
+        <v>208</v>
+      </c>
+      <c r="F126" s="6">
+        <v>309</v>
+      </c>
+      <c r="G126" s="6">
+        <v>414</v>
+      </c>
+      <c r="H126" s="6">
+        <v>501</v>
+      </c>
+      <c r="I126" s="6">
+        <v>536</v>
+      </c>
+      <c r="J126" s="6">
+        <v>464</v>
+      </c>
+      <c r="K126" s="6">
+        <v>440</v>
+      </c>
+      <c r="L126" s="6">
+        <v>256</v>
+      </c>
+      <c r="M126" s="6">
+        <v>271</v>
+      </c>
+      <c r="N126" s="6">
+        <v>493</v>
+      </c>
+      <c r="O126" s="6">
+        <v>3111</v>
+      </c>
+      <c r="P126" s="6">
+        <v>742</v>
+      </c>
+      <c r="Q126" s="42"/>
+    </row>
+    <row r="127" spans="1:17">
+      <c r="A127" s="8">
+        <v>46166</v>
+      </c>
+      <c r="B127" s="6">
+        <v>3623</v>
+      </c>
+      <c r="C127" s="6">
+        <v>194</v>
+      </c>
+      <c r="D127" s="6">
+        <v>236</v>
+      </c>
+      <c r="E127" s="6">
+        <v>218</v>
+      </c>
+      <c r="F127" s="6">
+        <v>344</v>
+      </c>
+      <c r="G127" s="6">
+        <v>469</v>
+      </c>
+      <c r="H127" s="6">
+        <v>580</v>
+      </c>
+      <c r="I127" s="6">
+        <v>530</v>
+      </c>
+      <c r="J127" s="6">
+        <v>427</v>
+      </c>
+      <c r="K127" s="6">
+        <v>129</v>
+      </c>
+      <c r="L127" s="6"/>
+      <c r="M127" s="6"/>
+      <c r="N127" s="6">
+        <v>496</v>
+      </c>
+      <c r="O127" s="6">
+        <v>2564</v>
+      </c>
+      <c r="P127" s="6">
+        <v>563</v>
+      </c>
+      <c r="Q127" s="42"/>
+    </row>
+    <row r="128" spans="1:17" ht="16.8" customHeight="1">
+      <c r="A128" s="8">
+        <v>46167</v>
+      </c>
+      <c r="B128" s="6">
+        <v>2518</v>
+      </c>
+      <c r="C128" s="6">
+        <v>121</v>
+      </c>
+      <c r="D128" s="6">
+        <v>170</v>
+      </c>
+      <c r="E128" s="6">
+        <v>183</v>
+      </c>
+      <c r="F128" s="6">
+        <v>271</v>
+      </c>
+      <c r="G128" s="6">
+        <v>259</v>
+      </c>
+      <c r="H128" s="6">
+        <v>323</v>
+      </c>
+      <c r="I128" s="6">
+        <v>349</v>
+      </c>
+      <c r="J128" s="6">
+        <v>273</v>
+      </c>
+      <c r="K128" s="6">
+        <v>85</v>
+      </c>
+      <c r="L128" s="6"/>
+      <c r="M128" s="6"/>
+      <c r="N128" s="6">
+        <v>483</v>
+      </c>
+      <c r="O128" s="6">
+        <v>1632</v>
+      </c>
+      <c r="P128" s="6">
+        <v>403</v>
+      </c>
+      <c r="Q128" s="42"/>
+    </row>
+    <row r="129" spans="1:17">
+      <c r="A129" s="8">
+        <v>46169</v>
+      </c>
+      <c r="B129" s="6">
+        <v>1206</v>
+      </c>
+      <c r="C129" s="6">
+        <v>60</v>
+      </c>
+      <c r="D129" s="6">
+        <v>85</v>
+      </c>
+      <c r="E129" s="6">
+        <v>72</v>
+      </c>
+      <c r="F129" s="6">
+        <v>438</v>
+      </c>
+      <c r="G129" s="6">
+        <v>122</v>
+      </c>
+      <c r="H129" s="6">
+        <v>111</v>
+      </c>
+      <c r="I129" s="6">
+        <v>98</v>
+      </c>
+      <c r="J129" s="6">
+        <v>60</v>
+      </c>
+      <c r="K129" s="6">
+        <v>8</v>
+      </c>
+      <c r="L129" s="6"/>
+      <c r="M129" s="6"/>
+      <c r="N129" s="6">
+        <v>152</v>
+      </c>
+      <c r="O129" s="6">
+        <v>1045</v>
+      </c>
+      <c r="P129" s="6">
+        <v>9</v>
+      </c>
+      <c r="Q129" s="42"/>
+    </row>
+    <row r="130" spans="1:17">
+      <c r="A130" s="8">
+        <v>46170</v>
+      </c>
+      <c r="B130" s="6">
+        <v>1062</v>
+      </c>
+      <c r="C130" s="6">
+        <v>37</v>
+      </c>
+      <c r="D130" s="6">
+        <v>49</v>
+      </c>
+      <c r="E130" s="6">
+        <v>102</v>
+      </c>
+      <c r="F130" s="6">
+        <v>428</v>
+      </c>
+      <c r="G130" s="6">
+        <v>114</v>
+      </c>
+      <c r="H130" s="6">
+        <v>86</v>
+      </c>
+      <c r="I130" s="6">
+        <v>78</v>
+      </c>
+      <c r="J130" s="6">
+        <v>80</v>
+      </c>
+      <c r="K130" s="6">
+        <v>27</v>
+      </c>
+      <c r="L130" s="6"/>
+      <c r="M130" s="6"/>
+      <c r="N130" s="6">
+        <v>30</v>
+      </c>
+      <c r="O130" s="6">
+        <v>1001</v>
+      </c>
+      <c r="P130" s="6">
+        <v>31</v>
+      </c>
+      <c r="Q130" s="42"/>
+    </row>
+    <row r="131" spans="1:17">
+      <c r="A131" s="8">
+        <v>46171</v>
+      </c>
+      <c r="B131" s="6">
+        <v>1625</v>
+      </c>
+      <c r="C131" s="6">
+        <v>241</v>
+      </c>
+      <c r="D131" s="6">
+        <v>93</v>
+      </c>
+      <c r="E131" s="6">
+        <v>146</v>
+      </c>
+      <c r="F131" s="6">
+        <v>437</v>
+      </c>
+      <c r="G131" s="6">
+        <v>131</v>
+      </c>
+      <c r="H131" s="6">
+        <v>77</v>
+      </c>
+      <c r="I131" s="6">
+        <v>80</v>
+      </c>
+      <c r="J131" s="6">
+        <v>145</v>
+      </c>
+      <c r="K131" s="6">
+        <v>60</v>
+      </c>
+      <c r="L131" s="6"/>
+      <c r="M131" s="6"/>
+      <c r="N131" s="6">
+        <v>170</v>
+      </c>
+      <c r="O131" s="6">
+        <v>1410</v>
+      </c>
+      <c r="P131" s="6">
+        <v>45</v>
+      </c>
+      <c r="Q131" s="42"/>
+    </row>
+    <row r="132" spans="1:17">
+      <c r="A132" s="8">
+        <v>46172</v>
+      </c>
+      <c r="B132" s="6">
+        <v>2984</v>
+      </c>
+      <c r="C132" s="6">
+        <v>85</v>
+      </c>
+      <c r="D132" s="6">
+        <v>130</v>
+      </c>
+      <c r="E132" s="6">
+        <v>131</v>
+      </c>
+      <c r="F132" s="6">
+        <v>195</v>
+      </c>
+      <c r="G132" s="6">
+        <v>240</v>
+      </c>
+      <c r="H132" s="6">
+        <v>299</v>
+      </c>
+      <c r="I132" s="6">
+        <v>265</v>
+      </c>
+      <c r="J132" s="6">
+        <v>364</v>
+      </c>
+      <c r="K132" s="6">
+        <v>289</v>
+      </c>
+      <c r="L132" s="6">
+        <v>267</v>
+      </c>
+      <c r="M132" s="6">
+        <v>258</v>
+      </c>
+      <c r="N132" s="6">
+        <v>394</v>
+      </c>
+      <c r="O132" s="6">
+        <v>2587</v>
+      </c>
+      <c r="P132" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q132" s="42"/>
+    </row>
+    <row r="133" spans="1:17">
+      <c r="A133" s="8">
+        <v>46173</v>
+      </c>
+      <c r="B133" s="6">
+        <v>1971</v>
+      </c>
+      <c r="C133" s="6">
+        <v>104</v>
+      </c>
+      <c r="D133" s="6">
+        <v>86</v>
+      </c>
+      <c r="E133" s="6">
+        <v>94</v>
+      </c>
+      <c r="F133" s="6">
+        <v>148</v>
+      </c>
+      <c r="G133" s="6">
+        <v>211</v>
+      </c>
+      <c r="H133" s="6">
+        <v>206</v>
+      </c>
+      <c r="I133" s="6">
+        <v>317</v>
+      </c>
+      <c r="J133" s="6">
+        <v>230</v>
+      </c>
+      <c r="K133" s="6">
+        <v>81</v>
+      </c>
+      <c r="L133" s="6"/>
+      <c r="M133" s="6"/>
+      <c r="N133" s="6">
+        <v>359</v>
+      </c>
+      <c r="O133" s="6">
+        <v>1477</v>
+      </c>
+      <c r="P133" s="6">
+        <v>135</v>
+      </c>
+      <c r="Q133" s="42"/>
+    </row>
+    <row r="134" spans="1:17">
+      <c r="A134" s="8">
+        <v>46175</v>
+      </c>
+      <c r="B134" s="6">
+        <v>762</v>
+      </c>
+      <c r="C134" s="6">
+        <v>114</v>
+      </c>
+      <c r="D134" s="6">
+        <v>36</v>
+      </c>
+      <c r="E134" s="6">
+        <v>70</v>
+      </c>
+      <c r="F134" s="6">
+        <v>210</v>
+      </c>
+      <c r="G134" s="6">
+        <v>66</v>
+      </c>
+      <c r="H134" s="6">
+        <v>49</v>
+      </c>
+      <c r="I134" s="6">
+        <v>47</v>
+      </c>
+      <c r="J134" s="6">
+        <v>56</v>
+      </c>
+      <c r="K134" s="6">
+        <v>19</v>
+      </c>
+      <c r="L134" s="6"/>
+      <c r="M134" s="6"/>
+      <c r="N134" s="6">
+        <v>68</v>
+      </c>
+      <c r="O134" s="6">
+        <v>664</v>
+      </c>
+      <c r="P134" s="6">
+        <v>30</v>
+      </c>
+      <c r="Q134" s="42"/>
+    </row>
+    <row r="135" spans="1:17">
+      <c r="A135" s="8">
+        <v>46176</v>
+      </c>
+      <c r="B135" s="6">
+        <v>2067</v>
+      </c>
+      <c r="C135" s="6">
+        <v>111</v>
+      </c>
+      <c r="D135" s="6">
+        <v>158</v>
+      </c>
+      <c r="E135" s="6">
+        <v>113</v>
+      </c>
+      <c r="F135" s="6">
+        <v>163</v>
+      </c>
+      <c r="G135" s="6">
+        <v>246</v>
+      </c>
+      <c r="H135" s="6">
+        <v>257</v>
+      </c>
+      <c r="I135" s="6">
+        <v>266</v>
+      </c>
+      <c r="J135" s="6">
+        <v>210</v>
+      </c>
+      <c r="K135" s="6">
+        <v>71</v>
+      </c>
+      <c r="L135" s="6"/>
+      <c r="M135" s="6"/>
+      <c r="N135" s="6">
+        <v>447</v>
+      </c>
+      <c r="O135" s="6">
+        <v>1595</v>
+      </c>
+      <c r="P135" s="6">
+        <v>25</v>
+      </c>
+      <c r="Q135" s="42"/>
+    </row>
+    <row r="136" spans="1:17">
+      <c r="A136" s="8">
+        <v>46177</v>
+      </c>
+      <c r="B136" s="6">
+        <v>839</v>
+      </c>
+      <c r="C136" s="6">
+        <v>67</v>
+      </c>
+      <c r="D136" s="6">
+        <v>76</v>
+      </c>
+      <c r="E136" s="6">
+        <v>104</v>
+      </c>
+      <c r="F136" s="6">
+        <v>232</v>
+      </c>
+      <c r="G136" s="6">
+        <v>47</v>
+      </c>
+      <c r="H136" s="6">
+        <v>39</v>
+      </c>
+      <c r="I136" s="6">
+        <v>52</v>
+      </c>
+      <c r="J136" s="6">
+        <v>73</v>
+      </c>
+      <c r="K136" s="6">
+        <v>9</v>
+      </c>
+      <c r="L136" s="6"/>
+      <c r="M136" s="6"/>
+      <c r="N136" s="6">
+        <v>95</v>
+      </c>
+      <c r="O136" s="6">
+        <v>699</v>
+      </c>
+      <c r="P136" s="6">
+        <v>45</v>
+      </c>
+      <c r="Q136" s="42"/>
+    </row>
+    <row r="137" spans="1:17">
+      <c r="A137" s="8">
+        <v>46178</v>
+      </c>
+      <c r="B137" s="6">
+        <v>1305</v>
+      </c>
+      <c r="C137" s="6">
+        <v>49</v>
+      </c>
+      <c r="D137" s="6">
+        <v>92</v>
+      </c>
+      <c r="E137" s="6">
+        <v>97</v>
+      </c>
+      <c r="F137" s="6">
+        <v>375</v>
+      </c>
+      <c r="G137" s="6">
+        <v>118</v>
+      </c>
+      <c r="H137" s="6">
+        <v>107</v>
+      </c>
+      <c r="I137" s="6">
+        <v>115</v>
+      </c>
+      <c r="J137" s="6">
+        <v>130</v>
+      </c>
+      <c r="K137" s="6">
+        <v>37</v>
+      </c>
+      <c r="L137" s="6"/>
+      <c r="M137" s="6"/>
+      <c r="N137" s="6">
+        <v>151</v>
+      </c>
+      <c r="O137" s="6">
+        <v>1120</v>
+      </c>
+      <c r="P137" s="6">
+        <v>34</v>
+      </c>
+      <c r="Q137" s="42"/>
+    </row>
+    <row r="138" spans="1:17">
+      <c r="A138" s="8">
+        <v>46179</v>
+      </c>
+      <c r="B138" s="6">
+        <v>3714</v>
+      </c>
+      <c r="C138" s="6">
+        <v>155</v>
+      </c>
+      <c r="D138" s="6">
+        <v>153</v>
+      </c>
+      <c r="E138" s="6">
+        <v>167</v>
+      </c>
+      <c r="F138" s="6">
+        <v>226</v>
+      </c>
+      <c r="G138" s="6">
+        <v>278</v>
+      </c>
+      <c r="H138" s="6">
+        <v>394</v>
+      </c>
+      <c r="I138" s="6">
+        <v>459</v>
+      </c>
+      <c r="J138" s="6">
+        <v>392</v>
+      </c>
+      <c r="K138" s="6">
+        <v>245</v>
+      </c>
+      <c r="L138" s="6">
+        <v>241</v>
+      </c>
+      <c r="M138" s="6">
+        <v>190</v>
+      </c>
+      <c r="N138" s="6">
+        <v>563</v>
+      </c>
+      <c r="O138" s="6">
+        <v>2961</v>
+      </c>
+      <c r="P138" s="6">
+        <v>190</v>
+      </c>
+      <c r="Q138" s="42"/>
+    </row>
+    <row r="139" spans="1:17">
+      <c r="A139" s="8">
+        <v>46180</v>
+      </c>
+      <c r="B139" s="6">
+        <v>2234</v>
+      </c>
+      <c r="C139" s="6">
+        <v>119</v>
+      </c>
+      <c r="D139" s="6">
+        <v>148</v>
+      </c>
+      <c r="E139" s="6">
+        <v>124</v>
+      </c>
+      <c r="F139" s="6">
+        <v>219</v>
+      </c>
+      <c r="G139" s="6">
+        <v>286</v>
+      </c>
+      <c r="H139" s="6">
+        <v>279</v>
+      </c>
+      <c r="I139" s="6">
+        <v>260</v>
+      </c>
+      <c r="J139" s="6">
+        <v>275</v>
+      </c>
+      <c r="K139" s="6">
+        <v>73</v>
+      </c>
+      <c r="L139" s="6"/>
+      <c r="M139" s="6"/>
+      <c r="N139" s="6">
+        <v>390</v>
+      </c>
+      <c r="O139" s="6">
+        <v>1783</v>
+      </c>
+      <c r="P139" s="6">
+        <v>61</v>
+      </c>
+      <c r="Q139" s="42"/>
+    </row>
+    <row r="140" spans="1:17">
+      <c r="A140" s="8">
+        <v>46182</v>
+      </c>
+      <c r="B140" s="6">
+        <v>1061</v>
+      </c>
+      <c r="C140" s="6">
+        <v>95</v>
+      </c>
+      <c r="D140" s="6">
+        <v>60</v>
+      </c>
+      <c r="E140" s="6">
+        <v>124</v>
+      </c>
+      <c r="F140" s="6">
+        <v>281</v>
+      </c>
+      <c r="G140" s="6">
+        <v>98</v>
+      </c>
+      <c r="H140" s="6">
+        <v>75</v>
+      </c>
+      <c r="I140" s="6">
+        <v>102</v>
+      </c>
+      <c r="J140" s="6">
+        <v>107</v>
+      </c>
+      <c r="K140" s="6">
+        <v>19</v>
+      </c>
+      <c r="L140" s="6"/>
+      <c r="M140" s="6"/>
+      <c r="N140" s="6">
+        <v>46</v>
+      </c>
+      <c r="O140" s="6">
+        <v>960</v>
+      </c>
+      <c r="P140" s="6">
+        <v>55</v>
+      </c>
+      <c r="Q140" s="42"/>
+    </row>
+    <row r="141" spans="1:17">
+      <c r="A141" s="8">
+        <v>46183</v>
+      </c>
+      <c r="B141" s="6">
+        <v>1172</v>
+      </c>
+      <c r="C141" s="6">
+        <v>45</v>
+      </c>
+      <c r="D141" s="6">
+        <v>55</v>
+      </c>
+      <c r="E141" s="6">
+        <v>103</v>
+      </c>
+      <c r="F141" s="6">
+        <v>422</v>
+      </c>
+      <c r="G141" s="6">
+        <v>115</v>
+      </c>
+      <c r="H141" s="6">
+        <v>97</v>
+      </c>
+      <c r="I141" s="6">
+        <v>95</v>
+      </c>
+      <c r="J141" s="6">
+        <v>68</v>
+      </c>
+      <c r="K141" s="6">
+        <v>25</v>
+      </c>
+      <c r="L141" s="6"/>
+      <c r="M141" s="6"/>
+      <c r="N141" s="6">
+        <v>126</v>
+      </c>
+      <c r="O141" s="6">
+        <v>1019</v>
+      </c>
+      <c r="P141" s="6">
+        <v>27</v>
+      </c>
+      <c r="Q141" s="42"/>
+    </row>
+    <row r="142" spans="1:17">
+      <c r="A142" s="8">
+        <v>46184</v>
+      </c>
+      <c r="B142" s="6">
+        <v>1188</v>
+      </c>
+      <c r="C142" s="6">
+        <v>55</v>
+      </c>
+      <c r="D142" s="6">
+        <v>90</v>
+      </c>
+      <c r="E142" s="6">
+        <v>77</v>
+      </c>
+      <c r="F142" s="6">
+        <v>386</v>
+      </c>
+      <c r="G142" s="6">
+        <v>114</v>
+      </c>
+      <c r="H142" s="6">
+        <v>90</v>
+      </c>
+      <c r="I142" s="6">
+        <v>101</v>
+      </c>
+      <c r="J142" s="6">
+        <v>127</v>
+      </c>
+      <c r="K142" s="6">
+        <v>40</v>
+      </c>
+      <c r="L142" s="6"/>
+      <c r="M142" s="6"/>
+      <c r="N142" s="6">
+        <v>108</v>
+      </c>
+      <c r="O142" s="6">
+        <v>947</v>
+      </c>
+      <c r="P142" s="6">
+        <v>133</v>
+      </c>
+      <c r="Q142" s="42"/>
+    </row>
+    <row r="143" spans="1:17">
+      <c r="A143" s="8">
+        <v>46185</v>
+      </c>
+      <c r="B143" s="6">
+        <v>1216</v>
+      </c>
+      <c r="C143" s="6">
+        <v>74</v>
+      </c>
+      <c r="D143" s="6">
+        <v>89</v>
+      </c>
+      <c r="E143" s="6">
+        <v>88</v>
+      </c>
+      <c r="F143" s="6">
+        <v>292</v>
+      </c>
+      <c r="G143" s="6">
+        <v>66</v>
+      </c>
+      <c r="H143" s="6">
+        <v>120</v>
+      </c>
+      <c r="I143" s="6">
+        <v>129</v>
+      </c>
+      <c r="J143" s="6">
+        <v>131</v>
+      </c>
+      <c r="K143" s="6">
+        <v>41</v>
+      </c>
+      <c r="L143" s="6"/>
+      <c r="M143" s="6"/>
+      <c r="N143" s="6">
+        <v>186</v>
+      </c>
+      <c r="O143" s="6">
+        <v>908</v>
+      </c>
+      <c r="P143" s="6">
+        <v>122</v>
+      </c>
+      <c r="Q143" s="42"/>
+    </row>
+    <row r="144" spans="1:17">
+      <c r="A144" s="8">
+        <v>46186</v>
+      </c>
+      <c r="B144" s="6">
+        <v>3260</v>
+      </c>
+      <c r="C144" s="6">
+        <v>140</v>
+      </c>
+      <c r="D144" s="6">
+        <v>223</v>
+      </c>
+      <c r="E144" s="6">
+        <v>154</v>
+      </c>
+      <c r="F144" s="6">
+        <v>169</v>
+      </c>
+      <c r="G144" s="6">
+        <v>312</v>
+      </c>
+      <c r="H144" s="6">
+        <v>340</v>
+      </c>
+      <c r="I144" s="6">
+        <v>317</v>
+      </c>
+      <c r="J144" s="6">
+        <v>280</v>
+      </c>
+      <c r="K144" s="6">
+        <v>262</v>
+      </c>
+      <c r="L144" s="6">
+        <v>251</v>
+      </c>
+      <c r="M144" s="6">
+        <v>267</v>
+      </c>
+      <c r="N144" s="6">
+        <v>450</v>
+      </c>
+      <c r="O144" s="6">
+        <v>2241</v>
+      </c>
+      <c r="P144" s="6">
+        <v>569</v>
+      </c>
+      <c r="Q144" s="42"/>
+    </row>
+    <row r="145" spans="1:17">
+      <c r="A145" s="8">
+        <v>46187</v>
+      </c>
+      <c r="B145" s="6">
+        <v>1940</v>
+      </c>
+      <c r="C145" s="6">
+        <v>156</v>
+      </c>
+      <c r="D145" s="6">
+        <v>156</v>
+      </c>
+      <c r="E145" s="6">
+        <v>124</v>
+      </c>
+      <c r="F145" s="6">
+        <v>163</v>
+      </c>
+      <c r="G145" s="6">
+        <v>267</v>
+      </c>
+      <c r="H145" s="6">
+        <v>274</v>
+      </c>
+      <c r="I145" s="6">
+        <v>205</v>
+      </c>
+      <c r="J145" s="6">
+        <v>137</v>
+      </c>
+      <c r="K145" s="6">
+        <v>46</v>
+      </c>
+      <c r="L145" s="6"/>
+      <c r="M145" s="6"/>
+      <c r="N145" s="6">
+        <v>412</v>
+      </c>
+      <c r="O145" s="6">
+        <v>1076</v>
+      </c>
+      <c r="P145" s="6">
+        <v>452</v>
+      </c>
+      <c r="Q145" s="42"/>
+    </row>
+    <row r="146" spans="1:17">
+      <c r="A146" s="8">
+        <v>46189</v>
+      </c>
+      <c r="B146" s="6">
+        <v>734</v>
+      </c>
+      <c r="C146" s="6">
+        <v>73</v>
+      </c>
+      <c r="D146" s="6">
+        <v>33</v>
+      </c>
+      <c r="E146" s="6">
+        <v>89</v>
+      </c>
+      <c r="F146" s="6">
+        <v>194</v>
+      </c>
+      <c r="G146" s="6">
+        <v>71</v>
+      </c>
+      <c r="H146" s="6">
+        <v>55</v>
+      </c>
+      <c r="I146" s="6">
+        <v>57</v>
+      </c>
+      <c r="J146" s="6">
+        <v>64</v>
+      </c>
+      <c r="K146" s="6">
+        <v>33</v>
+      </c>
+      <c r="L146" s="6"/>
+      <c r="M146" s="6"/>
+      <c r="N146" s="6">
+        <v>65</v>
+      </c>
+      <c r="O146" s="6">
+        <v>601</v>
+      </c>
+      <c r="P146" s="6">
+        <v>68</v>
+      </c>
+      <c r="Q146" s="42"/>
+    </row>
+    <row r="147" spans="1:17">
+      <c r="A147" s="8">
+        <v>46190</v>
+      </c>
+      <c r="B147" s="6">
+        <v>794</v>
+      </c>
+      <c r="C147" s="6">
+        <v>62</v>
+      </c>
+      <c r="D147" s="6">
+        <v>42</v>
+      </c>
+      <c r="E147" s="6">
+        <v>86</v>
+      </c>
+      <c r="F147" s="6">
+        <v>174</v>
+      </c>
+      <c r="G147" s="6">
+        <v>59</v>
+      </c>
+      <c r="H147" s="6">
+        <v>93</v>
+      </c>
+      <c r="I147" s="6">
+        <v>82</v>
+      </c>
+      <c r="J147" s="6">
+        <v>120</v>
+      </c>
+      <c r="K147" s="6">
+        <v>36</v>
+      </c>
+      <c r="L147" s="6"/>
+      <c r="M147" s="6"/>
+      <c r="N147" s="6">
+        <v>40</v>
+      </c>
+      <c r="O147" s="6">
+        <v>632</v>
+      </c>
+      <c r="P147" s="6">
+        <v>122</v>
+      </c>
+      <c r="Q147" s="42"/>
+    </row>
+    <row r="148" spans="1:17">
+      <c r="A148" s="8">
+        <v>46191</v>
+      </c>
+      <c r="B148" s="6">
+        <v>667</v>
+      </c>
+      <c r="C148" s="6">
+        <v>64</v>
+      </c>
+      <c r="D148" s="6">
+        <v>44</v>
+      </c>
+      <c r="E148" s="6">
+        <v>68</v>
+      </c>
+      <c r="F148" s="6">
+        <v>142</v>
+      </c>
+      <c r="G148" s="6">
+        <v>51</v>
+      </c>
+      <c r="H148" s="6">
+        <v>59</v>
+      </c>
+      <c r="I148" s="6">
+        <v>45</v>
+      </c>
+      <c r="J148" s="6">
+        <v>45</v>
+      </c>
+      <c r="K148" s="6">
+        <v>21</v>
+      </c>
+      <c r="L148" s="6"/>
+      <c r="M148" s="6"/>
+      <c r="N148" s="6">
+        <v>128</v>
+      </c>
+      <c r="O148" s="6">
+        <v>480</v>
+      </c>
+      <c r="P148" s="6">
+        <v>59</v>
+      </c>
+      <c r="Q148" s="42"/>
+    </row>
+    <row r="149" spans="1:17">
+      <c r="A149" s="8">
+        <v>46192</v>
+      </c>
+      <c r="B149" s="6">
+        <v>627</v>
+      </c>
+      <c r="C149" s="6">
+        <v>53</v>
+      </c>
+      <c r="D149" s="6">
+        <v>42</v>
+      </c>
+      <c r="E149" s="6">
+        <v>47</v>
+      </c>
+      <c r="F149" s="6">
+        <v>122</v>
+      </c>
+      <c r="G149" s="6">
+        <v>55</v>
+      </c>
+      <c r="H149" s="6">
+        <v>58</v>
+      </c>
+      <c r="I149" s="6">
+        <v>77</v>
+      </c>
+      <c r="J149" s="6">
+        <v>23</v>
+      </c>
+      <c r="K149" s="6"/>
+      <c r="L149" s="6"/>
+      <c r="M149" s="6"/>
+      <c r="N149" s="6">
+        <v>142</v>
+      </c>
+      <c r="O149" s="6">
+        <v>415</v>
+      </c>
+      <c r="P149" s="6">
+        <v>62</v>
+      </c>
+      <c r="Q149" s="42"/>
+    </row>
+    <row r="150" spans="1:17">
+      <c r="A150" s="8">
+        <v>46193</v>
+      </c>
+      <c r="B150" s="6">
+        <v>1030</v>
+      </c>
+      <c r="C150" s="6">
+        <v>37</v>
+      </c>
+      <c r="D150" s="6">
+        <v>22</v>
+      </c>
+      <c r="E150" s="6">
+        <v>26</v>
+      </c>
+      <c r="F150" s="6">
+        <v>50</v>
+      </c>
+      <c r="G150" s="6">
+        <v>72</v>
+      </c>
+      <c r="H150" s="6">
+        <v>82</v>
+      </c>
+      <c r="I150" s="6">
+        <v>120</v>
+      </c>
+      <c r="J150" s="6">
+        <v>162</v>
+      </c>
+      <c r="K150" s="6">
+        <v>90</v>
+      </c>
+      <c r="L150" s="6">
+        <v>88</v>
+      </c>
+      <c r="M150" s="6">
+        <v>82</v>
+      </c>
+      <c r="N150" s="6">
+        <v>136</v>
+      </c>
+      <c r="O150" s="6">
+        <v>746</v>
+      </c>
+      <c r="P150" s="6">
+        <v>148</v>
+      </c>
+      <c r="Q150" s="42"/>
+    </row>
+    <row r="151" spans="1:17">
+      <c r="A151" s="8">
+        <v>46194</v>
+      </c>
+      <c r="B151" s="6">
+        <v>2784</v>
+      </c>
+      <c r="C151" s="6">
+        <v>219</v>
+      </c>
+      <c r="D151" s="6">
+        <v>157</v>
+      </c>
+      <c r="E151" s="6">
+        <v>172</v>
+      </c>
+      <c r="F151" s="6">
+        <v>212</v>
+      </c>
+      <c r="G151" s="6">
+        <v>313</v>
+      </c>
+      <c r="H151" s="6">
+        <v>428</v>
+      </c>
+      <c r="I151" s="6">
+        <v>351</v>
+      </c>
+      <c r="J151" s="6">
+        <v>312</v>
+      </c>
+      <c r="K151" s="6">
+        <v>149</v>
+      </c>
+      <c r="L151" s="6"/>
+      <c r="M151" s="6"/>
+      <c r="N151" s="6">
+        <v>471</v>
+      </c>
+      <c r="O151" s="6">
+        <v>1727</v>
+      </c>
+      <c r="P151" s="6">
+        <v>586</v>
+      </c>
+      <c r="Q151" s="42"/>
+    </row>
+    <row r="152" spans="1:17">
+      <c r="A152" s="8">
+        <v>46196</v>
+      </c>
+      <c r="B152" s="6">
+        <v>863</v>
+      </c>
+      <c r="C152" s="6">
+        <v>96</v>
+      </c>
+      <c r="D152" s="6">
+        <v>43</v>
+      </c>
+      <c r="E152" s="6">
+        <v>77</v>
+      </c>
+      <c r="F152" s="6">
+        <v>196</v>
+      </c>
+      <c r="G152" s="6">
+        <v>101</v>
+      </c>
+      <c r="H152" s="6">
+        <v>62</v>
+      </c>
+      <c r="I152" s="6">
+        <v>60</v>
+      </c>
+      <c r="J152" s="6">
+        <v>86</v>
+      </c>
+      <c r="K152" s="6">
+        <v>38</v>
+      </c>
+      <c r="L152" s="6"/>
+      <c r="M152" s="6"/>
+      <c r="N152" s="6">
+        <v>104</v>
+      </c>
+      <c r="O152" s="6">
+        <v>675</v>
+      </c>
+      <c r="P152" s="6">
+        <v>84</v>
+      </c>
+      <c r="Q152" s="42"/>
+    </row>
+    <row r="153" spans="1:17">
+      <c r="A153" s="8">
+        <v>46197</v>
+      </c>
+      <c r="B153" s="6">
+        <v>1117</v>
+      </c>
+      <c r="C153" s="6">
+        <v>67</v>
+      </c>
+      <c r="D153" s="6">
+        <v>105</v>
+      </c>
+      <c r="E153" s="6">
+        <v>100</v>
+      </c>
+      <c r="F153" s="6">
+        <v>274</v>
+      </c>
+      <c r="G153" s="6">
+        <v>95</v>
+      </c>
+      <c r="H153" s="6">
+        <v>103</v>
+      </c>
+      <c r="I153" s="6">
+        <v>126</v>
+      </c>
+      <c r="J153" s="6">
+        <v>89</v>
+      </c>
+      <c r="K153" s="6">
+        <v>41</v>
+      </c>
+      <c r="L153" s="6"/>
+      <c r="M153" s="6"/>
+      <c r="N153" s="6">
+        <v>117</v>
+      </c>
+      <c r="O153" s="6">
+        <v>863</v>
+      </c>
+      <c r="P153" s="6">
+        <v>137</v>
+      </c>
+      <c r="Q153" s="42"/>
+    </row>
+    <row r="154" spans="1:17">
+      <c r="A154" s="8">
+        <v>46198</v>
+      </c>
+      <c r="B154" s="6">
+        <v>1077</v>
+      </c>
+      <c r="C154" s="6">
+        <v>89</v>
+      </c>
+      <c r="D154" s="6">
+        <v>76</v>
+      </c>
+      <c r="E154" s="6">
+        <v>77</v>
+      </c>
+      <c r="F154" s="6">
+        <v>293</v>
+      </c>
+      <c r="G154" s="6">
+        <v>107</v>
+      </c>
+      <c r="H154" s="6">
+        <v>114</v>
+      </c>
+      <c r="I154" s="6">
+        <v>113</v>
+      </c>
+      <c r="J154" s="6">
+        <v>122</v>
+      </c>
+      <c r="K154" s="6">
+        <v>18</v>
+      </c>
+      <c r="L154" s="6"/>
+      <c r="M154" s="6"/>
+      <c r="N154" s="6">
+        <v>68</v>
+      </c>
+      <c r="O154" s="6">
+        <v>866</v>
+      </c>
+      <c r="P154" s="6">
+        <v>143</v>
+      </c>
+      <c r="Q154" s="42"/>
+    </row>
+    <row r="155" spans="1:17">
+      <c r="A155" s="8">
+        <v>46199</v>
+      </c>
+      <c r="B155" s="6">
+        <v>1141</v>
+      </c>
+      <c r="C155" s="6">
+        <v>79</v>
+      </c>
+      <c r="D155" s="6">
+        <v>118</v>
+      </c>
+      <c r="E155" s="6">
+        <v>95</v>
+      </c>
+      <c r="F155" s="6">
+        <v>248</v>
+      </c>
+      <c r="G155" s="6">
+        <v>119</v>
+      </c>
+      <c r="H155" s="6">
+        <v>81</v>
+      </c>
+      <c r="I155" s="6">
+        <v>99</v>
+      </c>
+      <c r="J155" s="6">
+        <v>98</v>
+      </c>
+      <c r="K155" s="6">
+        <v>40</v>
+      </c>
+      <c r="L155" s="6"/>
+      <c r="M155" s="6"/>
+      <c r="N155" s="6">
+        <v>164</v>
+      </c>
+      <c r="O155" s="6">
+        <v>878</v>
+      </c>
+      <c r="P155" s="6">
+        <v>99</v>
+      </c>
+      <c r="Q155" s="42"/>
+    </row>
+    <row r="156" spans="1:17">
+      <c r="A156" s="8">
+        <v>46200</v>
+      </c>
+      <c r="B156" s="6">
+        <v>2597</v>
+      </c>
+      <c r="C156" s="6">
+        <v>168</v>
+      </c>
+      <c r="D156" s="6">
+        <v>134</v>
+      </c>
+      <c r="E156" s="6">
+        <v>108</v>
+      </c>
+      <c r="F156" s="6">
+        <v>183</v>
+      </c>
+      <c r="G156" s="6">
+        <v>184</v>
+      </c>
+      <c r="H156" s="6">
+        <v>251</v>
+      </c>
+      <c r="I156" s="6">
+        <v>266</v>
+      </c>
+      <c r="J156" s="6">
+        <v>230</v>
+      </c>
+      <c r="K156" s="6">
+        <v>177</v>
+      </c>
+      <c r="L156" s="6">
+        <v>197</v>
+      </c>
+      <c r="M156" s="6">
+        <v>242</v>
+      </c>
+      <c r="N156" s="6">
+        <v>384</v>
+      </c>
+      <c r="O156" s="6">
+        <v>1569</v>
+      </c>
+      <c r="P156" s="6">
+        <v>644</v>
+      </c>
+      <c r="Q156" s="42"/>
+    </row>
+    <row r="157" spans="1:17">
+      <c r="A157" s="8">
+        <v>46201</v>
+      </c>
+      <c r="B157" s="6">
+        <v>1690</v>
+      </c>
+      <c r="C157" s="6">
+        <v>181</v>
+      </c>
+      <c r="D157" s="6">
+        <v>126</v>
+      </c>
+      <c r="E157" s="6">
+        <v>85</v>
+      </c>
+      <c r="F157" s="6">
+        <v>193</v>
+      </c>
+      <c r="G157" s="6">
+        <v>144</v>
+      </c>
+      <c r="H157" s="6">
+        <v>206</v>
+      </c>
+      <c r="I157" s="6">
+        <v>165</v>
+      </c>
+      <c r="J157" s="6">
+        <v>167</v>
+      </c>
+      <c r="K157" s="6">
+        <v>58</v>
+      </c>
+      <c r="L157" s="6"/>
+      <c r="M157" s="6"/>
+      <c r="N157" s="6">
+        <v>365</v>
+      </c>
+      <c r="O157" s="6">
+        <v>966</v>
+      </c>
+      <c r="P157" s="6">
+        <v>359</v>
+      </c>
+      <c r="Q157" s="42"/>
+    </row>
+    <row r="158" spans="1:17">
+      <c r="A158" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B158" s="6">
+        <v>667</v>
+      </c>
+      <c r="C158" s="6">
+        <v>94</v>
+      </c>
+      <c r="D158" s="6">
+        <v>48</v>
+      </c>
+      <c r="E158" s="6">
+        <v>64</v>
+      </c>
+      <c r="F158" s="6">
+        <v>136</v>
+      </c>
+      <c r="G158" s="6">
+        <v>63</v>
+      </c>
+      <c r="H158" s="6">
+        <v>54</v>
+      </c>
+      <c r="I158" s="6">
+        <v>61</v>
+      </c>
+      <c r="J158" s="6">
+        <v>65</v>
+      </c>
+      <c r="K158" s="6">
+        <v>31</v>
+      </c>
+      <c r="L158" s="6"/>
+      <c r="M158" s="6"/>
+      <c r="N158" s="6">
+        <v>51</v>
+      </c>
+      <c r="O158" s="6">
+        <v>550</v>
+      </c>
+      <c r="P158" s="6">
+        <v>66</v>
+      </c>
+      <c r="Q158" s="42"/>
+    </row>
+    <row r="159" spans="1:17">
+      <c r="A159" s="8">
+        <v>46204</v>
+      </c>
+      <c r="B159" s="6">
+        <v>597</v>
+      </c>
+      <c r="C159" s="6">
+        <v>52</v>
+      </c>
+      <c r="D159" s="6">
+        <v>73</v>
+      </c>
+      <c r="E159" s="6">
+        <v>53</v>
+      </c>
+      <c r="F159" s="6">
+        <v>88</v>
+      </c>
+      <c r="G159" s="6">
+        <v>65</v>
+      </c>
+      <c r="H159" s="6">
+        <v>43</v>
+      </c>
+      <c r="I159" s="6">
+        <v>50</v>
+      </c>
+      <c r="J159" s="6">
+        <v>59</v>
+      </c>
+      <c r="K159" s="6">
+        <v>15</v>
+      </c>
+      <c r="L159" s="6"/>
+      <c r="M159" s="6"/>
+      <c r="N159" s="6">
+        <v>82</v>
+      </c>
+      <c r="O159" s="6">
+        <v>493</v>
+      </c>
+      <c r="P159" s="6">
+        <v>22</v>
+      </c>
+      <c r="Q159" s="42"/>
+    </row>
+    <row r="160" spans="1:17">
+      <c r="A160" s="8">
+        <v>46205</v>
+      </c>
+      <c r="B160" s="6">
+        <v>793</v>
+      </c>
+      <c r="C160" s="6">
+        <v>47</v>
+      </c>
+      <c r="D160" s="6">
+        <v>46</v>
+      </c>
+      <c r="E160" s="6">
+        <v>72</v>
+      </c>
+      <c r="F160" s="6">
+        <v>295</v>
+      </c>
+      <c r="G160" s="6">
+        <v>63</v>
+      </c>
+      <c r="H160" s="6">
+        <v>60</v>
+      </c>
+      <c r="I160" s="6">
+        <v>65</v>
+      </c>
+      <c r="J160" s="6">
+        <v>53</v>
+      </c>
+      <c r="K160" s="6">
+        <v>13</v>
+      </c>
+      <c r="L160" s="6"/>
+      <c r="M160" s="6"/>
+      <c r="N160" s="6">
+        <v>43</v>
+      </c>
+      <c r="O160" s="6">
+        <v>714</v>
+      </c>
+      <c r="P160" s="6">
+        <v>36</v>
+      </c>
+      <c r="Q160" s="42"/>
+    </row>
+    <row r="161" spans="1:17">
+      <c r="A161" s="8">
+        <v>46206</v>
+      </c>
+      <c r="B161" s="6">
+        <v>822</v>
+      </c>
+      <c r="C161" s="6">
+        <v>32</v>
+      </c>
+      <c r="D161" s="6">
+        <v>40</v>
+      </c>
+      <c r="E161" s="6">
+        <v>55</v>
+      </c>
+      <c r="F161" s="6">
+        <v>193</v>
+      </c>
+      <c r="G161" s="6">
+        <v>83</v>
+      </c>
+      <c r="H161" s="6">
+        <v>67</v>
+      </c>
+      <c r="I161" s="6">
+        <v>62</v>
+      </c>
+      <c r="J161" s="6">
+        <v>67</v>
+      </c>
+      <c r="K161" s="6">
+        <v>38</v>
+      </c>
+      <c r="L161" s="6"/>
+      <c r="M161" s="6"/>
+      <c r="N161" s="6">
+        <v>146</v>
+      </c>
+      <c r="O161" s="6">
+        <v>624</v>
+      </c>
+      <c r="P161" s="6">
+        <v>52</v>
+      </c>
+      <c r="Q161" s="42"/>
+    </row>
+    <row r="162" spans="1:17">
+      <c r="A162" s="8">
+        <v>46207</v>
+      </c>
+      <c r="B162" s="6">
+        <v>2876</v>
+      </c>
+      <c r="C162" s="6">
+        <v>125</v>
+      </c>
+      <c r="D162" s="6">
+        <v>154</v>
+      </c>
+      <c r="E162" s="6">
+        <v>133</v>
+      </c>
+      <c r="F162" s="6">
+        <v>178</v>
+      </c>
+      <c r="G162" s="6">
+        <v>332</v>
+      </c>
+      <c r="H162" s="6">
+        <v>282</v>
+      </c>
+      <c r="I162" s="6">
+        <v>264</v>
+      </c>
+      <c r="J162" s="6">
+        <v>229</v>
+      </c>
+      <c r="K162" s="6">
+        <v>209</v>
+      </c>
+      <c r="L162" s="6">
+        <v>225</v>
+      </c>
+      <c r="M162" s="6">
+        <v>256</v>
+      </c>
+      <c r="N162" s="6">
+        <v>374</v>
+      </c>
+      <c r="O162" s="6">
+        <v>1680</v>
+      </c>
+      <c r="P162" s="6">
+        <v>822</v>
+      </c>
+      <c r="Q162" s="42"/>
+    </row>
+    <row r="163" spans="1:17">
+      <c r="A163" s="8">
+        <v>46208</v>
+      </c>
+      <c r="B163" s="6">
+        <v>1882</v>
+      </c>
+      <c r="C163" s="6">
+        <v>184</v>
+      </c>
+      <c r="D163" s="6">
+        <v>194</v>
+      </c>
+      <c r="E163" s="6">
+        <v>145</v>
+      </c>
+      <c r="F163" s="6">
+        <v>189</v>
+      </c>
+      <c r="G163" s="6">
+        <v>236</v>
+      </c>
+      <c r="H163" s="6">
+        <v>215</v>
+      </c>
+      <c r="I163" s="6">
+        <v>203</v>
+      </c>
+      <c r="J163" s="6">
+        <v>161</v>
+      </c>
+      <c r="K163" s="6">
+        <v>28</v>
+      </c>
+      <c r="L163" s="6"/>
+      <c r="M163" s="6"/>
+      <c r="N163" s="6">
+        <v>327</v>
+      </c>
+      <c r="O163" s="6">
+        <v>815</v>
+      </c>
+      <c r="P163" s="6">
+        <v>740</v>
+      </c>
+      <c r="Q163" s="42"/>
+    </row>
+    <row r="164" spans="1:17">
+      <c r="A164" s="8">
+        <v>46210</v>
+      </c>
+      <c r="B164" s="6">
+        <v>583</v>
+      </c>
+      <c r="C164" s="6">
+        <v>28</v>
+      </c>
+      <c r="D164" s="6">
+        <v>32</v>
+      </c>
+      <c r="E164" s="6">
+        <v>53</v>
+      </c>
+      <c r="F164" s="6">
+        <v>100</v>
+      </c>
+      <c r="G164" s="6">
+        <v>55</v>
+      </c>
+      <c r="H164" s="6">
+        <v>53</v>
+      </c>
+      <c r="I164" s="6">
+        <v>48</v>
+      </c>
+      <c r="J164" s="6">
+        <v>85</v>
+      </c>
+      <c r="K164" s="6">
+        <v>28</v>
+      </c>
+      <c r="L164" s="6"/>
+      <c r="M164" s="6"/>
+      <c r="N164" s="6">
+        <v>101</v>
+      </c>
+      <c r="O164" s="6">
+        <v>384</v>
+      </c>
+      <c r="P164" s="6">
+        <v>98</v>
+      </c>
+      <c r="Q164" s="42"/>
+    </row>
+    <row r="165" spans="1:17">
+      <c r="A165" s="8">
+        <v>46211</v>
+      </c>
+      <c r="B165" s="6">
+        <v>510</v>
+      </c>
+      <c r="C165" s="6">
+        <v>17</v>
+      </c>
+      <c r="D165" s="6">
+        <v>23</v>
+      </c>
+      <c r="E165" s="6">
+        <v>38</v>
+      </c>
+      <c r="F165" s="6">
+        <v>95</v>
+      </c>
+      <c r="G165" s="6">
+        <v>77</v>
+      </c>
+      <c r="H165" s="6">
+        <v>73</v>
+      </c>
+      <c r="I165" s="6">
+        <v>62</v>
+      </c>
+      <c r="J165" s="6">
+        <v>74</v>
+      </c>
+      <c r="K165" s="6">
+        <v>13</v>
+      </c>
+      <c r="L165" s="6"/>
+      <c r="M165" s="6"/>
+      <c r="N165" s="6">
+        <v>38</v>
+      </c>
+      <c r="O165" s="6">
+        <v>384</v>
+      </c>
+      <c r="P165" s="6">
+        <v>88</v>
+      </c>
+      <c r="Q165" s="42"/>
+    </row>
+    <row r="166" spans="1:17">
+      <c r="A166" s="8">
+        <v>46212</v>
+      </c>
+      <c r="B166" s="6">
+        <v>383</v>
+      </c>
+      <c r="C166" s="6">
+        <v>48</v>
+      </c>
+      <c r="D166" s="6">
+        <v>16</v>
+      </c>
+      <c r="E166" s="6">
+        <v>18</v>
+      </c>
+      <c r="F166" s="6">
+        <v>41</v>
+      </c>
+      <c r="G166" s="6">
+        <v>19</v>
+      </c>
+      <c r="H166" s="6">
+        <v>30</v>
+      </c>
+      <c r="I166" s="6">
+        <v>58</v>
+      </c>
+      <c r="J166" s="6">
+        <v>67</v>
+      </c>
+      <c r="K166" s="6">
+        <v>36</v>
+      </c>
+      <c r="L166" s="6"/>
+      <c r="M166" s="6"/>
+      <c r="N166" s="6">
+        <v>50</v>
+      </c>
+      <c r="O166" s="6">
+        <v>243</v>
+      </c>
+      <c r="P166" s="6">
+        <v>90</v>
+      </c>
+      <c r="Q166" s="42"/>
+    </row>
+    <row r="167" spans="1:17">
+      <c r="A167" s="8">
+        <v>46213</v>
+      </c>
+      <c r="B167" s="6">
+        <v>556</v>
+      </c>
+      <c r="C167" s="6">
+        <v>46</v>
+      </c>
+      <c r="D167" s="6">
+        <v>19</v>
+      </c>
+      <c r="E167" s="6">
+        <v>40</v>
+      </c>
+      <c r="F167" s="6">
+        <v>127</v>
+      </c>
+      <c r="G167" s="6">
+        <v>31</v>
+      </c>
+      <c r="H167" s="6">
+        <v>53</v>
+      </c>
+      <c r="I167" s="6">
+        <v>66</v>
+      </c>
+      <c r="J167" s="6">
+        <v>55</v>
+      </c>
+      <c r="K167" s="6">
+        <v>16</v>
+      </c>
+      <c r="L167" s="6"/>
+      <c r="M167" s="6"/>
+      <c r="N167" s="6">
+        <v>103</v>
+      </c>
+      <c r="O167" s="6">
+        <v>337</v>
+      </c>
+      <c r="P167" s="6">
+        <v>116</v>
+      </c>
+      <c r="Q167" s="42"/>
+    </row>
+    <row r="168" spans="1:17">
+      <c r="A168" s="8">
+        <v>46214</v>
+      </c>
+      <c r="B168" s="6">
+        <v>1731</v>
+      </c>
+      <c r="C168" s="6">
+        <v>178</v>
+      </c>
+      <c r="D168" s="6">
+        <v>87</v>
+      </c>
+      <c r="E168" s="6">
+        <v>68</v>
+      </c>
+      <c r="F168" s="6">
+        <v>105</v>
+      </c>
+      <c r="G168" s="6">
+        <v>146</v>
+      </c>
+      <c r="H168" s="6">
+        <v>162</v>
+      </c>
+      <c r="I168" s="6">
+        <v>163</v>
+      </c>
+      <c r="J168" s="6">
+        <v>155</v>
+      </c>
+      <c r="K168" s="6">
+        <v>101</v>
+      </c>
+      <c r="L168" s="6">
+        <v>94</v>
+      </c>
+      <c r="M168" s="6">
+        <v>189</v>
+      </c>
+      <c r="N168" s="6">
+        <v>200</v>
+      </c>
+      <c r="O168" s="6">
+        <v>1015</v>
+      </c>
+      <c r="P168" s="6">
+        <v>516</v>
+      </c>
+      <c r="Q168" s="42"/>
+    </row>
+    <row r="169" spans="1:17">
+      <c r="A169" s="8">
+        <v>46215</v>
+      </c>
+      <c r="B169" s="6">
+        <v>1306</v>
+      </c>
+      <c r="C169" s="6">
+        <v>140</v>
+      </c>
+      <c r="D169" s="6">
+        <v>134</v>
+      </c>
+      <c r="E169" s="6">
+        <v>79</v>
+      </c>
+      <c r="F169" s="6">
+        <v>75</v>
+      </c>
+      <c r="G169" s="6">
+        <v>175</v>
+      </c>
+      <c r="H169" s="6">
+        <v>127</v>
+      </c>
+      <c r="I169" s="6">
+        <v>186</v>
+      </c>
+      <c r="J169" s="6">
+        <v>114</v>
+      </c>
+      <c r="K169" s="6">
+        <v>40</v>
+      </c>
+      <c r="L169" s="6"/>
+      <c r="M169" s="6"/>
+      <c r="N169" s="6">
+        <v>236</v>
+      </c>
+      <c r="O169" s="6">
+        <v>537</v>
+      </c>
+      <c r="P169" s="6">
+        <v>533</v>
+      </c>
+      <c r="Q169" s="42"/>
+    </row>
+    <row r="170" spans="1:17">
+      <c r="A170" s="8">
+        <v>46217</v>
+      </c>
+      <c r="B170" s="6">
+        <v>477</v>
+      </c>
+      <c r="C170" s="6">
+        <v>54</v>
+      </c>
+      <c r="D170" s="6">
+        <v>38</v>
+      </c>
+      <c r="E170" s="6">
+        <v>45</v>
+      </c>
+      <c r="F170" s="6">
+        <v>84</v>
+      </c>
+      <c r="G170" s="6">
+        <v>45</v>
+      </c>
+      <c r="H170" s="6">
+        <v>49</v>
+      </c>
+      <c r="I170" s="6">
+        <v>77</v>
+      </c>
+      <c r="J170" s="6">
+        <v>32</v>
+      </c>
+      <c r="K170" s="6">
+        <v>16</v>
+      </c>
+      <c r="L170" s="6"/>
+      <c r="M170" s="6"/>
+      <c r="N170" s="6">
+        <v>37</v>
+      </c>
+      <c r="O170" s="6">
+        <v>297</v>
+      </c>
+      <c r="P170" s="6">
+        <v>143</v>
+      </c>
+      <c r="Q170" s="42"/>
+    </row>
+    <row r="171" spans="1:17">
+      <c r="A171" s="8">
+        <v>46218</v>
+      </c>
+      <c r="B171" s="6">
+        <v>550</v>
+      </c>
+      <c r="C171" s="6">
+        <v>23</v>
+      </c>
+      <c r="D171" s="6">
+        <v>28</v>
+      </c>
+      <c r="E171" s="6">
+        <v>17</v>
+      </c>
+      <c r="F171" s="6">
+        <v>113</v>
+      </c>
+      <c r="G171" s="6">
+        <v>57</v>
+      </c>
+      <c r="H171" s="6">
+        <v>65</v>
+      </c>
+      <c r="I171" s="6">
+        <v>76</v>
+      </c>
+      <c r="J171" s="6">
+        <v>98</v>
+      </c>
+      <c r="K171" s="6"/>
+      <c r="L171" s="6"/>
+      <c r="M171" s="6"/>
+      <c r="N171" s="6">
+        <v>73</v>
+      </c>
+      <c r="O171" s="6">
+        <v>324</v>
+      </c>
+      <c r="P171" s="6">
+        <v>153</v>
+      </c>
+      <c r="Q171" s="42"/>
+    </row>
+    <row r="172" spans="1:17">
+      <c r="A172" s="8">
+        <v>46219</v>
+      </c>
+      <c r="B172" s="6">
+        <v>658</v>
+      </c>
+      <c r="C172" s="6">
+        <v>66</v>
+      </c>
+      <c r="D172" s="6">
+        <v>77</v>
+      </c>
+      <c r="E172" s="6">
+        <v>23</v>
+      </c>
+      <c r="F172" s="6">
+        <v>106</v>
+      </c>
+      <c r="G172" s="6">
+        <v>63</v>
+      </c>
+      <c r="H172" s="6">
+        <v>55</v>
+      </c>
+      <c r="I172" s="6">
+        <v>40</v>
+      </c>
+      <c r="J172" s="6">
+        <v>77</v>
+      </c>
+      <c r="K172" s="6">
+        <v>36</v>
+      </c>
+      <c r="L172" s="6"/>
+      <c r="M172" s="6"/>
+      <c r="N172" s="6">
+        <v>115</v>
+      </c>
+      <c r="O172" s="6">
+        <v>472</v>
+      </c>
+      <c r="P172" s="6">
+        <v>71</v>
+      </c>
+      <c r="Q172" s="42"/>
+    </row>
+    <row r="173" spans="1:17">
+      <c r="A173" s="8">
+        <v>46220</v>
+      </c>
+      <c r="B173" s="6">
+        <v>2113</v>
+      </c>
+      <c r="C173" s="6">
+        <v>165</v>
+      </c>
+      <c r="D173" s="6">
+        <v>196</v>
+      </c>
+      <c r="E173" s="6">
+        <v>136</v>
+      </c>
+      <c r="F173" s="6">
+        <v>189</v>
+      </c>
+      <c r="G173" s="6">
+        <v>239</v>
+      </c>
+      <c r="H173" s="6">
+        <v>218</v>
+      </c>
+      <c r="I173" s="6">
+        <v>229</v>
+      </c>
+      <c r="J173" s="6">
+        <v>249</v>
+      </c>
+      <c r="K173" s="6">
+        <v>64</v>
+      </c>
+      <c r="L173" s="6"/>
+      <c r="M173" s="6"/>
+      <c r="N173" s="6">
+        <v>428</v>
+      </c>
+      <c r="O173" s="6">
+        <v>1007</v>
+      </c>
+      <c r="P173" s="6">
+        <v>678</v>
+      </c>
+      <c r="Q173" s="42"/>
+    </row>
+    <row r="174" spans="1:17">
+      <c r="A174" s="8">
+        <v>46221</v>
+      </c>
+      <c r="B174" s="6">
+        <v>1655</v>
+      </c>
+      <c r="C174" s="6">
+        <v>73</v>
+      </c>
+      <c r="D174" s="6">
+        <v>55</v>
+      </c>
+      <c r="E174" s="6">
+        <v>97</v>
+      </c>
+      <c r="F174" s="6">
+        <v>135</v>
+      </c>
+      <c r="G174" s="6">
+        <v>162</v>
+      </c>
+      <c r="H174" s="6">
+        <v>155</v>
+      </c>
+      <c r="I174" s="6">
+        <v>153</v>
+      </c>
+      <c r="J174" s="6">
+        <v>205</v>
+      </c>
+      <c r="K174" s="6">
+        <v>146</v>
+      </c>
+      <c r="L174" s="6">
+        <v>111</v>
+      </c>
+      <c r="M174" s="6">
+        <v>108</v>
+      </c>
+      <c r="N174" s="6">
+        <v>212</v>
+      </c>
+      <c r="O174" s="6">
+        <v>980</v>
+      </c>
+      <c r="P174" s="6">
+        <v>463</v>
+      </c>
+      <c r="Q174" s="42"/>
+    </row>
+    <row r="175" spans="1:17">
+      <c r="A175" s="8">
+        <v>46222</v>
+      </c>
+      <c r="B175" s="6">
+        <v>1871</v>
+      </c>
+      <c r="C175" s="6">
+        <v>69</v>
+      </c>
+      <c r="D175" s="6">
+        <v>93</v>
+      </c>
+      <c r="E175" s="6">
+        <v>134</v>
+      </c>
+      <c r="F175" s="6">
+        <v>186</v>
+      </c>
+      <c r="G175" s="6">
+        <v>257</v>
+      </c>
+      <c r="H175" s="6">
+        <v>215</v>
+      </c>
+      <c r="I175" s="6">
+        <v>244</v>
+      </c>
+      <c r="J175" s="6">
+        <v>168</v>
+      </c>
+      <c r="K175" s="6">
+        <v>64</v>
+      </c>
+      <c r="L175" s="6"/>
+      <c r="M175" s="6"/>
+      <c r="N175" s="6">
+        <v>441</v>
+      </c>
+      <c r="O175" s="6">
+        <v>920</v>
+      </c>
+      <c r="P175" s="6">
+        <v>510</v>
+      </c>
+      <c r="Q175" s="42"/>
+    </row>
+    <row r="176" spans="1:17">
+      <c r="A176" s="8">
+        <v>46224</v>
+      </c>
+      <c r="B176" s="6">
+        <v>307</v>
+      </c>
+      <c r="C176" s="6">
+        <v>34</v>
+      </c>
+      <c r="D176" s="6">
+        <v>29</v>
+      </c>
+      <c r="E176" s="6">
+        <v>20</v>
+      </c>
+      <c r="F176" s="6">
+        <v>31</v>
+      </c>
+      <c r="G176" s="6">
+        <v>35</v>
+      </c>
+      <c r="H176" s="6">
+        <v>36</v>
+      </c>
+      <c r="I176" s="6">
+        <v>43</v>
+      </c>
+      <c r="J176" s="6">
+        <v>50</v>
+      </c>
+      <c r="K176" s="6">
+        <v>8</v>
+      </c>
+      <c r="L176" s="6"/>
+      <c r="M176" s="6"/>
+      <c r="N176" s="6">
+        <v>21</v>
+      </c>
+      <c r="O176" s="6">
+        <v>221</v>
+      </c>
+      <c r="P176" s="6">
+        <v>65</v>
+      </c>
+      <c r="Q176" s="42"/>
+    </row>
+    <row r="177" spans="1:243">
+      <c r="A177" s="8">
+        <v>46225</v>
+      </c>
+      <c r="B177" s="6">
+        <v>461</v>
+      </c>
+      <c r="C177" s="6">
+        <v>38</v>
+      </c>
+      <c r="D177" s="6">
+        <v>66</v>
+      </c>
+      <c r="E177" s="6">
+        <v>31</v>
+      </c>
+      <c r="F177" s="6">
+        <v>46</v>
+      </c>
+      <c r="G177" s="6">
+        <v>51</v>
+      </c>
+      <c r="H177" s="6">
+        <v>39</v>
+      </c>
+      <c r="I177" s="6">
+        <v>61</v>
+      </c>
+      <c r="J177" s="6">
+        <v>62</v>
+      </c>
+      <c r="K177" s="6">
+        <v>20</v>
+      </c>
+      <c r="L177" s="6"/>
+      <c r="M177" s="6"/>
+      <c r="N177" s="6">
+        <v>47</v>
+      </c>
+      <c r="O177" s="6">
+        <v>305</v>
+      </c>
+      <c r="P177" s="6">
+        <v>109</v>
+      </c>
+      <c r="Q177" s="42"/>
+    </row>
+    <row r="178" spans="1:243">
+      <c r="A178" s="8">
+        <v>46226</v>
+      </c>
+      <c r="B178" s="6">
+        <v>478</v>
+      </c>
+      <c r="C178" s="6">
+        <v>71</v>
+      </c>
+      <c r="D178" s="6">
+        <v>38</v>
+      </c>
+      <c r="E178" s="6">
+        <v>33</v>
+      </c>
+      <c r="F178" s="6">
+        <v>76</v>
+      </c>
+      <c r="G178" s="6">
+        <v>48</v>
+      </c>
+      <c r="H178" s="6">
+        <v>62</v>
+      </c>
+      <c r="I178" s="6">
+        <v>48</v>
+      </c>
+      <c r="J178" s="6">
+        <v>56</v>
+      </c>
+      <c r="K178" s="6">
+        <v>13</v>
+      </c>
+      <c r="L178" s="6"/>
+      <c r="M178" s="6"/>
+      <c r="N178" s="6">
+        <v>33</v>
+      </c>
+      <c r="O178" s="6">
+        <v>314</v>
+      </c>
+      <c r="P178" s="6">
+        <v>131</v>
+      </c>
+      <c r="Q178" s="42"/>
+    </row>
+    <row r="179" spans="1:243">
+      <c r="A179" s="8">
+        <v>46227</v>
+      </c>
+      <c r="B179" s="6">
+        <v>546</v>
+      </c>
+      <c r="C179" s="6">
+        <v>55</v>
+      </c>
+      <c r="D179" s="6">
+        <v>30</v>
+      </c>
+      <c r="E179" s="6">
+        <v>46</v>
+      </c>
+      <c r="F179" s="6">
+        <v>102</v>
+      </c>
+      <c r="G179" s="6">
+        <v>67</v>
+      </c>
+      <c r="H179" s="6">
+        <v>57</v>
+      </c>
+      <c r="I179" s="6">
+        <v>46</v>
+      </c>
+      <c r="J179" s="6">
+        <v>50</v>
+      </c>
+      <c r="K179" s="6">
+        <v>35</v>
+      </c>
+      <c r="L179" s="6"/>
+      <c r="M179" s="6"/>
+      <c r="N179" s="6">
+        <v>58</v>
+      </c>
+      <c r="O179" s="6">
+        <v>406</v>
+      </c>
+      <c r="P179" s="6">
+        <v>82</v>
+      </c>
+      <c r="Q179" s="42"/>
+    </row>
+    <row r="180" spans="1:243">
+      <c r="A180" s="8">
+        <v>46228</v>
+      </c>
+      <c r="B180" s="6">
+        <v>1549</v>
+      </c>
+      <c r="C180" s="6">
+        <v>114</v>
+      </c>
+      <c r="D180" s="6">
+        <v>62</v>
+      </c>
+      <c r="E180" s="6">
+        <v>87</v>
+      </c>
+      <c r="F180" s="6">
+        <v>82</v>
+      </c>
+      <c r="G180" s="6">
+        <v>124</v>
+      </c>
+      <c r="H180" s="6">
+        <v>151</v>
+      </c>
+      <c r="I180" s="6">
+        <v>149</v>
+      </c>
+      <c r="J180" s="6">
+        <v>139</v>
+      </c>
+      <c r="K180" s="6">
+        <v>103</v>
+      </c>
+      <c r="L180" s="6">
+        <v>115</v>
+      </c>
+      <c r="M180" s="6">
+        <v>93</v>
+      </c>
+      <c r="N180" s="6">
+        <v>272</v>
+      </c>
+      <c r="O180" s="6">
+        <v>1020</v>
+      </c>
+      <c r="P180" s="6">
+        <v>257</v>
+      </c>
+      <c r="Q180" s="42"/>
+    </row>
+    <row r="181" spans="1:243">
+      <c r="A181" s="8">
+        <v>46229</v>
+      </c>
+      <c r="B181" s="6">
+        <v>1368</v>
+      </c>
+      <c r="C181" s="6">
+        <v>92</v>
+      </c>
+      <c r="D181" s="6">
+        <v>102</v>
+      </c>
+      <c r="E181" s="6">
+        <v>107</v>
+      </c>
+      <c r="F181" s="6">
+        <v>109</v>
+      </c>
+      <c r="G181" s="6">
+        <v>127</v>
+      </c>
+      <c r="H181" s="6">
+        <v>150</v>
+      </c>
+      <c r="I181" s="6">
+        <v>126</v>
+      </c>
+      <c r="J181" s="6">
+        <v>127</v>
+      </c>
+      <c r="K181" s="6">
+        <v>66</v>
+      </c>
+      <c r="L181" s="6"/>
+      <c r="M181" s="6"/>
+      <c r="N181" s="6">
+        <v>362</v>
+      </c>
+      <c r="O181" s="6">
+        <v>724</v>
+      </c>
+      <c r="P181" s="6">
+        <v>282</v>
+      </c>
+      <c r="Q181" s="42"/>
+    </row>
+    <row r="182" spans="1:243">
+      <c r="A182" s="8">
+        <v>46231</v>
+      </c>
+      <c r="B182" s="6">
+        <v>670</v>
+      </c>
+      <c r="C182" s="6">
+        <v>56</v>
+      </c>
+      <c r="D182" s="6">
+        <v>61</v>
+      </c>
+      <c r="E182" s="6">
+        <v>36</v>
+      </c>
+      <c r="F182" s="6">
+        <v>102</v>
+      </c>
+      <c r="G182" s="6">
+        <v>80</v>
+      </c>
+      <c r="H182" s="6">
+        <v>70</v>
+      </c>
+      <c r="I182" s="6">
+        <v>52</v>
+      </c>
+      <c r="J182" s="6">
+        <v>51</v>
+      </c>
+      <c r="K182" s="6">
+        <v>17</v>
+      </c>
+      <c r="L182" s="6"/>
+      <c r="M182" s="6"/>
+      <c r="N182" s="6">
+        <v>145</v>
+      </c>
+      <c r="O182" s="6">
+        <v>449</v>
+      </c>
+      <c r="P182" s="6">
+        <v>76</v>
+      </c>
+      <c r="Q182" s="42"/>
+    </row>
+    <row r="183" spans="1:243">
+      <c r="A183" s="8">
+        <v>46232</v>
+      </c>
+      <c r="B183" s="6">
+        <v>481</v>
+      </c>
+      <c r="C183" s="6">
+        <v>33</v>
+      </c>
+      <c r="D183" s="6">
+        <v>50</v>
+      </c>
+      <c r="E183" s="6">
+        <v>30</v>
+      </c>
+      <c r="F183" s="6">
+        <v>75</v>
+      </c>
+      <c r="G183" s="6">
+        <v>63</v>
+      </c>
+      <c r="H183" s="6">
+        <v>56</v>
+      </c>
+      <c r="I183" s="6">
+        <v>43</v>
+      </c>
+      <c r="J183" s="6">
+        <v>35</v>
+      </c>
+      <c r="K183" s="6">
+        <v>25</v>
+      </c>
+      <c r="L183" s="6"/>
+      <c r="M183" s="6"/>
+      <c r="N183" s="6">
+        <v>71</v>
+      </c>
+      <c r="O183" s="6">
+        <v>354</v>
+      </c>
+      <c r="P183" s="6">
+        <v>56</v>
+      </c>
+      <c r="Q183" s="42"/>
+    </row>
+    <row r="184" spans="1:243">
+      <c r="A184" s="8">
+        <v>46233</v>
+      </c>
+      <c r="B184" s="36">
+        <v>674</v>
+      </c>
+      <c r="C184" s="36">
+        <v>58</v>
+      </c>
+      <c r="D184" s="36">
+        <v>39</v>
+      </c>
+      <c r="E184" s="36">
+        <v>49</v>
+      </c>
+      <c r="F184" s="36">
+        <v>106</v>
+      </c>
+      <c r="G184" s="36">
+        <v>64</v>
+      </c>
+      <c r="H184" s="36">
+        <v>76</v>
+      </c>
+      <c r="I184" s="36">
+        <v>86</v>
+      </c>
+      <c r="J184" s="36">
+        <v>50</v>
+      </c>
+      <c r="K184" s="36">
+        <v>26</v>
+      </c>
+      <c r="L184" s="36"/>
+      <c r="M184" s="36"/>
+      <c r="N184" s="36">
+        <v>120</v>
+      </c>
+      <c r="O184" s="36">
+        <v>441</v>
+      </c>
+      <c r="P184" s="36">
+        <v>87</v>
+      </c>
+      <c r="Q184" s="45">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="185" spans="1:243">
+      <c r="A185" s="8">
+        <v>46234</v>
+      </c>
+      <c r="B185" s="36">
+        <v>671</v>
+      </c>
+      <c r="C185" s="36">
+        <v>58</v>
+      </c>
+      <c r="D185" s="36">
+        <v>36</v>
+      </c>
+      <c r="E185" s="36">
+        <v>49</v>
+      </c>
+      <c r="F185" s="36">
+        <v>124</v>
+      </c>
+      <c r="G185" s="36">
+        <v>79</v>
+      </c>
+      <c r="H185" s="36">
+        <v>77</v>
+      </c>
+      <c r="I185" s="36">
+        <v>59</v>
+      </c>
+      <c r="J185" s="36">
+        <v>56</v>
+      </c>
+      <c r="K185" s="36">
+        <v>28</v>
+      </c>
+      <c r="L185" s="36"/>
+      <c r="M185" s="36"/>
+      <c r="N185" s="36">
+        <v>105</v>
+      </c>
+      <c r="O185" s="36">
+        <v>434</v>
+      </c>
+      <c r="P185" s="36">
+        <v>56</v>
+      </c>
+      <c r="Q185" s="45">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="186" spans="1:243">
+      <c r="A186" s="8">
+        <v>46235</v>
+      </c>
+      <c r="B186" s="36">
+        <v>1109</v>
+      </c>
+      <c r="C186" s="36">
+        <v>132</v>
+      </c>
+      <c r="D186" s="36">
+        <v>87</v>
+      </c>
+      <c r="E186" s="36">
+        <v>58</v>
+      </c>
+      <c r="F186" s="36">
+        <v>73</v>
+      </c>
+      <c r="G186" s="36">
+        <v>83</v>
+      </c>
+      <c r="H186" s="36">
+        <v>99</v>
+      </c>
+      <c r="I186" s="36">
+        <v>81</v>
+      </c>
+      <c r="J186" s="36">
+        <v>62</v>
+      </c>
+      <c r="K186" s="36">
+        <v>51</v>
+      </c>
+      <c r="L186" s="36">
+        <v>81</v>
+      </c>
+      <c r="M186" s="36">
+        <v>110</v>
+      </c>
+      <c r="N186" s="36">
+        <v>192</v>
+      </c>
+      <c r="O186" s="36">
+        <v>644</v>
+      </c>
+      <c r="P186" s="36">
+        <v>203</v>
+      </c>
+      <c r="Q186" s="45">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="187" spans="1:243">
+      <c r="A187" s="8">
+        <v>46236</v>
+      </c>
+      <c r="B187" s="36">
+        <v>693</v>
+      </c>
+      <c r="C187" s="36">
+        <v>59</v>
+      </c>
+      <c r="D187" s="36">
+        <v>40</v>
+      </c>
+      <c r="E187" s="36">
+        <v>40</v>
+      </c>
+      <c r="F187" s="36">
+        <v>29</v>
+      </c>
+      <c r="G187" s="36">
+        <v>54</v>
+      </c>
+      <c r="H187" s="36">
+        <v>67</v>
+      </c>
+      <c r="I187" s="36">
+        <v>68</v>
+      </c>
+      <c r="J187" s="36">
+        <v>95</v>
+      </c>
+      <c r="K187" s="36">
+        <v>27</v>
+      </c>
+      <c r="L187" s="36"/>
+      <c r="M187" s="36"/>
+      <c r="N187" s="36">
+        <v>214</v>
+      </c>
+      <c r="O187" s="36">
+        <v>380</v>
+      </c>
+      <c r="P187" s="36">
+        <v>64</v>
+      </c>
+      <c r="Q187" s="45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="188" spans="1:243">
+      <c r="A188" s="35"/>
+      <c r="B188" s="43">
+        <f>SUM(B2:B187)</f>
+        <v>277367</v>
+      </c>
+      <c r="C188" s="43">
+        <f t="shared" ref="B188:P188" si="2">SUM(C2:C186)</f>
+        <v>16618</v>
+      </c>
+      <c r="D188" s="43">
         <f t="shared" si="2"/>
-        <v>15883</v>
-      </c>
-      <c r="F117" s="35">
+        <v>18326</v>
+      </c>
+      <c r="E188" s="43">
         <f t="shared" si="2"/>
-        <v>33842</v>
-      </c>
-      <c r="G117" s="35">
+        <v>22632</v>
+      </c>
+      <c r="F188" s="43">
         <f t="shared" si="2"/>
-        <v>23628</v>
-      </c>
-      <c r="H117" s="35">
+        <v>48432</v>
+      </c>
+      <c r="G188" s="43">
         <f t="shared" si="2"/>
-        <v>23503</v>
-      </c>
-      <c r="I117" s="35">
+        <v>33804</v>
+      </c>
+      <c r="H188" s="43">
         <f t="shared" si="2"/>
-        <v>23108</v>
-      </c>
-      <c r="J117" s="35">
+        <v>33843</v>
+      </c>
+      <c r="I188" s="43">
         <f t="shared" si="2"/>
-        <v>18506</v>
-      </c>
-      <c r="K117" s="35">
+        <v>33462</v>
+      </c>
+      <c r="J188" s="43">
         <f t="shared" si="2"/>
-        <v>4265</v>
-      </c>
-      <c r="L117" s="35">
+        <v>28216</v>
+      </c>
+      <c r="K188" s="43">
         <f t="shared" si="2"/>
-        <v>2159</v>
-      </c>
-      <c r="M117" s="35">
+        <v>8713</v>
+      </c>
+      <c r="L188" s="43">
         <f t="shared" si="2"/>
-        <v>1310</v>
-      </c>
-      <c r="N117" s="35">
+        <v>4404</v>
+      </c>
+      <c r="M188" s="43">
         <f t="shared" si="2"/>
-        <v>12017</v>
-      </c>
-      <c r="O117" s="35">
-        <f>SUM(O2:O116)</f>
-        <v>126057</v>
-      </c>
-      <c r="P117" s="35">
-        <f t="shared" si="2"/>
-        <v>39416</v>
-      </c>
-    </row>
-    <row r="118" spans="1:243">
-      <c r="A118" s="25"/>
-    </row>
-    <row r="119" spans="1:243">
-      <c r="A119" s="4"/>
-      <c r="C119" s="4"/>
-      <c r="D119" s="4"/>
-      <c r="E119" s="4"/>
-      <c r="F119" s="4"/>
-      <c r="G119" s="4"/>
-      <c r="H119" s="4"/>
-      <c r="I119" s="4"/>
-      <c r="J119" s="4"/>
-      <c r="N119" s="4"/>
-      <c r="Q119" s="4"/>
-      <c r="R119" s="4"/>
-      <c r="S119" s="4"/>
-      <c r="T119" s="4"/>
-      <c r="U119" s="4"/>
-      <c r="V119" s="4"/>
-      <c r="W119" s="4"/>
-      <c r="X119" s="4"/>
-      <c r="Y119" s="4"/>
-      <c r="Z119" s="4"/>
-      <c r="AA119" s="4"/>
-      <c r="AB119" s="4"/>
-      <c r="AC119" s="4"/>
-      <c r="AD119" s="4"/>
-      <c r="AE119" s="4"/>
-      <c r="AF119" s="4"/>
-      <c r="AG119" s="4"/>
-      <c r="AH119" s="4"/>
-      <c r="AI119" s="4"/>
-      <c r="AJ119" s="4"/>
-      <c r="AK119" s="4"/>
-      <c r="AL119" s="4"/>
-      <c r="AM119" s="4"/>
-      <c r="AN119" s="4"/>
-      <c r="AO119" s="4"/>
-      <c r="AP119" s="4"/>
-      <c r="AQ119" s="4"/>
-      <c r="AR119" s="4"/>
-      <c r="AS119" s="4"/>
-      <c r="AT119" s="4"/>
-      <c r="AU119" s="4"/>
-      <c r="AV119" s="4"/>
-      <c r="AW119" s="4"/>
-      <c r="AX119" s="4"/>
-      <c r="AY119" s="4"/>
-      <c r="AZ119" s="4"/>
-      <c r="BA119" s="4"/>
-      <c r="BB119" s="4"/>
-      <c r="BC119" s="4"/>
-      <c r="BD119" s="4"/>
-      <c r="BE119" s="4"/>
-      <c r="BF119" s="4"/>
-      <c r="BG119" s="4"/>
-      <c r="BH119" s="4"/>
-      <c r="BI119" s="4"/>
-      <c r="BJ119" s="4"/>
-      <c r="BK119" s="4"/>
-      <c r="BL119" s="4"/>
-      <c r="BM119" s="4"/>
-      <c r="BN119" s="4"/>
-      <c r="BO119" s="4"/>
-      <c r="BP119" s="4"/>
-      <c r="BQ119" s="4"/>
-      <c r="BR119" s="4"/>
-      <c r="BS119" s="4"/>
-      <c r="BT119" s="4"/>
-      <c r="BU119" s="4"/>
-      <c r="BV119" s="4"/>
-      <c r="BW119" s="4"/>
-      <c r="BX119" s="4"/>
-      <c r="BY119" s="4"/>
-      <c r="BZ119" s="4"/>
-      <c r="CA119" s="4"/>
-      <c r="CB119" s="4"/>
-      <c r="CC119" s="4"/>
-      <c r="CD119" s="4"/>
-      <c r="CE119" s="4"/>
-      <c r="CF119" s="4"/>
-      <c r="CG119" s="4"/>
-      <c r="CH119" s="4"/>
-      <c r="CI119" s="4"/>
-      <c r="CJ119" s="4"/>
-      <c r="CK119" s="4"/>
-      <c r="CL119" s="4"/>
-      <c r="CM119" s="4"/>
-      <c r="CN119" s="4"/>
-      <c r="CO119" s="4"/>
-      <c r="CP119" s="4"/>
-      <c r="CQ119" s="4"/>
-      <c r="CR119" s="4"/>
-      <c r="CS119" s="4"/>
-      <c r="CT119" s="4"/>
-      <c r="CU119" s="4"/>
-      <c r="CV119" s="4"/>
-      <c r="CW119" s="4"/>
-      <c r="CX119" s="4"/>
-      <c r="CY119" s="4"/>
-      <c r="CZ119" s="4"/>
-      <c r="DA119" s="4"/>
-      <c r="DB119" s="4"/>
-      <c r="DC119" s="4"/>
-      <c r="DD119" s="4"/>
-      <c r="DE119" s="4"/>
-      <c r="DF119" s="4"/>
-      <c r="DG119" s="4"/>
-      <c r="DH119" s="4"/>
-      <c r="DI119" s="4"/>
-      <c r="DJ119" s="4"/>
-      <c r="DK119" s="4"/>
-      <c r="DL119" s="4"/>
-      <c r="DM119" s="4"/>
-      <c r="DN119" s="4"/>
-      <c r="DO119" s="4"/>
-      <c r="DP119" s="4"/>
-      <c r="DQ119" s="4"/>
-      <c r="DR119" s="4"/>
-      <c r="DS119" s="4"/>
-      <c r="DT119" s="4"/>
-      <c r="DU119" s="4"/>
-      <c r="DV119" s="4"/>
-      <c r="DW119" s="4"/>
-      <c r="DX119" s="4"/>
-      <c r="DY119" s="4"/>
-      <c r="DZ119" s="4"/>
-      <c r="EA119" s="4"/>
-      <c r="EB119" s="4"/>
-      <c r="EC119" s="4"/>
-      <c r="ED119" s="4"/>
-      <c r="EE119" s="4"/>
-      <c r="EF119" s="4"/>
-      <c r="EG119" s="4"/>
-      <c r="EH119" s="4"/>
-      <c r="EI119" s="4"/>
-      <c r="EJ119" s="4"/>
-      <c r="EK119" s="4"/>
-      <c r="EL119" s="4"/>
-      <c r="EM119" s="4"/>
-      <c r="EN119" s="4"/>
-      <c r="EO119" s="4"/>
-      <c r="EP119" s="4"/>
-      <c r="EQ119" s="4"/>
-      <c r="ER119" s="4"/>
-      <c r="ES119" s="4"/>
-      <c r="ET119" s="4"/>
-      <c r="EU119" s="4"/>
-      <c r="EV119" s="4"/>
-      <c r="EW119" s="4"/>
-      <c r="EX119" s="4"/>
-      <c r="EY119" s="4"/>
-      <c r="EZ119" s="4"/>
-      <c r="FA119" s="4"/>
-      <c r="FB119" s="4"/>
-      <c r="FC119" s="4"/>
-      <c r="FD119" s="4"/>
-      <c r="FE119" s="4"/>
-      <c r="FF119" s="4"/>
-      <c r="FG119" s="4"/>
-      <c r="FH119" s="4"/>
-      <c r="FI119" s="4"/>
-      <c r="FJ119" s="4"/>
-      <c r="FK119" s="4"/>
-      <c r="FL119" s="4"/>
-      <c r="FM119" s="4"/>
-      <c r="FN119" s="4"/>
-      <c r="FO119" s="4"/>
-      <c r="FP119" s="4"/>
-      <c r="FQ119" s="4"/>
-      <c r="FR119" s="4"/>
-      <c r="FS119" s="4"/>
-      <c r="FT119" s="4"/>
-      <c r="FU119" s="4"/>
-      <c r="FV119" s="4"/>
-      <c r="FW119" s="4"/>
-      <c r="FX119" s="4"/>
-      <c r="FY119" s="4"/>
-      <c r="FZ119" s="4"/>
-      <c r="GA119" s="4"/>
-      <c r="GB119" s="4"/>
-      <c r="GC119" s="4"/>
-      <c r="GD119" s="4"/>
-      <c r="GE119" s="4"/>
-      <c r="GF119" s="4"/>
-      <c r="GG119" s="4"/>
-      <c r="GH119" s="4"/>
-      <c r="GI119" s="4"/>
-      <c r="GJ119" s="4"/>
-      <c r="GK119" s="4"/>
-      <c r="GL119" s="4"/>
-      <c r="GM119" s="4"/>
-      <c r="GN119" s="4"/>
-      <c r="GO119" s="4"/>
-      <c r="GP119" s="4"/>
-      <c r="GQ119" s="4"/>
-      <c r="GR119" s="4"/>
-      <c r="GS119" s="4"/>
-      <c r="GT119" s="4"/>
-      <c r="GU119" s="4"/>
-      <c r="GV119" s="4"/>
-      <c r="GW119" s="4"/>
-      <c r="GX119" s="4"/>
-      <c r="GY119" s="4"/>
-      <c r="GZ119" s="4"/>
-      <c r="HA119" s="4"/>
-      <c r="HB119" s="4"/>
-      <c r="HC119" s="4"/>
-      <c r="HD119" s="4"/>
-      <c r="HE119" s="4"/>
-      <c r="HF119" s="4"/>
-      <c r="HG119" s="4"/>
-      <c r="HH119" s="4"/>
-      <c r="HI119" s="4"/>
-      <c r="HJ119" s="4"/>
-      <c r="HK119" s="4"/>
-      <c r="HL119" s="4"/>
-      <c r="HM119" s="4"/>
-      <c r="HN119" s="4"/>
-      <c r="HO119" s="4"/>
-      <c r="HP119" s="4"/>
-      <c r="HQ119" s="4"/>
-      <c r="HR119" s="4"/>
-      <c r="HS119" s="4"/>
-      <c r="HT119" s="4"/>
-      <c r="HU119" s="4"/>
-      <c r="HV119" s="4"/>
-      <c r="HW119" s="4"/>
-      <c r="HX119" s="4"/>
-      <c r="HY119" s="4"/>
-      <c r="HZ119" s="4"/>
-      <c r="IA119" s="4"/>
-      <c r="IB119" s="4"/>
-      <c r="IC119" s="4"/>
-      <c r="ID119" s="4"/>
-      <c r="IE119" s="4"/>
-      <c r="IF119" s="4"/>
-      <c r="IG119" s="4"/>
-      <c r="IH119" s="4"/>
-      <c r="II119" s="4"/>
-    </row>
-    <row r="120" spans="1:243">
-      <c r="B120" s="23"/>
-      <c r="C120" s="23"/>
-      <c r="D120" s="23"/>
-      <c r="Q120" s="4"/>
-      <c r="R120" s="4"/>
-      <c r="S120" s="4"/>
-      <c r="T120" s="4"/>
-      <c r="U120" s="4"/>
-      <c r="V120" s="4"/>
-      <c r="W120" s="4"/>
-      <c r="X120" s="4"/>
-      <c r="Y120" s="4"/>
-      <c r="Z120" s="4"/>
-      <c r="AA120" s="4"/>
-      <c r="AB120" s="4"/>
-      <c r="AC120" s="4"/>
-      <c r="AD120" s="4"/>
-      <c r="AE120" s="4"/>
-      <c r="AF120" s="4"/>
-      <c r="AG120" s="4"/>
-      <c r="AH120" s="4"/>
-      <c r="AI120" s="4"/>
-      <c r="AJ120" s="4"/>
-      <c r="AK120" s="4"/>
-      <c r="AL120" s="4"/>
-      <c r="AM120" s="4"/>
-      <c r="AN120" s="4"/>
-      <c r="AO120" s="4"/>
-      <c r="AP120" s="4"/>
-      <c r="AQ120" s="4"/>
-      <c r="AR120" s="4"/>
-      <c r="AS120" s="4"/>
-      <c r="AT120" s="4"/>
-      <c r="AU120" s="4"/>
-      <c r="AV120" s="4"/>
-      <c r="AW120" s="4"/>
-      <c r="AX120" s="4"/>
-      <c r="AY120" s="4"/>
-      <c r="AZ120" s="4"/>
-      <c r="BA120" s="4"/>
-      <c r="BB120" s="4"/>
-      <c r="BC120" s="4"/>
-      <c r="BD120" s="4"/>
-      <c r="BE120" s="4"/>
-      <c r="BF120" s="4"/>
-      <c r="BG120" s="4"/>
-      <c r="BH120" s="4"/>
-      <c r="BI120" s="4"/>
-      <c r="BJ120" s="4"/>
-      <c r="BK120" s="4"/>
-      <c r="BL120" s="4"/>
-      <c r="BM120" s="4"/>
-      <c r="BN120" s="4"/>
-      <c r="BO120" s="4"/>
-      <c r="BP120" s="4"/>
-      <c r="BQ120" s="4"/>
-      <c r="BR120" s="4"/>
-      <c r="BS120" s="4"/>
-      <c r="BT120" s="4"/>
-      <c r="BU120" s="4"/>
-      <c r="BV120" s="4"/>
-      <c r="BW120" s="4"/>
-      <c r="BX120" s="4"/>
-      <c r="BY120" s="4"/>
-      <c r="BZ120" s="4"/>
-      <c r="CA120" s="4"/>
-      <c r="CB120" s="4"/>
-      <c r="CC120" s="4"/>
-      <c r="CD120" s="4"/>
-      <c r="CE120" s="4"/>
-      <c r="CF120" s="4"/>
-      <c r="CG120" s="4"/>
-      <c r="CH120" s="4"/>
-      <c r="CI120" s="4"/>
-      <c r="CJ120" s="4"/>
-      <c r="CK120" s="4"/>
-      <c r="CL120" s="4"/>
-      <c r="CM120" s="4"/>
-      <c r="CN120" s="4"/>
-      <c r="CO120" s="4"/>
-      <c r="CP120" s="4"/>
-      <c r="CQ120" s="4"/>
-      <c r="CR120" s="4"/>
-      <c r="CS120" s="4"/>
-      <c r="CT120" s="4"/>
-      <c r="CU120" s="4"/>
-      <c r="CV120" s="4"/>
-      <c r="CW120" s="4"/>
-      <c r="CX120" s="4"/>
-      <c r="CY120" s="4"/>
-      <c r="CZ120" s="4"/>
-      <c r="DA120" s="4"/>
-      <c r="DB120" s="4"/>
-      <c r="DC120" s="4"/>
-      <c r="DD120" s="4"/>
-      <c r="DE120" s="4"/>
-      <c r="DF120" s="4"/>
-      <c r="DG120" s="4"/>
-      <c r="DH120" s="4"/>
-      <c r="DI120" s="4"/>
-      <c r="DJ120" s="4"/>
-      <c r="DK120" s="4"/>
-      <c r="DL120" s="4"/>
-      <c r="DM120" s="4"/>
-      <c r="DN120" s="4"/>
-      <c r="DO120" s="4"/>
-      <c r="DP120" s="4"/>
-      <c r="DQ120" s="4"/>
-      <c r="DR120" s="4"/>
-      <c r="DS120" s="4"/>
-      <c r="DT120" s="4"/>
-      <c r="DU120" s="4"/>
-      <c r="DV120" s="4"/>
-      <c r="DW120" s="4"/>
-      <c r="DX120" s="4"/>
-      <c r="DY120" s="4"/>
-      <c r="DZ120" s="4"/>
-      <c r="EA120" s="4"/>
-      <c r="EB120" s="4"/>
-      <c r="EC120" s="4"/>
-      <c r="ED120" s="4"/>
-      <c r="EE120" s="4"/>
-      <c r="EF120" s="4"/>
-      <c r="EG120" s="4"/>
-      <c r="EH120" s="4"/>
-      <c r="EI120" s="4"/>
-      <c r="EJ120" s="4"/>
-      <c r="EK120" s="4"/>
-      <c r="EL120" s="4"/>
-      <c r="EM120" s="4"/>
-      <c r="EN120" s="4"/>
-      <c r="EO120" s="4"/>
-      <c r="EP120" s="4"/>
-      <c r="EQ120" s="4"/>
-      <c r="ER120" s="4"/>
-      <c r="ES120" s="4"/>
-      <c r="ET120" s="4"/>
-      <c r="EU120" s="4"/>
-      <c r="EV120" s="4"/>
-      <c r="EW120" s="4"/>
-      <c r="EX120" s="4"/>
-      <c r="EY120" s="4"/>
-      <c r="EZ120" s="4"/>
-      <c r="FA120" s="4"/>
-      <c r="FB120" s="4"/>
-      <c r="FC120" s="4"/>
-      <c r="FD120" s="4"/>
-      <c r="FE120" s="4"/>
-      <c r="FF120" s="4"/>
-      <c r="FG120" s="4"/>
-      <c r="FH120" s="4"/>
-      <c r="FI120" s="4"/>
-      <c r="FJ120" s="4"/>
-      <c r="FK120" s="4"/>
-      <c r="FL120" s="4"/>
-      <c r="FM120" s="4"/>
-      <c r="FN120" s="4"/>
-      <c r="FO120" s="4"/>
-      <c r="FP120" s="4"/>
-      <c r="FQ120" s="4"/>
-      <c r="FR120" s="4"/>
-      <c r="FS120" s="4"/>
-      <c r="FT120" s="4"/>
-      <c r="FU120" s="4"/>
-      <c r="FV120" s="4"/>
-      <c r="FW120" s="4"/>
-      <c r="FX120" s="4"/>
-      <c r="FY120" s="4"/>
-      <c r="FZ120" s="4"/>
-      <c r="GA120" s="4"/>
-      <c r="GB120" s="4"/>
-      <c r="GC120" s="4"/>
-      <c r="GD120" s="4"/>
-      <c r="GE120" s="4"/>
-      <c r="GF120" s="4"/>
-      <c r="GG120" s="4"/>
-      <c r="GH120" s="4"/>
-      <c r="GI120" s="4"/>
-      <c r="GJ120" s="4"/>
-      <c r="GK120" s="4"/>
-      <c r="GL120" s="4"/>
-      <c r="GM120" s="4"/>
-      <c r="GN120" s="4"/>
-      <c r="GO120" s="4"/>
-      <c r="GP120" s="4"/>
-      <c r="GQ120" s="4"/>
-      <c r="GR120" s="4"/>
-      <c r="GS120" s="4"/>
-      <c r="GT120" s="4"/>
-      <c r="GU120" s="4"/>
-      <c r="GV120" s="4"/>
-      <c r="GW120" s="4"/>
-      <c r="GX120" s="4"/>
-      <c r="GY120" s="4"/>
-      <c r="GZ120" s="4"/>
-      <c r="HA120" s="4"/>
-      <c r="HB120" s="4"/>
-      <c r="HC120" s="4"/>
-      <c r="HD120" s="4"/>
-      <c r="HE120" s="4"/>
-      <c r="HF120" s="4"/>
-      <c r="HG120" s="4"/>
-      <c r="HH120" s="4"/>
-      <c r="HI120" s="4"/>
-      <c r="HJ120" s="4"/>
-      <c r="HK120" s="4"/>
-      <c r="HL120" s="4"/>
-      <c r="HM120" s="4"/>
-      <c r="HN120" s="4"/>
-      <c r="HO120" s="4"/>
-      <c r="HP120" s="4"/>
-      <c r="HQ120" s="4"/>
-      <c r="HR120" s="4"/>
-      <c r="HS120" s="4"/>
-      <c r="HT120" s="4"/>
-      <c r="HU120" s="4"/>
-      <c r="HV120" s="4"/>
-      <c r="HW120" s="4"/>
-      <c r="HX120" s="4"/>
-      <c r="HY120" s="4"/>
-      <c r="HZ120" s="4"/>
-      <c r="IA120" s="4"/>
-      <c r="IB120" s="4"/>
-      <c r="IC120" s="4"/>
-      <c r="ID120" s="4"/>
-      <c r="IE120" s="4"/>
-      <c r="IF120" s="4"/>
-      <c r="IG120" s="4"/>
-      <c r="IH120" s="4"/>
-      <c r="II120" s="4"/>
-    </row>
-    <row r="121" spans="1:243" ht="17">
-      <c r="B121" s="23"/>
-      <c r="C121" s="23"/>
-      <c r="D121" s="23"/>
-      <c r="L121" s="38"/>
-    </row>
-    <row r="122" spans="1:243">
-      <c r="B122" s="23"/>
-      <c r="C122" s="23"/>
-      <c r="D122" s="23"/>
-      <c r="H122" s="22"/>
-    </row>
-    <row r="123" spans="1:243">
-      <c r="B123" s="23"/>
-      <c r="C123" s="23"/>
-      <c r="D123" s="23"/>
-    </row>
-    <row r="124" spans="1:243">
-      <c r="B124" s="23"/>
-      <c r="C124" s="23"/>
-      <c r="D124" s="23"/>
-    </row>
-    <row r="125" spans="1:243">
-      <c r="B125" s="23"/>
-      <c r="C125" s="23"/>
-      <c r="D125" s="23"/>
-    </row>
-    <row r="126" spans="1:243">
-      <c r="B126" s="23"/>
-      <c r="C126" s="23"/>
-      <c r="D126" s="23"/>
-    </row>
-    <row r="127" spans="1:243">
-      <c r="B127" s="23"/>
-      <c r="C127" s="23"/>
-      <c r="D127" s="23"/>
-    </row>
-    <row r="128" spans="1:243" ht="16.75" customHeight="1"/>
+        <v>3640</v>
+      </c>
+      <c r="N188" s="43">
+        <f>SUM(N2:N187)</f>
+        <v>26101</v>
+      </c>
+      <c r="O188" s="43">
+        <f>SUM(O2:O187)</f>
+        <v>196106</v>
+      </c>
+      <c r="P188" s="43">
+        <f>SUM(P2:P187)</f>
+        <v>54945</v>
+      </c>
+      <c r="Q188" s="43">
+        <f>SUM(Q2:Q187)</f>
+        <v>207</v>
+      </c>
+    </row>
+    <row r="189" spans="1:243">
+      <c r="A189" s="25"/>
+    </row>
+    <row r="190" spans="1:243">
+      <c r="A190" s="4"/>
+      <c r="C190" s="4"/>
+      <c r="D190" s="4"/>
+      <c r="E190" s="4"/>
+      <c r="F190" s="4"/>
+      <c r="G190" s="4"/>
+      <c r="H190" s="4"/>
+      <c r="I190" s="4"/>
+      <c r="J190" s="4"/>
+      <c r="N190" s="4"/>
+      <c r="Q190" s="4"/>
+      <c r="R190" s="4"/>
+      <c r="S190" s="4"/>
+      <c r="T190" s="4"/>
+      <c r="U190" s="4"/>
+      <c r="V190" s="4"/>
+      <c r="W190" s="4"/>
+      <c r="X190" s="4"/>
+      <c r="Y190" s="4"/>
+      <c r="Z190" s="4"/>
+      <c r="AA190" s="4"/>
+      <c r="AB190" s="4"/>
+      <c r="AC190" s="4"/>
+      <c r="AD190" s="4"/>
+      <c r="AE190" s="4"/>
+      <c r="AF190" s="4"/>
+      <c r="AG190" s="4"/>
+      <c r="AH190" s="4"/>
+      <c r="AI190" s="4"/>
+      <c r="AJ190" s="4"/>
+      <c r="AK190" s="4"/>
+      <c r="AL190" s="4"/>
+      <c r="AM190" s="4"/>
+      <c r="AN190" s="4"/>
+      <c r="AO190" s="4"/>
+      <c r="AP190" s="4"/>
+      <c r="AQ190" s="4"/>
+      <c r="AR190" s="4"/>
+      <c r="AS190" s="4"/>
+      <c r="AT190" s="4"/>
+      <c r="AU190" s="4"/>
+      <c r="AV190" s="4"/>
+      <c r="AW190" s="4"/>
+      <c r="AX190" s="4"/>
+      <c r="AY190" s="4"/>
+      <c r="AZ190" s="4"/>
+      <c r="BA190" s="4"/>
+      <c r="BB190" s="4"/>
+      <c r="BC190" s="4"/>
+      <c r="BD190" s="4"/>
+      <c r="BE190" s="4"/>
+      <c r="BF190" s="4"/>
+      <c r="BG190" s="4"/>
+      <c r="BH190" s="4"/>
+      <c r="BI190" s="4"/>
+      <c r="BJ190" s="4"/>
+      <c r="BK190" s="4"/>
+      <c r="BL190" s="4"/>
+      <c r="BM190" s="4"/>
+      <c r="BN190" s="4"/>
+      <c r="BO190" s="4"/>
+      <c r="BP190" s="4"/>
+      <c r="BQ190" s="4"/>
+      <c r="BR190" s="4"/>
+      <c r="BS190" s="4"/>
+      <c r="BT190" s="4"/>
+      <c r="BU190" s="4"/>
+      <c r="BV190" s="4"/>
+      <c r="BW190" s="4"/>
+      <c r="BX190" s="4"/>
+      <c r="BY190" s="4"/>
+      <c r="BZ190" s="4"/>
+      <c r="CA190" s="4"/>
+      <c r="CB190" s="4"/>
+      <c r="CC190" s="4"/>
+      <c r="CD190" s="4"/>
+      <c r="CE190" s="4"/>
+      <c r="CF190" s="4"/>
+      <c r="CG190" s="4"/>
+      <c r="CH190" s="4"/>
+      <c r="CI190" s="4"/>
+      <c r="CJ190" s="4"/>
+      <c r="CK190" s="4"/>
+      <c r="CL190" s="4"/>
+      <c r="CM190" s="4"/>
+      <c r="CN190" s="4"/>
+      <c r="CO190" s="4"/>
+      <c r="CP190" s="4"/>
+      <c r="CQ190" s="4"/>
+      <c r="CR190" s="4"/>
+      <c r="CS190" s="4"/>
+      <c r="CT190" s="4"/>
+      <c r="CU190" s="4"/>
+      <c r="CV190" s="4"/>
+      <c r="CW190" s="4"/>
+      <c r="CX190" s="4"/>
+      <c r="CY190" s="4"/>
+      <c r="CZ190" s="4"/>
+      <c r="DA190" s="4"/>
+      <c r="DB190" s="4"/>
+      <c r="DC190" s="4"/>
+      <c r="DD190" s="4"/>
+      <c r="DE190" s="4"/>
+      <c r="DF190" s="4"/>
+      <c r="DG190" s="4"/>
+      <c r="DH190" s="4"/>
+      <c r="DI190" s="4"/>
+      <c r="DJ190" s="4"/>
+      <c r="DK190" s="4"/>
+      <c r="DL190" s="4"/>
+      <c r="DM190" s="4"/>
+      <c r="DN190" s="4"/>
+      <c r="DO190" s="4"/>
+      <c r="DP190" s="4"/>
+      <c r="DQ190" s="4"/>
+      <c r="DR190" s="4"/>
+      <c r="DS190" s="4"/>
+      <c r="DT190" s="4"/>
+      <c r="DU190" s="4"/>
+      <c r="DV190" s="4"/>
+      <c r="DW190" s="4"/>
+      <c r="DX190" s="4"/>
+      <c r="DY190" s="4"/>
+      <c r="DZ190" s="4"/>
+      <c r="EA190" s="4"/>
+      <c r="EB190" s="4"/>
+      <c r="EC190" s="4"/>
+      <c r="ED190" s="4"/>
+      <c r="EE190" s="4"/>
+      <c r="EF190" s="4"/>
+      <c r="EG190" s="4"/>
+      <c r="EH190" s="4"/>
+      <c r="EI190" s="4"/>
+      <c r="EJ190" s="4"/>
+      <c r="EK190" s="4"/>
+      <c r="EL190" s="4"/>
+      <c r="EM190" s="4"/>
+      <c r="EN190" s="4"/>
+      <c r="EO190" s="4"/>
+      <c r="EP190" s="4"/>
+      <c r="EQ190" s="4"/>
+      <c r="ER190" s="4"/>
+      <c r="ES190" s="4"/>
+      <c r="ET190" s="4"/>
+      <c r="EU190" s="4"/>
+      <c r="EV190" s="4"/>
+      <c r="EW190" s="4"/>
+      <c r="EX190" s="4"/>
+      <c r="EY190" s="4"/>
+      <c r="EZ190" s="4"/>
+      <c r="FA190" s="4"/>
+      <c r="FB190" s="4"/>
+      <c r="FC190" s="4"/>
+      <c r="FD190" s="4"/>
+      <c r="FE190" s="4"/>
+      <c r="FF190" s="4"/>
+      <c r="FG190" s="4"/>
+      <c r="FH190" s="4"/>
+      <c r="FI190" s="4"/>
+      <c r="FJ190" s="4"/>
+      <c r="FK190" s="4"/>
+      <c r="FL190" s="4"/>
+      <c r="FM190" s="4"/>
+      <c r="FN190" s="4"/>
+      <c r="FO190" s="4"/>
+      <c r="FP190" s="4"/>
+      <c r="FQ190" s="4"/>
+      <c r="FR190" s="4"/>
+      <c r="FS190" s="4"/>
+      <c r="FT190" s="4"/>
+      <c r="FU190" s="4"/>
+      <c r="FV190" s="4"/>
+      <c r="FW190" s="4"/>
+      <c r="FX190" s="4"/>
+      <c r="FY190" s="4"/>
+      <c r="FZ190" s="4"/>
+      <c r="GA190" s="4"/>
+      <c r="GB190" s="4"/>
+      <c r="GC190" s="4"/>
+      <c r="GD190" s="4"/>
+      <c r="GE190" s="4"/>
+      <c r="GF190" s="4"/>
+      <c r="GG190" s="4"/>
+      <c r="GH190" s="4"/>
+      <c r="GI190" s="4"/>
+      <c r="GJ190" s="4"/>
+      <c r="GK190" s="4"/>
+      <c r="GL190" s="4"/>
+      <c r="GM190" s="4"/>
+      <c r="GN190" s="4"/>
+      <c r="GO190" s="4"/>
+      <c r="GP190" s="4"/>
+      <c r="GQ190" s="4"/>
+      <c r="GR190" s="4"/>
+      <c r="GS190" s="4"/>
+      <c r="GT190" s="4"/>
+      <c r="GU190" s="4"/>
+      <c r="GV190" s="4"/>
+      <c r="GW190" s="4"/>
+      <c r="GX190" s="4"/>
+      <c r="GY190" s="4"/>
+      <c r="GZ190" s="4"/>
+      <c r="HA190" s="4"/>
+      <c r="HB190" s="4"/>
+      <c r="HC190" s="4"/>
+      <c r="HD190" s="4"/>
+      <c r="HE190" s="4"/>
+      <c r="HF190" s="4"/>
+      <c r="HG190" s="4"/>
+      <c r="HH190" s="4"/>
+      <c r="HI190" s="4"/>
+      <c r="HJ190" s="4"/>
+      <c r="HK190" s="4"/>
+      <c r="HL190" s="4"/>
+      <c r="HM190" s="4"/>
+      <c r="HN190" s="4"/>
+      <c r="HO190" s="4"/>
+      <c r="HP190" s="4"/>
+      <c r="HQ190" s="4"/>
+      <c r="HR190" s="4"/>
+      <c r="HS190" s="4"/>
+      <c r="HT190" s="4"/>
+      <c r="HU190" s="4"/>
+      <c r="HV190" s="4"/>
+      <c r="HW190" s="4"/>
+      <c r="HX190" s="4"/>
+      <c r="HY190" s="4"/>
+      <c r="HZ190" s="4"/>
+      <c r="IA190" s="4"/>
+      <c r="IB190" s="4"/>
+      <c r="IC190" s="4"/>
+      <c r="ID190" s="4"/>
+      <c r="IE190" s="4"/>
+      <c r="IF190" s="4"/>
+      <c r="IG190" s="4"/>
+      <c r="IH190" s="4"/>
+      <c r="II190" s="4"/>
+    </row>
+    <row r="191" spans="1:243">
+      <c r="B191" s="23"/>
+      <c r="C191" s="23"/>
+      <c r="D191" s="23"/>
+      <c r="Q191" s="4"/>
+      <c r="R191" s="4"/>
+      <c r="S191" s="4"/>
+      <c r="T191" s="4"/>
+      <c r="U191" s="4"/>
+      <c r="V191" s="4"/>
+      <c r="W191" s="4"/>
+      <c r="X191" s="4"/>
+      <c r="Y191" s="4"/>
+      <c r="Z191" s="4"/>
+      <c r="AA191" s="4"/>
+      <c r="AB191" s="4"/>
+      <c r="AC191" s="4"/>
+      <c r="AD191" s="4"/>
+      <c r="AE191" s="4"/>
+      <c r="AF191" s="4"/>
+      <c r="AG191" s="4"/>
+      <c r="AH191" s="4"/>
+      <c r="AI191" s="4"/>
+      <c r="AJ191" s="4"/>
+      <c r="AK191" s="4"/>
+      <c r="AL191" s="4"/>
+      <c r="AM191" s="4"/>
+      <c r="AN191" s="4"/>
+      <c r="AO191" s="4"/>
+      <c r="AP191" s="4"/>
+      <c r="AQ191" s="4"/>
+      <c r="AR191" s="4"/>
+      <c r="AS191" s="4"/>
+      <c r="AT191" s="4"/>
+      <c r="AU191" s="4"/>
+      <c r="AV191" s="4"/>
+      <c r="AW191" s="4"/>
+      <c r="AX191" s="4"/>
+      <c r="AY191" s="4"/>
+      <c r="AZ191" s="4"/>
+      <c r="BA191" s="4"/>
+      <c r="BB191" s="4"/>
+      <c r="BC191" s="4"/>
+      <c r="BD191" s="4"/>
+      <c r="BE191" s="4"/>
+      <c r="BF191" s="4"/>
+      <c r="BG191" s="4"/>
+      <c r="BH191" s="4"/>
+      <c r="BI191" s="4"/>
+      <c r="BJ191" s="4"/>
+      <c r="BK191" s="4"/>
+      <c r="BL191" s="4"/>
+      <c r="BM191" s="4"/>
+      <c r="BN191" s="4"/>
+      <c r="BO191" s="4"/>
+      <c r="BP191" s="4"/>
+      <c r="BQ191" s="4"/>
+      <c r="BR191" s="4"/>
+      <c r="BS191" s="4"/>
+      <c r="BT191" s="4"/>
+      <c r="BU191" s="4"/>
+      <c r="BV191" s="4"/>
+      <c r="BW191" s="4"/>
+      <c r="BX191" s="4"/>
+      <c r="BY191" s="4"/>
+      <c r="BZ191" s="4"/>
+      <c r="CA191" s="4"/>
+      <c r="CB191" s="4"/>
+      <c r="CC191" s="4"/>
+      <c r="CD191" s="4"/>
+      <c r="CE191" s="4"/>
+      <c r="CF191" s="4"/>
+      <c r="CG191" s="4"/>
+      <c r="CH191" s="4"/>
+      <c r="CI191" s="4"/>
+      <c r="CJ191" s="4"/>
+      <c r="CK191" s="4"/>
+      <c r="CL191" s="4"/>
+      <c r="CM191" s="4"/>
+      <c r="CN191" s="4"/>
+      <c r="CO191" s="4"/>
+      <c r="CP191" s="4"/>
+      <c r="CQ191" s="4"/>
+      <c r="CR191" s="4"/>
+      <c r="CS191" s="4"/>
+      <c r="CT191" s="4"/>
+      <c r="CU191" s="4"/>
+      <c r="CV191" s="4"/>
+      <c r="CW191" s="4"/>
+      <c r="CX191" s="4"/>
+      <c r="CY191" s="4"/>
+      <c r="CZ191" s="4"/>
+      <c r="DA191" s="4"/>
+      <c r="DB191" s="4"/>
+      <c r="DC191" s="4"/>
+      <c r="DD191" s="4"/>
+      <c r="DE191" s="4"/>
+      <c r="DF191" s="4"/>
+      <c r="DG191" s="4"/>
+      <c r="DH191" s="4"/>
+      <c r="DI191" s="4"/>
+      <c r="DJ191" s="4"/>
+      <c r="DK191" s="4"/>
+      <c r="DL191" s="4"/>
+      <c r="DM191" s="4"/>
+      <c r="DN191" s="4"/>
+      <c r="DO191" s="4"/>
+      <c r="DP191" s="4"/>
+      <c r="DQ191" s="4"/>
+      <c r="DR191" s="4"/>
+      <c r="DS191" s="4"/>
+      <c r="DT191" s="4"/>
+      <c r="DU191" s="4"/>
+      <c r="DV191" s="4"/>
+      <c r="DW191" s="4"/>
+      <c r="DX191" s="4"/>
+      <c r="DY191" s="4"/>
+      <c r="DZ191" s="4"/>
+      <c r="EA191" s="4"/>
+      <c r="EB191" s="4"/>
+      <c r="EC191" s="4"/>
+      <c r="ED191" s="4"/>
+      <c r="EE191" s="4"/>
+      <c r="EF191" s="4"/>
+      <c r="EG191" s="4"/>
+      <c r="EH191" s="4"/>
+      <c r="EI191" s="4"/>
+      <c r="EJ191" s="4"/>
+      <c r="EK191" s="4"/>
+      <c r="EL191" s="4"/>
+      <c r="EM191" s="4"/>
+      <c r="EN191" s="4"/>
+      <c r="EO191" s="4"/>
+      <c r="EP191" s="4"/>
+      <c r="EQ191" s="4"/>
+      <c r="ER191" s="4"/>
+      <c r="ES191" s="4"/>
+      <c r="ET191" s="4"/>
+      <c r="EU191" s="4"/>
+      <c r="EV191" s="4"/>
+      <c r="EW191" s="4"/>
+      <c r="EX191" s="4"/>
+      <c r="EY191" s="4"/>
+      <c r="EZ191" s="4"/>
+      <c r="FA191" s="4"/>
+      <c r="FB191" s="4"/>
+      <c r="FC191" s="4"/>
+      <c r="FD191" s="4"/>
+      <c r="FE191" s="4"/>
+      <c r="FF191" s="4"/>
+      <c r="FG191" s="4"/>
+      <c r="FH191" s="4"/>
+      <c r="FI191" s="4"/>
+      <c r="FJ191" s="4"/>
+      <c r="FK191" s="4"/>
+      <c r="FL191" s="4"/>
+      <c r="FM191" s="4"/>
+      <c r="FN191" s="4"/>
+      <c r="FO191" s="4"/>
+      <c r="FP191" s="4"/>
+      <c r="FQ191" s="4"/>
+      <c r="FR191" s="4"/>
+      <c r="FS191" s="4"/>
+      <c r="FT191" s="4"/>
+      <c r="FU191" s="4"/>
+      <c r="FV191" s="4"/>
+      <c r="FW191" s="4"/>
+      <c r="FX191" s="4"/>
+      <c r="FY191" s="4"/>
+      <c r="FZ191" s="4"/>
+      <c r="GA191" s="4"/>
+      <c r="GB191" s="4"/>
+      <c r="GC191" s="4"/>
+      <c r="GD191" s="4"/>
+      <c r="GE191" s="4"/>
+      <c r="GF191" s="4"/>
+      <c r="GG191" s="4"/>
+      <c r="GH191" s="4"/>
+      <c r="GI191" s="4"/>
+      <c r="GJ191" s="4"/>
+      <c r="GK191" s="4"/>
+      <c r="GL191" s="4"/>
+      <c r="GM191" s="4"/>
+      <c r="GN191" s="4"/>
+      <c r="GO191" s="4"/>
+      <c r="GP191" s="4"/>
+      <c r="GQ191" s="4"/>
+      <c r="GR191" s="4"/>
+      <c r="GS191" s="4"/>
+      <c r="GT191" s="4"/>
+      <c r="GU191" s="4"/>
+      <c r="GV191" s="4"/>
+      <c r="GW191" s="4"/>
+      <c r="GX191" s="4"/>
+      <c r="GY191" s="4"/>
+      <c r="GZ191" s="4"/>
+      <c r="HA191" s="4"/>
+      <c r="HB191" s="4"/>
+      <c r="HC191" s="4"/>
+      <c r="HD191" s="4"/>
+      <c r="HE191" s="4"/>
+      <c r="HF191" s="4"/>
+      <c r="HG191" s="4"/>
+      <c r="HH191" s="4"/>
+      <c r="HI191" s="4"/>
+      <c r="HJ191" s="4"/>
+      <c r="HK191" s="4"/>
+      <c r="HL191" s="4"/>
+      <c r="HM191" s="4"/>
+      <c r="HN191" s="4"/>
+      <c r="HO191" s="4"/>
+      <c r="HP191" s="4"/>
+      <c r="HQ191" s="4"/>
+      <c r="HR191" s="4"/>
+      <c r="HS191" s="4"/>
+      <c r="HT191" s="4"/>
+      <c r="HU191" s="4"/>
+      <c r="HV191" s="4"/>
+      <c r="HW191" s="4"/>
+      <c r="HX191" s="4"/>
+      <c r="HY191" s="4"/>
+      <c r="HZ191" s="4"/>
+      <c r="IA191" s="4"/>
+      <c r="IB191" s="4"/>
+      <c r="IC191" s="4"/>
+      <c r="ID191" s="4"/>
+      <c r="IE191" s="4"/>
+      <c r="IF191" s="4"/>
+      <c r="IG191" s="4"/>
+      <c r="IH191" s="4"/>
+      <c r="II191" s="4"/>
+    </row>
+    <row r="192" spans="1:243" ht="17.399999999999999">
+      <c r="B192" s="23"/>
+      <c r="C192" s="23"/>
+      <c r="D192" s="23"/>
+      <c r="L192" s="38"/>
+    </row>
+    <row r="193" spans="2:8" ht="15">
+      <c r="B193" s="23"/>
+      <c r="C193" s="23"/>
+      <c r="D193" s="23"/>
+      <c r="H193" s="22"/>
+    </row>
+    <row r="194" spans="2:8">
+      <c r="B194" s="23"/>
+      <c r="C194" s="23"/>
+      <c r="D194" s="23"/>
+    </row>
+    <row r="195" spans="2:8">
+      <c r="B195" s="23"/>
+      <c r="C195" s="23"/>
+      <c r="D195" s="23"/>
+    </row>
+    <row r="196" spans="2:8">
+      <c r="B196" s="23"/>
+      <c r="C196" s="23"/>
+      <c r="D196" s="23"/>
+    </row>
+    <row r="197" spans="2:8">
+      <c r="B197" s="23"/>
+      <c r="C197" s="23"/>
+      <c r="D197" s="23"/>
+    </row>
+    <row r="198" spans="2:8">
+      <c r="B198" s="23"/>
+      <c r="C198" s="23"/>
+      <c r="D198" s="23"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
